--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6.68</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.54</v>
+        <v>1.77</v>
       </c>
       <c r="O53" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P53" t="n">
-        <v>1.84</v>
+        <v>3.69</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8879,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.77</v>
+        <v>2.65</v>
       </c>
       <c r="O54" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P54" t="n">
-        <v>3.69</v>
+        <v>2.26</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -12449,22 +12449,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12926,22 +12926,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,22 +13085,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18374,13 +18374,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
@@ -18413,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="O114" t="n">
-        <v>3.25</v>
+        <v>4.27</v>
       </c>
       <c r="P114" t="n">
-        <v>2.72</v>
+        <v>6.59</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18572,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G125" t="n">

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU127"/>
+  <dimension ref="A1:AU126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.73</v>
+        <v>1.85</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>1.62</v>
+        <v>3.59</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46229.375</v>
+        <v>46229.39583333334</v>
       </c>
     </row>
     <row r="27">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4971,27 +4971,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="AU29" s="3" t="n">
-        <v>46229.39583333334</v>
+        <v>46229.40625</v>
       </c>
     </row>
     <row r="30">
@@ -5130,27 +5130,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46229.40625</v>
+        <v>46229.41666666666</v>
       </c>
     </row>
     <row r="31">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46229.41666666666</v>
+        <v>46229.44791666666</v>
       </c>
     </row>
     <row r="35">
@@ -5925,27 +5925,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="AU35" s="3" t="n">
-        <v>46229.44791666666</v>
+        <v>46229.45833333334</v>
       </c>
     </row>
     <row r="36">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="O36" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>5.39</v>
+        <v>7.55</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="P39" t="n">
-        <v>7.55</v>
+        <v>5.39</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>46229.45833333334</v>
+        <v>46229.47916666666</v>
       </c>
     </row>
     <row r="41">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="AU44" s="3" t="n">
-        <v>46229.47916666666</v>
+        <v>46229.5</v>
       </c>
     </row>
     <row r="45">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3.54</v>
+        <v>2.23</v>
       </c>
       <c r="O48" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P48" t="n">
-        <v>1.84</v>
+        <v>2.57</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9264,27 +9264,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>46229.5</v>
+        <v>46229.52083333334</v>
       </c>
     </row>
     <row r="57">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10059,27 +10059,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46229.52083333334</v>
+        <v>46229.53125</v>
       </c>
     </row>
     <row r="62">
@@ -10218,27 +10218,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46229.53125</v>
+        <v>46229.54166666666</v>
       </c>
     </row>
     <row r="63">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>3.74</v>
+        <v>4.08</v>
       </c>
       <c r="O68" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P68" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>46229.54166666666</v>
+        <v>46229.5625</v>
       </c>
     </row>
     <row r="69">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11649,27 +11649,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11799,7 +11799,7 @@
         <v>0</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>46229.5625</v>
+        <v>46229.58333333334</v>
       </c>
     </row>
     <row r="72">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11967,27 +11967,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12117,7 +12117,7 @@
         <v>0</v>
       </c>
       <c r="AU73" s="3" t="n">
-        <v>46229.58333333334</v>
+        <v>46229.59375</v>
       </c>
     </row>
     <row r="74">
@@ -12126,27 +12126,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>46229.59375</v>
+        <v>46229.60416666666</v>
       </c>
     </row>
     <row r="75">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12435,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>46229.60416666666</v>
+        <v>46229.625</v>
       </c>
     </row>
     <row r="76">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12926,22 +12926,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,22 +13085,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13557,27 +13557,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46229.625</v>
+        <v>46229.63541666666</v>
       </c>
     </row>
     <row r="84">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46229.63541666666</v>
+        <v>46229.64583333334</v>
       </c>
     </row>
     <row r="87">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14357,22 +14357,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14511,12 +14511,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>46229.64583333334</v>
+        <v>46229.66666666666</v>
       </c>
     </row>
     <row r="90">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="O98" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P98" t="n">
-        <v>3.54</v>
+        <v>4.27</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16578,12 +16578,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,64 +16625,64 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -16695,10 +16695,10 @@
         </is>
       </c>
       <c r="AJ102" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK102" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL102" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="AU102" s="3" t="n">
-        <v>46229.66666666666</v>
+        <v>46229.67708333334</v>
       </c>
     </row>
     <row r="103">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,64 +16784,64 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -16854,10 +16854,10 @@
         </is>
       </c>
       <c r="AJ103" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK103" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL103" t="n">
         <v>0</v>
@@ -16896,12 +16896,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17046,7 +17046,7 @@
         <v>0</v>
       </c>
       <c r="AU104" s="3" t="n">
-        <v>46229.67708333334</v>
+        <v>46229.6875</v>
       </c>
     </row>
     <row r="105">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17205,7 +17205,7 @@
         <v>0</v>
       </c>
       <c r="AU105" s="3" t="n">
-        <v>46229.6875</v>
+        <v>46229.75</v>
       </c>
     </row>
     <row r="106">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17532,12 +17532,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17682,7 +17682,7 @@
         <v>0</v>
       </c>
       <c r="AU108" s="3" t="n">
-        <v>46229.75</v>
+        <v>46229.76041666666</v>
       </c>
     </row>
     <row r="109">
@@ -17691,12 +17691,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17738,13 +17738,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -17841,7 +17841,7 @@
         <v>0</v>
       </c>
       <c r="AU109" s="3" t="n">
-        <v>46229.76041666666</v>
+        <v>46229.77083333334</v>
       </c>
     </row>
     <row r="110">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -17936,10 +17936,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18572,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18963,7 +18963,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="O117" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="P117" t="n">
-        <v>5.14</v>
+        <v>3.29</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="AU117" s="3" t="n">
-        <v>46229.77083333334</v>
+        <v>46229.8125</v>
       </c>
     </row>
     <row r="118">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19431,7 +19431,7 @@
         <v>0</v>
       </c>
       <c r="AU119" s="3" t="n">
-        <v>46229.8125</v>
+        <v>46229.83333333334</v>
       </c>
     </row>
     <row r="120">
@@ -19440,12 +19440,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19590,7 +19590,7 @@
         <v>0</v>
       </c>
       <c r="AU120" s="3" t="n">
-        <v>46229.83333333334</v>
+        <v>46229.85416666666</v>
       </c>
     </row>
     <row r="121">
@@ -19758,12 +19758,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19908,7 +19908,7 @@
         <v>0</v>
       </c>
       <c r="AU122" s="3" t="n">
-        <v>46229.85416666666</v>
+        <v>46229.875</v>
       </c>
     </row>
     <row r="123">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20235,12 +20235,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20282,64 +20282,64 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U125" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W125" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD125" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG125" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20352,10 +20352,10 @@
         </is>
       </c>
       <c r="AJ125" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK125" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL125" t="n">
         <v>0</v>
@@ -20385,7 +20385,7 @@
         <v>0</v>
       </c>
       <c r="AU125" s="3" t="n">
-        <v>46229.875</v>
+        <v>46229.89583333334</v>
       </c>
     </row>
     <row r="126">
@@ -20394,12 +20394,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20441,64 +20441,64 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X126" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20511,10 +20511,10 @@
         </is>
       </c>
       <c r="AJ126" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AK126" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL126" t="n">
         <v>0</v>
@@ -20544,165 +20544,6 @@
         <v>0</v>
       </c>
       <c r="AU126" s="3" t="n">
-        <v>46229.89583333334</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" t="n">
-        <v>0</v>
-      </c>
-      <c r="W127" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU127" s="3" t="n">
         <v>46229.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6.68</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.73</v>
+        <v>2.23</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P46" t="n">
-        <v>1.8</v>
+        <v>2.57</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.77</v>
+        <v>3.73</v>
       </c>
       <c r="O53" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>3.69</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8879,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -12290,22 +12290,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,22 +13085,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,22 +13244,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14039,22 +14039,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14357,22 +14357,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="O94" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P94" t="n">
-        <v>3.54</v>
+        <v>4.27</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17738,13 +17738,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2.73</v>
+        <v>1.71</v>
       </c>
       <c r="O109" t="n">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="P109" t="n">
-        <v>2.72</v>
+        <v>5.14</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -17777,10 +17777,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -17936,10 +17936,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="O112" t="n">
-        <v>3.83</v>
+        <v>4.27</v>
       </c>
       <c r="P112" t="n">
-        <v>5.14</v>
+        <v>6.59</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G123" t="n">

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>4.73</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>3.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="P38" t="n">
-        <v>7.55</v>
+        <v>5.39</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.77</v>
+        <v>3.54</v>
       </c>
       <c r="O45" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P45" t="n">
-        <v>3.69</v>
+        <v>1.84</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.23</v>
+        <v>3.73</v>
       </c>
       <c r="O46" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>3.54</v>
+        <v>2.23</v>
       </c>
       <c r="O52" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P52" t="n">
-        <v>1.84</v>
+        <v>2.57</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,22 +12449,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,64 +16625,64 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -16695,10 +16695,10 @@
         </is>
       </c>
       <c r="AJ102" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK102" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL102" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,64 +16784,64 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -16854,10 +16854,10 @@
         </is>
       </c>
       <c r="AJ103" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK103" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL103" t="n">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17738,13 +17738,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -17777,10 +17777,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>2.73</v>
+        <v>1.71</v>
       </c>
       <c r="O111" t="n">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="P111" t="n">
-        <v>2.72</v>
+        <v>5.14</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18572,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18851,13 +18851,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="O117" t="n">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="P117" t="n">
-        <v>3.29</v>
+        <v>6.17</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O118" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="P118" t="n">
-        <v>6.17</v>
+        <v>3.29</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19604,7 +19604,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.73</v>
+        <v>5.81</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P25" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="O38" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
-        <v>5.39</v>
+        <v>7.55</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="O41" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="P41" t="n">
-        <v>6.68</v>
+        <v>4.22</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="O42" t="n">
-        <v>3.96</v>
+        <v>5.15</v>
       </c>
       <c r="P42" t="n">
-        <v>3.76</v>
+        <v>9.1</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8402,10 +8402,10 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="O52" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P52" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9197,10 +9197,10 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12449,22 +12449,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,22 +13085,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,22 +13244,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13403,22 +13403,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17738,13 +17738,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -17936,10 +17936,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18572,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18851,13 +18851,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O117" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="P117" t="n">
-        <v>6.17</v>
+        <v>3.29</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="O118" t="n">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="P118" t="n">
-        <v>3.29</v>
+        <v>6.17</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="O21" t="n">
-        <v>3.83</v>
+        <v>4.8</v>
       </c>
       <c r="P21" t="n">
-        <v>3.38</v>
+        <v>6.24</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.73</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P22" t="n">
-        <v>1.62</v>
+        <v>3.59</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.43</v>
+        <v>4.73</v>
       </c>
       <c r="O23" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>6.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>5.81</v>
+        <v>2.04</v>
       </c>
       <c r="O25" t="n">
-        <v>4.45</v>
+        <v>3.83</v>
       </c>
       <c r="P25" t="n">
-        <v>1.49</v>
+        <v>3.38</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="O40" t="n">
-        <v>4.8</v>
+        <v>3.96</v>
       </c>
       <c r="P40" t="n">
-        <v>6.68</v>
+        <v>3.76</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="O41" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="P41" t="n">
-        <v>4.22</v>
+        <v>6.68</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O43" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="P43" t="n">
-        <v>3.76</v>
+        <v>4.22</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="O44" t="n">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="P44" t="n">
-        <v>3.93</v>
+        <v>3.69</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.78</v>
+        <v>1.86</v>
       </c>
       <c r="O48" t="n">
-        <v>3.69</v>
+        <v>3.91</v>
       </c>
       <c r="P48" t="n">
-        <v>2.41</v>
+        <v>3.93</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.77</v>
+        <v>2.78</v>
       </c>
       <c r="O49" t="n">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="P49" t="n">
-        <v>3.69</v>
+        <v>2.41</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.73</v>
+        <v>7.07</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>5.17</v>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8879,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>7.07</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9197,10 +9197,10 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>3.74</v>
+        <v>1.65</v>
       </c>
       <c r="O63" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="P63" t="n">
-        <v>1.88</v>
+        <v>5.4</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -12290,22 +12290,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,22 +13085,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,22 +13244,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13403,22 +13403,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13967,10 +13967,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -14039,22 +14039,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14357,22 +14357,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,64 +16625,64 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -16695,10 +16695,10 @@
         </is>
       </c>
       <c r="AJ102" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK102" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL102" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,64 +16784,64 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -16854,10 +16854,10 @@
         </is>
       </c>
       <c r="AJ103" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK103" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL103" t="n">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="O110" t="n">
-        <v>3.83</v>
+        <v>4.27</v>
       </c>
       <c r="P110" t="n">
-        <v>5.14</v>
+        <v>6.59</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="O117" t="n">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="P117" t="n">
-        <v>3.29</v>
+        <v>6.17</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O118" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="P118" t="n">
-        <v>6.17</v>
+        <v>3.29</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19604,7 +19604,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="O22" t="n">
-        <v>4.05</v>
+        <v>3.83</v>
       </c>
       <c r="P22" t="n">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.73</v>
+        <v>1.85</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P23" t="n">
-        <v>1.62</v>
+        <v>3.59</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>5.81</v>
+        <v>1.43</v>
       </c>
       <c r="O24" t="n">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="P24" t="n">
-        <v>1.49</v>
+        <v>6.24</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.04</v>
+        <v>4.73</v>
       </c>
       <c r="O25" t="n">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>3.38</v>
+        <v>1.62</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="O36" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="P36" t="n">
-        <v>7.55</v>
+        <v>5.39</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O40" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="P40" t="n">
-        <v>3.76</v>
+        <v>4.22</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="O41" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="P41" t="n">
-        <v>6.68</v>
+        <v>9.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="O42" t="n">
-        <v>5.15</v>
+        <v>3.96</v>
       </c>
       <c r="P42" t="n">
-        <v>9.1</v>
+        <v>3.76</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="O43" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="P43" t="n">
-        <v>4.22</v>
+        <v>6.68</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.23</v>
+        <v>7.07</v>
       </c>
       <c r="O46" t="n">
-        <v>4.15</v>
+        <v>5.17</v>
       </c>
       <c r="P46" t="n">
-        <v>2.57</v>
+        <v>1.4</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="O50" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8402,10 +8402,10 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.65</v>
+        <v>3.54</v>
       </c>
       <c r="O51" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P51" t="n">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8561,10 +8561,10 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>7.07</v>
+        <v>2.65</v>
       </c>
       <c r="O53" t="n">
-        <v>5.17</v>
+        <v>3.85</v>
       </c>
       <c r="P53" t="n">
-        <v>1.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8879,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>3.52</v>
+        <v>1.71</v>
       </c>
       <c r="O58" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="P58" t="n">
-        <v>2.05</v>
+        <v>4.53</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,22 +13244,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13403,22 +13403,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -14039,22 +14039,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14198,22 +14198,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17738,13 +17738,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O117" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="P117" t="n">
-        <v>6.17</v>
+        <v>3.29</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="O118" t="n">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="P118" t="n">
-        <v>3.29</v>
+        <v>6.17</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19604,7 +19604,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12926,22 +12926,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13403,22 +13403,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,64 +16625,64 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -16695,10 +16695,10 @@
         </is>
       </c>
       <c r="AJ102" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK102" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL102" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,64 +16784,64 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -16854,10 +16854,10 @@
         </is>
       </c>
       <c r="AJ103" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK103" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL103" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="O110" t="n">
-        <v>4.27</v>
+        <v>3.83</v>
       </c>
       <c r="P110" t="n">
-        <v>6.59</v>
+        <v>5.14</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="O111" t="n">
-        <v>3.83</v>
+        <v>4.27</v>
       </c>
       <c r="P111" t="n">
-        <v>5.14</v>
+        <v>6.59</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5.81</v>
+        <v>1.85</v>
       </c>
       <c r="O20" t="n">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="P20" t="n">
-        <v>1.49</v>
+        <v>3.59</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.85</v>
+        <v>4.73</v>
       </c>
       <c r="O23" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>3.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.43</v>
+        <v>5.81</v>
       </c>
       <c r="O24" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="P24" t="n">
-        <v>6.24</v>
+        <v>1.49</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="O40" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="P40" t="n">
-        <v>4.22</v>
+        <v>6.68</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="O41" t="n">
-        <v>5.15</v>
+        <v>3.9</v>
       </c>
       <c r="P41" t="n">
-        <v>9.1</v>
+        <v>4.22</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="O43" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="P43" t="n">
-        <v>6.68</v>
+        <v>9.1</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>7.07</v>
       </c>
       <c r="O45" t="n">
-        <v>3.69</v>
+        <v>5.17</v>
       </c>
       <c r="P45" t="n">
-        <v>2.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>7.07</v>
+        <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>5.17</v>
+        <v>3.91</v>
       </c>
       <c r="P46" t="n">
-        <v>1.4</v>
+        <v>3.93</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.86</v>
+        <v>2.78</v>
       </c>
       <c r="O48" t="n">
-        <v>3.91</v>
+        <v>3.69</v>
       </c>
       <c r="P48" t="n">
-        <v>3.93</v>
+        <v>2.41</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3.54</v>
+        <v>2.65</v>
       </c>
       <c r="O51" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="P51" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8561,10 +8561,10 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.65</v>
+        <v>3.54</v>
       </c>
       <c r="O52" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P52" t="n">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -12290,22 +12290,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,22 +12449,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12926,22 +12926,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,22 +13244,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13649,10 +13649,10 @@
         <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="O85" t="n">
-        <v>5.55</v>
+        <v>3.42</v>
       </c>
       <c r="P85" t="n">
-        <v>7.4</v>
+        <v>4.78</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13967,10 +13967,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -14198,22 +14198,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14357,22 +14357,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,64 +16625,64 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -16695,10 +16695,10 @@
         </is>
       </c>
       <c r="AJ102" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK102" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL102" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,64 +16784,64 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -16854,10 +16854,10 @@
         </is>
       </c>
       <c r="AJ103" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK103" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL103" t="n">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -17936,10 +17936,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O18" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P19" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.85</v>
+        <v>4.73</v>
       </c>
       <c r="O20" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="O21" t="n">
-        <v>4.8</v>
+        <v>3.83</v>
       </c>
       <c r="P21" t="n">
-        <v>6.24</v>
+        <v>3.38</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.73</v>
+        <v>5.81</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P23" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>5.81</v>
+        <v>1.43</v>
       </c>
       <c r="O24" t="n">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="P24" t="n">
-        <v>1.49</v>
+        <v>6.24</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="O35" t="n">
-        <v>3.42</v>
+        <v>5</v>
       </c>
       <c r="P35" t="n">
-        <v>4.58</v>
+        <v>7.55</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="P39" t="n">
-        <v>7.55</v>
+        <v>5.39</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="O40" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="P40" t="n">
-        <v>6.68</v>
+        <v>4.22</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="O41" t="n">
-        <v>3.9</v>
+        <v>5.15</v>
       </c>
       <c r="P41" t="n">
-        <v>4.22</v>
+        <v>9.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="O42" t="n">
-        <v>3.96</v>
+        <v>4.8</v>
       </c>
       <c r="P42" t="n">
-        <v>3.76</v>
+        <v>6.68</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="O43" t="n">
-        <v>5.15</v>
+        <v>3.96</v>
       </c>
       <c r="P43" t="n">
-        <v>9.1</v>
+        <v>3.76</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>7.07</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.78</v>
+        <v>7.07</v>
       </c>
       <c r="O48" t="n">
-        <v>3.69</v>
+        <v>5.17</v>
       </c>
       <c r="P48" t="n">
-        <v>2.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="O49" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="P49" t="n">
-        <v>3.69</v>
+        <v>3.93</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.65</v>
+        <v>3.54</v>
       </c>
       <c r="O51" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P51" t="n">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8561,10 +8561,10 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="O52" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="O54" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="P54" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>3.74</v>
+        <v>1.65</v>
       </c>
       <c r="O63" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="P63" t="n">
-        <v>1.88</v>
+        <v>5.4</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,22 +12290,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,22 +12449,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -13085,22 +13085,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,22 +13244,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14198,22 +14198,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14357,22 +14357,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -17936,10 +17936,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18374,13 +18374,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18731,10 +18731,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="O117" t="n">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="P117" t="n">
-        <v>3.29</v>
+        <v>6.17</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O118" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="P118" t="n">
-        <v>6.17</v>
+        <v>3.29</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19604,7 +19604,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20441,13 +20441,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -20480,10 +20480,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU126"/>
+  <dimension ref="A1:AU130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P18" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O19" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.73</v>
+        <v>1.43</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P20" t="n">
-        <v>1.62</v>
+        <v>6.24</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.04</v>
+        <v>4.73</v>
       </c>
       <c r="O21" t="n">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
-        <v>3.38</v>
+        <v>1.62</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>5.81</v>
+        <v>1.85</v>
       </c>
       <c r="O23" t="n">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="P23" t="n">
-        <v>1.49</v>
+        <v>3.59</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="O24" t="n">
-        <v>4.8</v>
+        <v>3.83</v>
       </c>
       <c r="P24" t="n">
-        <v>6.24</v>
+        <v>3.38</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="O35" t="n">
-        <v>5</v>
+        <v>3.42</v>
       </c>
       <c r="P35" t="n">
-        <v>7.55</v>
+        <v>4.58</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="O40" t="n">
-        <v>3.9</v>
+        <v>5.15</v>
       </c>
       <c r="P40" t="n">
-        <v>4.22</v>
+        <v>9.1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="O41" t="n">
-        <v>5.15</v>
+        <v>3.96</v>
       </c>
       <c r="P41" t="n">
-        <v>9.1</v>
+        <v>3.76</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O43" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="P43" t="n">
-        <v>3.76</v>
+        <v>4.22</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.23</v>
+        <v>2.78</v>
       </c>
       <c r="O47" t="n">
-        <v>4.15</v>
+        <v>3.69</v>
       </c>
       <c r="P47" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>7.07</v>
+        <v>1.86</v>
       </c>
       <c r="O48" t="n">
-        <v>5.17</v>
+        <v>3.91</v>
       </c>
       <c r="P48" t="n">
-        <v>1.4</v>
+        <v>3.93</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.86</v>
+        <v>3.54</v>
       </c>
       <c r="O49" t="n">
-        <v>3.91</v>
+        <v>4.05</v>
       </c>
       <c r="P49" t="n">
-        <v>3.93</v>
+        <v>1.84</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.65</v>
+        <v>3.73</v>
       </c>
       <c r="O50" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3.54</v>
+        <v>2.23</v>
       </c>
       <c r="O51" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P51" t="n">
-        <v>1.84</v>
+        <v>2.57</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8561,10 +8561,10 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="O54" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="P54" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11967,27 +11967,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12117,7 +12117,7 @@
         <v>0</v>
       </c>
       <c r="AU73" s="3" t="n">
-        <v>46229.59375</v>
+        <v>46229.58333333334</v>
       </c>
     </row>
     <row r="74">
@@ -12126,27 +12126,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.65</v>
+        <v>6.5</v>
       </c>
       <c r="O74" t="n">
-        <v>3.2</v>
+        <v>4.76</v>
       </c>
       <c r="P74" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>46229.60416666666</v>
+        <v>46229.59375</v>
       </c>
     </row>
     <row r="75">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12435,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>46229.625</v>
+        <v>46229.60416666666</v>
       </c>
     </row>
     <row r="76">
@@ -12449,22 +12449,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13557,27 +13557,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13649,10 +13649,10 @@
         <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46229.63541666666</v>
+        <v>46229.625</v>
       </c>
     </row>
     <row r="84">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="O84" t="n">
-        <v>3.42</v>
+        <v>5.55</v>
       </c>
       <c r="P84" t="n">
-        <v>4.78</v>
+        <v>7.4</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13808,10 +13808,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14034,27 +14034,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46229.64583333334</v>
+        <v>46229.63541666666</v>
       </c>
     </row>
     <row r="87">
@@ -14198,22 +14198,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14357,22 +14357,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14511,27 +14511,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>46229.66666666666</v>
+        <v>46229.64583333334</v>
       </c>
     </row>
     <row r="90">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14820,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>46229.66666666666</v>
+        <v>46229.64583333334</v>
       </c>
     </row>
     <row r="91">
@@ -14829,27 +14829,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>46229.66666666666</v>
+        <v>46229.64583333334</v>
       </c>
     </row>
     <row r="92">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,22 +16265,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16578,12 +16578,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,64 +16625,64 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -16695,10 +16695,10 @@
         </is>
       </c>
       <c r="AJ102" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK102" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL102" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="AU102" s="3" t="n">
-        <v>46229.67708333334</v>
+        <v>46229.66666666666</v>
       </c>
     </row>
     <row r="103">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16887,7 +16887,7 @@
         <v>0</v>
       </c>
       <c r="AU103" s="3" t="n">
-        <v>46229.67708333334</v>
+        <v>46229.66666666666</v>
       </c>
     </row>
     <row r="104">
@@ -16896,12 +16896,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17046,7 +17046,7 @@
         <v>0</v>
       </c>
       <c r="AU104" s="3" t="n">
-        <v>46229.6875</v>
+        <v>46229.66666666666</v>
       </c>
     </row>
     <row r="105">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17205,7 +17205,7 @@
         <v>0</v>
       </c>
       <c r="AU105" s="3" t="n">
-        <v>46229.75</v>
+        <v>46229.66666666666</v>
       </c>
     </row>
     <row r="106">
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17364,7 +17364,7 @@
         <v>0</v>
       </c>
       <c r="AU106" s="3" t="n">
-        <v>46229.75</v>
+        <v>46229.67708333334</v>
       </c>
     </row>
     <row r="107">
@@ -17373,12 +17373,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,64 +17420,64 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1.59</v>
+        <v>2.28</v>
       </c>
       <c r="O107" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P107" t="n">
-        <v>4.83</v>
+        <v>2.43</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17490,10 +17490,10 @@
         </is>
       </c>
       <c r="AJ107" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK107" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL107" t="n">
         <v>0</v>
@@ -17523,7 +17523,7 @@
         <v>0</v>
       </c>
       <c r="AU107" s="3" t="n">
-        <v>46229.75</v>
+        <v>46229.67708333334</v>
       </c>
     </row>
     <row r="108">
@@ -17532,12 +17532,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17682,7 +17682,7 @@
         <v>0</v>
       </c>
       <c r="AU108" s="3" t="n">
-        <v>46229.76041666666</v>
+        <v>46229.6875</v>
       </c>
     </row>
     <row r="109">
@@ -17691,12 +17691,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17841,7 +17841,7 @@
         <v>0</v>
       </c>
       <c r="AU109" s="3" t="n">
-        <v>46229.77083333334</v>
+        <v>46229.75</v>
       </c>
     </row>
     <row r="110">
@@ -17850,12 +17850,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -17936,10 +17936,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -18000,7 +18000,7 @@
         <v>0</v>
       </c>
       <c r="AU110" s="3" t="n">
-        <v>46229.77083333334</v>
+        <v>46229.75</v>
       </c>
     </row>
     <row r="111">
@@ -18009,12 +18009,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -18159,7 +18159,7 @@
         <v>0</v>
       </c>
       <c r="AU111" s="3" t="n">
-        <v>46229.77083333334</v>
+        <v>46229.75</v>
       </c>
     </row>
     <row r="112">
@@ -18168,12 +18168,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18318,7 +18318,7 @@
         <v>0</v>
       </c>
       <c r="AU112" s="3" t="n">
-        <v>46229.77083333334</v>
+        <v>46229.76041666666</v>
       </c>
     </row>
     <row r="113">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18374,13 +18374,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1.71</v>
+        <v>2.73</v>
       </c>
       <c r="O115" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="P115" t="n">
-        <v>5.14</v>
+        <v>2.72</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18731,10 +18731,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18851,13 +18851,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -18890,10 +18890,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -18963,7 +18963,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="O117" t="n">
-        <v>3.89</v>
+        <v>4.27</v>
       </c>
       <c r="P117" t="n">
-        <v>6.17</v>
+        <v>6.59</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="AU117" s="3" t="n">
-        <v>46229.8125</v>
+        <v>46229.77083333334</v>
       </c>
     </row>
     <row r="118">
@@ -19122,12 +19122,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19272,7 +19272,7 @@
         <v>0</v>
       </c>
       <c r="AU118" s="3" t="n">
-        <v>46229.8125</v>
+        <v>46229.77083333334</v>
       </c>
     </row>
     <row r="119">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19431,7 +19431,7 @@
         <v>0</v>
       </c>
       <c r="AU119" s="3" t="n">
-        <v>46229.83333333334</v>
+        <v>46229.77083333334</v>
       </c>
     </row>
     <row r="120">
@@ -19440,12 +19440,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19590,7 +19590,7 @@
         <v>0</v>
       </c>
       <c r="AU120" s="3" t="n">
-        <v>46229.85416666666</v>
+        <v>46229.77083333334</v>
       </c>
     </row>
     <row r="121">
@@ -19599,12 +19599,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19646,13 +19646,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -19749,7 +19749,7 @@
         <v>0</v>
       </c>
       <c r="AU121" s="3" t="n">
-        <v>46229.85416666666</v>
+        <v>46229.8125</v>
       </c>
     </row>
     <row r="122">
@@ -19758,12 +19758,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19805,13 +19805,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -19908,7 +19908,7 @@
         <v>0</v>
       </c>
       <c r="AU122" s="3" t="n">
-        <v>46229.875</v>
+        <v>46229.8125</v>
       </c>
     </row>
     <row r="123">
@@ -19917,12 +19917,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20067,7 +20067,7 @@
         <v>0</v>
       </c>
       <c r="AU123" s="3" t="n">
-        <v>46229.875</v>
+        <v>46229.83333333334</v>
       </c>
     </row>
     <row r="124">
@@ -20076,12 +20076,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20226,7 +20226,7 @@
         <v>0</v>
       </c>
       <c r="AU124" s="3" t="n">
-        <v>46229.875</v>
+        <v>46229.85416666666</v>
       </c>
     </row>
     <row r="125">
@@ -20235,12 +20235,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20282,64 +20282,64 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U125" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X125" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20352,10 +20352,10 @@
         </is>
       </c>
       <c r="AJ125" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AK125" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL125" t="n">
         <v>0</v>
@@ -20385,7 +20385,7 @@
         <v>0</v>
       </c>
       <c r="AU125" s="3" t="n">
-        <v>46229.89583333334</v>
+        <v>46229.85416666666</v>
       </c>
     </row>
     <row r="126">
@@ -20394,156 +20394,792 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Lokomotiv</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Sogdiana</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" s="3" t="n">
+        <v>46229.875</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AGMK</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Mash'al</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" s="3" t="n">
+        <v>46229.875</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Andijan</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Buxoro</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" s="3" t="n">
+        <v>46229.875</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O129" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R129" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T129" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U129" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V129" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W129" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X129" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ129" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" s="3" t="n">
+        <v>46229.89583333334</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Racing Louisville</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N126" t="n">
+      <c r="N130" t="n">
         <v>1.56</v>
       </c>
-      <c r="O126" t="n">
+      <c r="O130" t="n">
         <v>3.8</v>
       </c>
-      <c r="P126" t="n">
+      <c r="P130" t="n">
         <v>5.07</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="n">
         <v>1.77</v>
       </c>
-      <c r="AB126" t="n">
+      <c r="AB130" t="n">
         <v>1.89</v>
       </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU126" s="3" t="n">
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" s="3" t="n">
         <v>46229.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="O51" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P51" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="O54" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="P54" t="n">
-        <v>2.26</v>
+        <v>2.57</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O18" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P19" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.43</v>
+        <v>2.44</v>
       </c>
       <c r="O20" t="n">
-        <v>4.8</v>
+        <v>3.01</v>
       </c>
       <c r="P20" t="n">
-        <v>6.24</v>
+        <v>3.11</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.73</v>
+        <v>1.43</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P21" t="n">
-        <v>1.62</v>
+        <v>6.24</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5.81</v>
+        <v>2.04</v>
       </c>
       <c r="O22" t="n">
-        <v>4.45</v>
+        <v>3.83</v>
       </c>
       <c r="P22" t="n">
-        <v>1.49</v>
+        <v>3.38</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.85</v>
+        <v>5.81</v>
       </c>
       <c r="O23" t="n">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="P23" t="n">
-        <v>3.59</v>
+        <v>1.49</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.04</v>
+        <v>4.73</v>
       </c>
       <c r="O24" t="n">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>3.38</v>
+        <v>1.62</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="O35" t="n">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="P35" t="n">
-        <v>4.58</v>
+        <v>8.4</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="O40" t="n">
-        <v>5.15</v>
+        <v>3.9</v>
       </c>
       <c r="P40" t="n">
-        <v>9.1</v>
+        <v>4.22</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="O41" t="n">
-        <v>3.96</v>
+        <v>5.15</v>
       </c>
       <c r="P41" t="n">
-        <v>3.76</v>
+        <v>9.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="O42" t="n">
-        <v>4.8</v>
+        <v>3.96</v>
       </c>
       <c r="P42" t="n">
-        <v>6.68</v>
+        <v>3.76</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="O43" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="P43" t="n">
-        <v>4.22</v>
+        <v>6.68</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.77</v>
+        <v>2.78</v>
       </c>
       <c r="O44" t="n">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="P44" t="n">
-        <v>3.69</v>
+        <v>2.41</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>7.07</v>
       </c>
       <c r="O45" t="n">
-        <v>3.35</v>
+        <v>5.17</v>
       </c>
       <c r="P45" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>7.07</v>
+        <v>2.72</v>
       </c>
       <c r="O46" t="n">
-        <v>5.17</v>
+        <v>2.92</v>
       </c>
       <c r="P46" t="n">
-        <v>1.4</v>
+        <v>2.82</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="O47" t="n">
-        <v>3.69</v>
+        <v>3.85</v>
       </c>
       <c r="P47" t="n">
-        <v>2.41</v>
+        <v>2.26</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
-        <v>3.91</v>
+        <v>3.35</v>
       </c>
       <c r="P48" t="n">
-        <v>3.93</v>
+        <v>2.3</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.54</v>
+        <v>1.86</v>
       </c>
       <c r="O49" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="P49" t="n">
-        <v>1.84</v>
+        <v>3.93</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>3.73</v>
+        <v>3.54</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P50" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8402,10 +8402,10 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.65</v>
+        <v>3.73</v>
       </c>
       <c r="O51" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12449,22 +12449,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,22 +13085,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,22 +13244,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,22 +13562,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="O84" t="n">
-        <v>5.55</v>
+        <v>3.42</v>
       </c>
       <c r="P84" t="n">
-        <v>7.4</v>
+        <v>4.78</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13808,10 +13808,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="O85" t="n">
-        <v>3.42</v>
+        <v>5.55</v>
       </c>
       <c r="P85" t="n">
-        <v>4.78</v>
+        <v>7.4</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13967,10 +13967,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -14198,22 +14198,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14834,22 +14834,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O95" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P95" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15545,16 +15545,16 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ106" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK106" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,64 +17420,64 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17490,10 +17490,10 @@
         </is>
       </c>
       <c r="AJ107" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK107" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL107" t="n">
         <v>0</v>
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -17936,10 +17936,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="O115" t="n">
-        <v>3.25</v>
+        <v>4.27</v>
       </c>
       <c r="P115" t="n">
-        <v>2.72</v>
+        <v>6.59</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18731,10 +18731,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1.52</v>
+        <v>2.73</v>
       </c>
       <c r="O117" t="n">
-        <v>4.27</v>
+        <v>3.25</v>
       </c>
       <c r="P117" t="n">
-        <v>6.59</v>
+        <v>2.72</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19445,7 +19445,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="Q106">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12730,10 +12730,10 @@
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12893,10 +12893,10 @@
         <v>0</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA77">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC109">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU130"/>
+  <dimension ref="A1:AU132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-07-26 12:00:00</t>
+          <t>2026-07-26 11:30:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="O45">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
-        <v>4.48</v>
+        <v>2.96</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="O47">
-        <v>3.91</v>
+        <v>3.26</v>
       </c>
       <c r="P47">
-        <v>3.93</v>
+        <v>4.48</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="O48">
-        <v>3.69</v>
+        <v>3.35</v>
       </c>
       <c r="P48">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>7.07</v>
+        <v>1.86</v>
       </c>
       <c r="O49">
-        <v>5.17</v>
+        <v>3.91</v>
       </c>
       <c r="P49">
-        <v>1.4</v>
+        <v>3.93</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8341,10 +8341,10 @@
         <v>0</v>
       </c>
       <c r="AC49">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE49">
         <v>0</v>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.77</v>
+        <v>2.78</v>
       </c>
       <c r="O50">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="P50">
-        <v>3.69</v>
+        <v>2.41</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8504,10 +8504,10 @@
         <v>0</v>
       </c>
       <c r="AC50">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE50">
         <v>0</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.54</v>
+        <v>7.07</v>
       </c>
       <c r="O51">
-        <v>4.05</v>
+        <v>5.17</v>
       </c>
       <c r="P51">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AD51">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.73</v>
+        <v>1.77</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P52">
-        <v>1.8</v>
+        <v>3.69</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8830,10 +8830,10 @@
         <v>0</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.65</v>
+        <v>3.54</v>
       </c>
       <c r="O53">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P53">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8993,10 +8993,10 @@
         <v>0</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.23</v>
+        <v>3.73</v>
       </c>
       <c r="O54">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P54">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="O55">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="P55">
-        <v>2.82</v>
+        <v>2.26</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-07-26 12:30:00</t>
+          <t>2026-07-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.71</v>
+        <v>2.72</v>
       </c>
       <c r="O57">
-        <v>3.74</v>
+        <v>2.92</v>
       </c>
       <c r="P57">
-        <v>4.53</v>
+        <v>2.82</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-07-26 12:30:00</t>
+          <t>2026-07-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.52</v>
+        <v>1.71</v>
       </c>
       <c r="O59">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="P59">
-        <v>2.05</v>
+        <v>4.53</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G60">
@@ -10205,27 +10205,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-07-26 12:45:00</t>
+          <t>2026-07-26 12:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-07-26 13:00:00</t>
+          <t>2026-07-26 12:45:00</t>
         </is>
       </c>
     </row>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G63">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.74</v>
+        <v>1.71</v>
       </c>
       <c r="O66">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P66">
-        <v>1.88</v>
+        <v>4.03</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB66">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.65</v>
+        <v>3.74</v>
       </c>
       <c r="O67">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="P67">
-        <v>5.4</v>
+        <v>1.88</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -11346,27 +11346,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-07-26 13:30:00</t>
+          <t>2026-07-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-07-26 14:00:00</t>
+          <t>2026-07-26 13:30:00</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12324,27 +12324,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>6.5</v>
+        <v>2.55</v>
       </c>
       <c r="O74">
-        <v>4.76</v>
+        <v>3.2</v>
       </c>
       <c r="P74">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-07-26 14:15:00</t>
+          <t>2026-07-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -12487,27 +12487,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.65</v>
+        <v>6.5</v>
       </c>
       <c r="O75">
-        <v>3.2</v>
+        <v>4.76</v>
       </c>
       <c r="P75">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-07-26 14:30:00</t>
+          <t>2026-07-26 14:15:00</t>
         </is>
       </c>
     </row>
@@ -12650,27 +12650,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="O76">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12730,16 +12730,16 @@
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z76">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-07-26 15:00:00</t>
+          <t>2026-07-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -12813,27 +12813,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.1</v>
+        <v>4.19</v>
       </c>
       <c r="O77">
-        <v>2.73</v>
+        <v>3.35</v>
       </c>
       <c r="P77">
-        <v>3.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="Z77">
-        <v>2.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-07-26 15:00:00</t>
+          <t>2026-07-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13056,10 +13056,10 @@
         <v>0</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13219,10 +13219,10 @@
         <v>0</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13382,10 +13382,10 @@
         <v>0</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA80">
         <v>0</v>
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13545,10 +13545,10 @@
         <v>0</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA81">
         <v>0</v>
@@ -13633,22 +13633,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G82">
@@ -13796,22 +13796,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G83">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.24</v>
+        <v>3.38</v>
       </c>
       <c r="O84">
-        <v>5.55</v>
+        <v>3.64</v>
       </c>
       <c r="P84">
-        <v>7.4</v>
+        <v>1.89</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-07-26 15:15:00</t>
+          <t>2026-07-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14117,27 +14117,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-07-26 15:15:00</t>
+          <t>2026-07-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="O86">
-        <v>3.42</v>
+        <v>5.55</v>
       </c>
       <c r="P86">
-        <v>4.78</v>
+        <v>7.4</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14372,10 +14372,10 @@
         <v>0</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE86">
         <v>0</v>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-07-26 15:30:00</t>
+          <t>2026-07-26 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-07-26 15:30:00</t>
+          <t>2026-07-26 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-07-26 15:30:00</t>
+          <t>2026-07-26 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-07-26 15:30:00</t>
+          <t>2026-07-26 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-07-26 16:00:00</t>
+          <t>2026-07-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P93">
-        <v>3.54</v>
+        <v>6.45</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15507,10 +15507,10 @@
         <v>0</v>
       </c>
       <c r="AA93">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB93">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC93">
         <v>0</v>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-07-26 16:00:00</t>
+          <t>2026-07-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15664,10 +15664,10 @@
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-07-26 16:00:00</t>
+          <t>2026-07-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16805,10 +16805,10 @@
         <v>0</v>
       </c>
       <c r="Y101">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z101">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="O102">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="P102">
-        <v>5.69</v>
+        <v>5.31</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16968,16 +16968,16 @@
         <v>0</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA102">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB102">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17131,10 +17131,10 @@
         <v>0</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA103">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17294,10 +17294,10 @@
         <v>0</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA104">
         <v>0</v>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-07-26 16:15:00</t>
+          <t>2026-07-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S107">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T107">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U107">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V107">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W107">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y107">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z107">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA107">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB107">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC107">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD107">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE107">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF107">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG107">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK107">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-07-26 16:15:00</t>
+          <t>2026-07-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-07-26 16:30:00</t>
+          <t>2026-07-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="O109">
-        <v>3.05</v>
+        <v>5.05</v>
       </c>
       <c r="P109">
-        <v>4.19</v>
+        <v>5.13</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB109">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-07-26 18:00:00</t>
+          <t>2026-07-26 16:15:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-07-26 18:00:00</t>
+          <t>2026-07-26 16:15:00</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="O111">
-        <v>3.78</v>
+        <v>3.24</v>
       </c>
       <c r="P111">
-        <v>4.83</v>
+        <v>5.1</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18435,16 +18435,16 @@
         <v>0</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA111">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB111">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-07-26 18:00:00</t>
+          <t>2026-07-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-07-26 18:15:00</t>
+          <t>2026-07-26 17:45:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-07-26 18:30:00</t>
+          <t>2026-07-26 18:00:00</t>
         </is>
       </c>
     </row>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O114">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P114">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB114">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-07-26 18:30:00</t>
+          <t>2026-07-26 18:00:00</t>
         </is>
       </c>
     </row>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.73</v>
+        <v>1.59</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="P115">
-        <v>2.72</v>
+        <v>4.83</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-07-26 18:30:00</t>
+          <t>2026-07-26 18:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB116">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-07-26 18:30:00</t>
+          <t>2026-07-26 18:15:00</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC120">
         <v>0</v>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O121">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="P121">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-07-26 19:30:00</t>
+          <t>2026-07-26 18:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O122">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P122">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-07-26 19:30:00</t>
+          <t>2026-07-26 18:30:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O123">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P123">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-07-26 20:00:00</t>
+          <t>2026-07-26 18:30:00</t>
         </is>
       </c>
     </row>
@@ -20474,12 +20474,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-07-26 20:30:00</t>
+          <t>2026-07-26 18:30:00</t>
         </is>
       </c>
     </row>
@@ -20637,12 +20637,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-07-26 20:30:00</t>
+          <t>2026-07-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-07-26 21:00:00</t>
+          <t>2026-07-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -20963,12 +20963,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-07-26 21:00:00</t>
+          <t>2026-07-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G128">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-07-26 21:00:00</t>
+          <t>2026-07-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O129">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P129">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q129">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R129">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S129">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T129">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U129">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V129">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W129">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X129">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y129">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z129">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA129">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB129">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC129">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD129">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE129">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF129">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG129">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AK129">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-07-26 21:30:00</t>
+          <t>2026-07-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -21452,156 +21452,482 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N130">
+        <v>2.6</v>
+      </c>
+      <c r="O130">
+        <v>3.1</v>
+      </c>
+      <c r="P130">
+        <v>2.65</v>
+      </c>
+      <c r="Q130">
+        <v>0</v>
+      </c>
+      <c r="R130">
+        <v>0</v>
+      </c>
+      <c r="S130">
+        <v>0</v>
+      </c>
+      <c r="T130">
+        <v>0</v>
+      </c>
+      <c r="U130">
+        <v>0</v>
+      </c>
+      <c r="V130">
+        <v>0</v>
+      </c>
+      <c r="W130">
+        <v>0</v>
+      </c>
+      <c r="X130">
+        <v>0</v>
+      </c>
+      <c r="Y130">
+        <v>0</v>
+      </c>
+      <c r="Z130">
+        <v>0</v>
+      </c>
+      <c r="AA130">
+        <v>0</v>
+      </c>
+      <c r="AB130">
+        <v>0</v>
+      </c>
+      <c r="AC130">
+        <v>0</v>
+      </c>
+      <c r="AD130">
+        <v>0</v>
+      </c>
+      <c r="AE130">
+        <v>0</v>
+      </c>
+      <c r="AF130">
+        <v>0</v>
+      </c>
+      <c r="AG130">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ130">
+        <v>0</v>
+      </c>
+      <c r="AK130">
+        <v>0</v>
+      </c>
+      <c r="AL130">
+        <v>0</v>
+      </c>
+      <c r="AM130">
+        <v>-1</v>
+      </c>
+      <c r="AN130">
+        <v>-1</v>
+      </c>
+      <c r="AO130">
+        <v>-1</v>
+      </c>
+      <c r="AP130">
+        <v>-1</v>
+      </c>
+      <c r="AQ130">
+        <v>0</v>
+      </c>
+      <c r="AR130">
+        <v>0</v>
+      </c>
+      <c r="AS130">
+        <v>0</v>
+      </c>
+      <c r="AT130">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N131">
+        <v>3.06</v>
+      </c>
+      <c r="O131">
+        <v>3.1</v>
+      </c>
+      <c r="P131">
+        <v>2.32</v>
+      </c>
+      <c r="Q131">
+        <v>4.2</v>
+      </c>
+      <c r="R131">
+        <v>2.2</v>
+      </c>
+      <c r="S131">
+        <v>1.35</v>
+      </c>
+      <c r="T131">
+        <v>3.16</v>
+      </c>
+      <c r="U131">
+        <v>2.77</v>
+      </c>
+      <c r="V131">
+        <v>1.44</v>
+      </c>
+      <c r="W131">
+        <v>1.09</v>
+      </c>
+      <c r="X131">
+        <v>1.04</v>
+      </c>
+      <c r="Y131">
+        <v>1.3</v>
+      </c>
+      <c r="Z131">
+        <v>3.3</v>
+      </c>
+      <c r="AA131">
+        <v>1.95</v>
+      </c>
+      <c r="AB131">
+        <v>1.85</v>
+      </c>
+      <c r="AC131">
+        <v>3.3</v>
+      </c>
+      <c r="AD131">
+        <v>1.3</v>
+      </c>
+      <c r="AE131">
+        <v>1.1</v>
+      </c>
+      <c r="AF131">
+        <v>1.8</v>
+      </c>
+      <c r="AG131">
+        <v>1.91</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ131">
+        <v>1.91</v>
+      </c>
+      <c r="AK131">
+        <v>1.22</v>
+      </c>
+      <c r="AL131">
+        <v>0</v>
+      </c>
+      <c r="AM131">
+        <v>-1</v>
+      </c>
+      <c r="AN131">
+        <v>-1</v>
+      </c>
+      <c r="AO131">
+        <v>-1</v>
+      </c>
+      <c r="AP131">
+        <v>-1</v>
+      </c>
+      <c r="AQ131">
+        <v>0</v>
+      </c>
+      <c r="AR131">
+        <v>0</v>
+      </c>
+      <c r="AS131">
+        <v>0</v>
+      </c>
+      <c r="AT131">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Racing Louisville</t>
         </is>
       </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr">
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N130">
+      <c r="N132">
         <v>1.56</v>
       </c>
-      <c r="O130">
+      <c r="O132">
         <v>3.8</v>
       </c>
-      <c r="P130">
+      <c r="P132">
         <v>5.07</v>
       </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
-      <c r="U130">
-        <v>0</v>
-      </c>
-      <c r="V130">
-        <v>0</v>
-      </c>
-      <c r="W130">
-        <v>0</v>
-      </c>
-      <c r="X130">
-        <v>0</v>
-      </c>
-      <c r="Y130">
-        <v>0</v>
-      </c>
-      <c r="Z130">
-        <v>0</v>
-      </c>
-      <c r="AA130">
+      <c r="Q132">
+        <v>0</v>
+      </c>
+      <c r="R132">
+        <v>0</v>
+      </c>
+      <c r="S132">
+        <v>0</v>
+      </c>
+      <c r="T132">
+        <v>0</v>
+      </c>
+      <c r="U132">
+        <v>0</v>
+      </c>
+      <c r="V132">
+        <v>0</v>
+      </c>
+      <c r="W132">
+        <v>0</v>
+      </c>
+      <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132">
+        <v>0</v>
+      </c>
+      <c r="Z132">
+        <v>0</v>
+      </c>
+      <c r="AA132">
         <v>1.77</v>
       </c>
-      <c r="AB130">
+      <c r="AB132">
         <v>1.89</v>
       </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
-      <c r="AD130">
-        <v>0</v>
-      </c>
-      <c r="AE130">
-        <v>0</v>
-      </c>
-      <c r="AF130">
-        <v>0</v>
-      </c>
-      <c r="AG130">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-      <c r="AK130">
-        <v>0</v>
-      </c>
-      <c r="AL130">
-        <v>0</v>
-      </c>
-      <c r="AM130">
-        <v>-1</v>
-      </c>
-      <c r="AN130">
-        <v>-1</v>
-      </c>
-      <c r="AO130">
-        <v>-1</v>
-      </c>
-      <c r="AP130">
-        <v>-1</v>
-      </c>
-      <c r="AQ130">
-        <v>0</v>
-      </c>
-      <c r="AR130">
-        <v>0</v>
-      </c>
-      <c r="AS130">
-        <v>0</v>
-      </c>
-      <c r="AT130">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
+      <c r="AC132">
+        <v>0</v>
+      </c>
+      <c r="AD132">
+        <v>0</v>
+      </c>
+      <c r="AE132">
+        <v>0</v>
+      </c>
+      <c r="AF132">
+        <v>0</v>
+      </c>
+      <c r="AG132">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
+        <v>0</v>
+      </c>
+      <c r="AK132">
+        <v>0</v>
+      </c>
+      <c r="AL132">
+        <v>0</v>
+      </c>
+      <c r="AM132">
+        <v>-1</v>
+      </c>
+      <c r="AN132">
+        <v>-1</v>
+      </c>
+      <c r="AO132">
+        <v>-1</v>
+      </c>
+      <c r="AP132">
+        <v>-1</v>
+      </c>
+      <c r="AQ132">
+        <v>0</v>
+      </c>
+      <c r="AR132">
+        <v>0</v>
+      </c>
+      <c r="AS132">
+        <v>0</v>
+      </c>
+      <c r="AT132">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
         <is>
           <t>2026-07-26 22:00:00</t>
         </is>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU132"/>
+  <dimension ref="A1:AU134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>5.81</v>
+        <v>2.14</v>
       </c>
       <c r="O22">
-        <v>4.45</v>
+        <v>3.23</v>
       </c>
       <c r="P22">
-        <v>1.49</v>
+        <v>3.69</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.43</v>
+        <v>5.81</v>
       </c>
       <c r="O23">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="P23">
-        <v>6.24</v>
+        <v>1.49</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4179,22 +4179,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.73</v>
+        <v>1.43</v>
       </c>
       <c r="O24">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P24">
-        <v>1.62</v>
+        <v>6.24</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4266,10 +4266,10 @@
         <v>0</v>
       </c>
       <c r="AC24">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE24">
         <v>0</v>
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.44</v>
+        <v>4.73</v>
       </c>
       <c r="O25">
-        <v>3.01</v>
+        <v>4.2</v>
       </c>
       <c r="P25">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4429,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE25">
         <v>0</v>
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="O26">
-        <v>3.34</v>
+        <v>3.01</v>
       </c>
       <c r="P26">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-07-26 09:30:00</t>
+          <t>2026-07-26 09:00:00</t>
         </is>
       </c>
     </row>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="O27">
-        <v>4.35</v>
+        <v>3.34</v>
       </c>
       <c r="P27">
-        <v>4.76</v>
+        <v>3.28</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4831,22 +4831,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-07-26 09:45:00</t>
+          <t>2026-07-26 09:30:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>5.78</v>
+        <v>1.6</v>
       </c>
       <c r="O30">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>1.64</v>
+        <v>4.95</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-07-26 10:00:00</t>
+          <t>2026-07-26 09:45:00</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="O33">
-        <v>3.11</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>4.32</v>
+        <v>3.7</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>5.59</v>
+        <v>1.96</v>
       </c>
       <c r="O34">
-        <v>4.15</v>
+        <v>3.11</v>
       </c>
       <c r="P34">
-        <v>1.47</v>
+        <v>4.32</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-07-26 10:45:00</t>
+          <t>2026-07-26 10:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.86</v>
+        <v>5.59</v>
       </c>
       <c r="O35">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="P35">
-        <v>4.58</v>
+        <v>1.47</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-07-26 11:00:00</t>
+          <t>2026-07-26 10:45:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="O36">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>5.39</v>
+        <v>4.58</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="P37">
-        <v>7.55</v>
+        <v>5.39</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6385,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.57</v>
+        <v>1.36</v>
       </c>
       <c r="O38">
-        <v>3.02</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>2.92</v>
+        <v>7.55</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.45</v>
+        <v>2.57</v>
       </c>
       <c r="O39">
-        <v>3.92</v>
+        <v>3.02</v>
       </c>
       <c r="P39">
-        <v>8.4</v>
+        <v>2.92</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="O40">
-        <v>4.8</v>
+        <v>3.92</v>
       </c>
       <c r="P40">
-        <v>6.68</v>
+        <v>8.4</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6874,10 +6874,10 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-07-26 11:30:00</t>
+          <t>2026-07-26 11:00:00</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="O41">
-        <v>3.96</v>
+        <v>4.8</v>
       </c>
       <c r="P41">
-        <v>3.76</v>
+        <v>6.68</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7037,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD41">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O42">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="P42">
-        <v>4.22</v>
+        <v>3.76</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7200,10 +7200,10 @@
         <v>0</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.52</v>
+        <v>1.75</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P44">
-        <v>2.05</v>
+        <v>4.22</v>
       </c>
       <c r="Q44">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.14</v>
+        <v>3.52</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-07-26 12:00:00</t>
+          <t>2026-07-26 11:30:00</t>
         </is>
       </c>
     </row>
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.88</v>
+        <v>1.93</v>
       </c>
       <c r="O48">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="P48">
-        <v>2.3</v>
+        <v>4.48</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="O50">
-        <v>3.69</v>
+        <v>3.35</v>
       </c>
       <c r="P50">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>7.07</v>
+        <v>1.86</v>
       </c>
       <c r="O51">
-        <v>5.17</v>
+        <v>3.91</v>
       </c>
       <c r="P51">
-        <v>1.4</v>
+        <v>3.93</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.77</v>
+        <v>2.78</v>
       </c>
       <c r="O52">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="P52">
-        <v>3.69</v>
+        <v>2.41</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8830,10 +8830,10 @@
         <v>0</v>
       </c>
       <c r="AC52">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.54</v>
+        <v>7.07</v>
       </c>
       <c r="O53">
-        <v>4.05</v>
+        <v>5.17</v>
       </c>
       <c r="P53">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8993,10 +8993,10 @@
         <v>0</v>
       </c>
       <c r="AC53">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AD53">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.73</v>
+        <v>1.77</v>
       </c>
       <c r="O54">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P54">
-        <v>1.8</v>
+        <v>3.69</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9156,10 +9156,10 @@
         <v>0</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.65</v>
+        <v>3.54</v>
       </c>
       <c r="O55">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P55">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.23</v>
+        <v>3.73</v>
       </c>
       <c r="O56">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="O57">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="P57">
-        <v>2.82</v>
+        <v>2.26</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-07-26 12:30:00</t>
+          <t>2026-07-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.71</v>
+        <v>2.72</v>
       </c>
       <c r="O59">
-        <v>3.74</v>
+        <v>2.92</v>
       </c>
       <c r="P59">
-        <v>4.53</v>
+        <v>2.82</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-07-26 12:30:00</t>
+          <t>2026-07-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="O61">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="P61">
-        <v>3.85</v>
+        <v>4.53</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10291,10 +10291,10 @@
         <v>0</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC61">
         <v>0</v>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-07-26 12:45:00</t>
+          <t>2026-07-26 12:30:00</t>
         </is>
       </c>
     </row>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-07-26 13:00:00</t>
+          <t>2026-07-26 12:30:00</t>
         </is>
       </c>
     </row>
@@ -10694,27 +10694,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-07-26 13:00:00</t>
+          <t>2026-07-26 12:45:00</t>
         </is>
       </c>
     </row>
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB65">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.74</v>
+        <v>2.04</v>
       </c>
       <c r="O67">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="P67">
-        <v>1.88</v>
+        <v>3.19</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AB67">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -11351,22 +11351,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="O68">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="P68">
-        <v>5.4</v>
+        <v>4.03</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11509,27 +11509,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-07-26 13:30:00</t>
+          <t>2026-07-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -11672,27 +11672,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-07-26 13:30:00</t>
+          <t>2026-07-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -11840,22 +11840,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11998,27 +11998,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G72">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-07-26 14:00:00</t>
+          <t>2026-07-26 13:30:00</t>
         </is>
       </c>
     </row>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.06</v>
+        <v>4.08</v>
       </c>
       <c r="O73">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P73">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-07-26 14:00:00</t>
+          <t>2026-07-26 13:30:00</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12487,27 +12487,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-07-26 14:15:00</t>
+          <t>2026-07-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.65</v>
+        <v>3.06</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P76">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-07-26 14:30:00</t>
+          <t>2026-07-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>4.19</v>
+        <v>2.55</v>
       </c>
       <c r="O77">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q77">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S77">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T77">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U77">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V77">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y77">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z77">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA77">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB77">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AC77">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD77">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK77">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-07-26 14:30:00</t>
+          <t>2026-07-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.17</v>
+        <v>6.5</v>
       </c>
       <c r="O78">
-        <v>2.68</v>
+        <v>4.76</v>
       </c>
       <c r="P78">
-        <v>3.77</v>
+        <v>1.46</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13056,10 +13056,10 @@
         <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z78">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA78">
         <v>0</v>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-07-26 15:00:00</t>
+          <t>2026-07-26 14:15:00</t>
         </is>
       </c>
     </row>
@@ -13139,27 +13139,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="O79">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13219,16 +13219,16 @@
         <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z79">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-07-26 15:00:00</t>
+          <t>2026-07-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -13302,27 +13302,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.18</v>
+        <v>4.19</v>
       </c>
       <c r="O80">
-        <v>2.73</v>
+        <v>3.35</v>
       </c>
       <c r="P80">
-        <v>3.64</v>
+        <v>1.87</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y80">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Z80">
-        <v>2.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-07-26 15:00:00</t>
+          <t>2026-07-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="O81">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="P81">
-        <v>3.33</v>
+        <v>3.89</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13545,10 +13545,10 @@
         <v>0</v>
       </c>
       <c r="Y81">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Z81">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13708,10 +13708,10 @@
         <v>0</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA82">
         <v>0</v>
@@ -13796,22 +13796,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13871,10 +13871,10 @@
         <v>0</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA83">
         <v>0</v>
@@ -13959,22 +13959,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.24</v>
+        <v>3.38</v>
       </c>
       <c r="O86">
-        <v>5.55</v>
+        <v>3.64</v>
       </c>
       <c r="P86">
-        <v>7.4</v>
+        <v>1.89</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14372,10 +14372,10 @@
         <v>0</v>
       </c>
       <c r="AC86">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD86">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE86">
         <v>0</v>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-07-26 15:15:00</t>
+          <t>2026-07-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14443,27 +14443,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="O87">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="P87">
-        <v>2.78</v>
+        <v>6.66</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-07-26 15:15:00</t>
+          <t>2026-07-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14698,10 +14698,10 @@
         <v>0</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE88">
         <v>0</v>
@@ -14774,22 +14774,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="O89">
         <v>3.3</v>
       </c>
       <c r="P89">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15095,27 +15095,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-07-26 15:30:00</t>
+          <t>2026-07-26 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-07-26 15:30:00</t>
+          <t>2026-07-26 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15426,22 +15426,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15664,10 +15664,10 @@
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z94">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA94">
         <v>0</v>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="O95">
-        <v>3.62</v>
+        <v>3.34</v>
       </c>
       <c r="P95">
-        <v>4.27</v>
+        <v>6.45</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB95">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-07-26 16:00:00</t>
+          <t>2026-07-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O96">
         <v>3.4</v>
       </c>
       <c r="P96">
-        <v>3.54</v>
+        <v>6.24</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15990,16 +15990,16 @@
         <v>0</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA96">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB96">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-07-26 16:00:00</t>
+          <t>2026-07-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>5.31</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16968,10 +16968,10 @@
         <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z102">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA102">
         <v>0</v>
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17131,10 +17131,10 @@
         <v>0</v>
       </c>
       <c r="Y103">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z103">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="O104">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="P104">
-        <v>3.3</v>
+        <v>5.31</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17294,10 +17294,10 @@
         <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z104">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="O105">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="P105">
-        <v>5.69</v>
+        <v>3.3</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17457,16 +17457,16 @@
         <v>0</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA105">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB105">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17946,10 +17946,10 @@
         <v>0</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA108">
         <v>0</v>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-07-26 16:15:00</t>
+          <t>2026-07-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P110">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S110">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T110">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U110">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V110">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W110">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z110">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA110">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB110">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC110">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD110">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE110">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF110">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG110">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK110">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-07-26 16:15:00</t>
+          <t>2026-07-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="O111">
-        <v>3.24</v>
+        <v>5.05</v>
       </c>
       <c r="P111">
-        <v>5.1</v>
+        <v>5.13</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="Y111">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z111">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-07-26 16:30:00</t>
+          <t>2026-07-26 16:15:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="O112">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P112">
-        <v>1.88</v>
+        <v>2.43</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-07-26 17:45:00</t>
+          <t>2026-07-26 16:15:00</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="O113">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P113">
-        <v>4.19</v>
+        <v>5.1</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18761,16 +18761,16 @@
         <v>0</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA113">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB113">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-07-26 18:00:00</t>
+          <t>2026-07-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-07-26 18:00:00</t>
+          <t>2026-07-26 17:45:00</t>
         </is>
       </c>
     </row>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="O115">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="P115">
-        <v>4.83</v>
+        <v>4.19</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="AB115">
-        <v>1.92</v>
+        <v>1.51</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-07-26 18:15:00</t>
+          <t>2026-07-26 18:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>0</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-07-26 18:30:00</t>
+          <t>2026-07-26 18:00:00</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O118">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P118">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB118">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-07-26 18:30:00</t>
+          <t>2026-07-26 18:15:00</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="O120">
-        <v>4.27</v>
+        <v>3.83</v>
       </c>
       <c r="P120">
-        <v>6.59</v>
+        <v>5.14</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20234,10 +20234,10 @@
         <v>0</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC122">
         <v>0</v>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G124">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O125">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="P125">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-07-26 19:30:00</t>
+          <t>2026-07-26 18:30:00</t>
         </is>
       </c>
     </row>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-07-26 19:30:00</t>
+          <t>2026-07-26 18:30:00</t>
         </is>
       </c>
     </row>
@@ -20963,12 +20963,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O127">
-        <v>3.84</v>
+        <v>3.89</v>
       </c>
       <c r="P127">
-        <v>4.72</v>
+        <v>6.17</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-07-26 20:00:00</t>
+          <t>2026-07-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-07-26 20:30:00</t>
+          <t>2026-07-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-07-26 20:30:00</t>
+          <t>2026-07-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -21452,12 +21452,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-07-26 21:15:00</t>
+          <t>2026-07-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O131">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P131">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S131">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T131">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U131">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V131">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W131">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X131">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y131">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z131">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA131">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB131">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC131">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD131">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE131">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF131">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG131">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AK131">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-07-26 21:30:00</t>
+          <t>2026-07-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -21778,156 +21778,482 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N132">
+        <v>2.6</v>
+      </c>
+      <c r="O132">
+        <v>3.1</v>
+      </c>
+      <c r="P132">
+        <v>2.65</v>
+      </c>
+      <c r="Q132">
+        <v>0</v>
+      </c>
+      <c r="R132">
+        <v>0</v>
+      </c>
+      <c r="S132">
+        <v>0</v>
+      </c>
+      <c r="T132">
+        <v>0</v>
+      </c>
+      <c r="U132">
+        <v>0</v>
+      </c>
+      <c r="V132">
+        <v>0</v>
+      </c>
+      <c r="W132">
+        <v>0</v>
+      </c>
+      <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132">
+        <v>0</v>
+      </c>
+      <c r="Z132">
+        <v>0</v>
+      </c>
+      <c r="AA132">
+        <v>0</v>
+      </c>
+      <c r="AB132">
+        <v>0</v>
+      </c>
+      <c r="AC132">
+        <v>0</v>
+      </c>
+      <c r="AD132">
+        <v>0</v>
+      </c>
+      <c r="AE132">
+        <v>0</v>
+      </c>
+      <c r="AF132">
+        <v>0</v>
+      </c>
+      <c r="AG132">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
+        <v>0</v>
+      </c>
+      <c r="AK132">
+        <v>0</v>
+      </c>
+      <c r="AL132">
+        <v>0</v>
+      </c>
+      <c r="AM132">
+        <v>-1</v>
+      </c>
+      <c r="AN132">
+        <v>-1</v>
+      </c>
+      <c r="AO132">
+        <v>-1</v>
+      </c>
+      <c r="AP132">
+        <v>-1</v>
+      </c>
+      <c r="AQ132">
+        <v>0</v>
+      </c>
+      <c r="AR132">
+        <v>0</v>
+      </c>
+      <c r="AS132">
+        <v>0</v>
+      </c>
+      <c r="AT132">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N133">
+        <v>3.06</v>
+      </c>
+      <c r="O133">
+        <v>3.1</v>
+      </c>
+      <c r="P133">
+        <v>2.32</v>
+      </c>
+      <c r="Q133">
+        <v>4.2</v>
+      </c>
+      <c r="R133">
+        <v>2.2</v>
+      </c>
+      <c r="S133">
+        <v>1.35</v>
+      </c>
+      <c r="T133">
+        <v>3.16</v>
+      </c>
+      <c r="U133">
+        <v>2.77</v>
+      </c>
+      <c r="V133">
+        <v>1.44</v>
+      </c>
+      <c r="W133">
+        <v>1.09</v>
+      </c>
+      <c r="X133">
+        <v>1.04</v>
+      </c>
+      <c r="Y133">
+        <v>1.3</v>
+      </c>
+      <c r="Z133">
+        <v>3.3</v>
+      </c>
+      <c r="AA133">
+        <v>1.95</v>
+      </c>
+      <c r="AB133">
+        <v>1.85</v>
+      </c>
+      <c r="AC133">
+        <v>3.3</v>
+      </c>
+      <c r="AD133">
+        <v>1.3</v>
+      </c>
+      <c r="AE133">
+        <v>1.1</v>
+      </c>
+      <c r="AF133">
+        <v>1.8</v>
+      </c>
+      <c r="AG133">
+        <v>1.91</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ133">
+        <v>1.91</v>
+      </c>
+      <c r="AK133">
+        <v>1.22</v>
+      </c>
+      <c r="AL133">
+        <v>0</v>
+      </c>
+      <c r="AM133">
+        <v>-1</v>
+      </c>
+      <c r="AN133">
+        <v>-1</v>
+      </c>
+      <c r="AO133">
+        <v>-1</v>
+      </c>
+      <c r="AP133">
+        <v>-1</v>
+      </c>
+      <c r="AQ133">
+        <v>0</v>
+      </c>
+      <c r="AR133">
+        <v>0</v>
+      </c>
+      <c r="AS133">
+        <v>0</v>
+      </c>
+      <c r="AT133">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Racing Louisville</t>
         </is>
       </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr">
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N132">
+      <c r="N134">
         <v>1.56</v>
       </c>
-      <c r="O132">
+      <c r="O134">
         <v>3.8</v>
       </c>
-      <c r="P132">
+      <c r="P134">
         <v>5.07</v>
       </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
-      <c r="AA132">
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+      <c r="S134">
+        <v>0</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134">
+        <v>0</v>
+      </c>
+      <c r="V134">
+        <v>0</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>0</v>
+      </c>
+      <c r="Z134">
+        <v>0</v>
+      </c>
+      <c r="AA134">
         <v>1.77</v>
       </c>
-      <c r="AB132">
+      <c r="AB134">
         <v>1.89</v>
       </c>
-      <c r="AC132">
-        <v>0</v>
-      </c>
-      <c r="AD132">
-        <v>0</v>
-      </c>
-      <c r="AE132">
-        <v>0</v>
-      </c>
-      <c r="AF132">
-        <v>0</v>
-      </c>
-      <c r="AG132">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-      <c r="AK132">
-        <v>0</v>
-      </c>
-      <c r="AL132">
-        <v>0</v>
-      </c>
-      <c r="AM132">
-        <v>-1</v>
-      </c>
-      <c r="AN132">
-        <v>-1</v>
-      </c>
-      <c r="AO132">
-        <v>-1</v>
-      </c>
-      <c r="AP132">
-        <v>-1</v>
-      </c>
-      <c r="AQ132">
-        <v>0</v>
-      </c>
-      <c r="AR132">
-        <v>0</v>
-      </c>
-      <c r="AS132">
-        <v>0</v>
-      </c>
-      <c r="AT132">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
+      <c r="AC134">
+        <v>0</v>
+      </c>
+      <c r="AD134">
+        <v>0</v>
+      </c>
+      <c r="AE134">
+        <v>0</v>
+      </c>
+      <c r="AF134">
+        <v>0</v>
+      </c>
+      <c r="AG134">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
+        <v>0</v>
+      </c>
+      <c r="AK134">
+        <v>0</v>
+      </c>
+      <c r="AL134">
+        <v>0</v>
+      </c>
+      <c r="AM134">
+        <v>-1</v>
+      </c>
+      <c r="AN134">
+        <v>-1</v>
+      </c>
+      <c r="AO134">
+        <v>-1</v>
+      </c>
+      <c r="AP134">
+        <v>-1</v>
+      </c>
+      <c r="AQ134">
+        <v>0</v>
+      </c>
+      <c r="AR134">
+        <v>0</v>
+      </c>
+      <c r="AS134">
+        <v>0</v>
+      </c>
+      <c r="AT134">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
         <is>
           <t>2026-07-26 22:00:00</t>
         </is>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="O7">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="P8">
+        <v>2.1</v>
+      </c>
+      <c r="Q8">
+        <v>4.5</v>
+      </c>
+      <c r="R8">
+        <v>2</v>
+      </c>
+      <c r="S8">
+        <v>1.43</v>
+      </c>
+      <c r="T8">
+        <v>2.36</v>
+      </c>
+      <c r="U8">
+        <v>3.3</v>
+      </c>
+      <c r="V8">
+        <v>1.29</v>
+      </c>
+      <c r="W8">
+        <v>1.02</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>1.44</v>
+      </c>
+      <c r="Z8">
+        <v>2.57</v>
+      </c>
+      <c r="AA8">
         <v>2.25</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="O9">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>4.22</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA10">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB10">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>3.65</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>5.07</v>
+        <v>4.5</v>
       </c>
       <c r="R7">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S7">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="T7">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="U7">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z7">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="AA7">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AB7">
         <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD7">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG7">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK7">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,65 +1613,65 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>1.79</v>
       </c>
       <c r="O8">
-        <v>2.9</v>
+        <v>3.68</v>
       </c>
       <c r="P8">
-        <v>2.1</v>
+        <v>4.22</v>
       </c>
       <c r="Q8">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="R8">
+        <v>2.2</v>
+      </c>
+      <c r="S8">
+        <v>1.36</v>
+      </c>
+      <c r="T8">
+        <v>2.89</v>
+      </c>
+      <c r="U8">
+        <v>2.51</v>
+      </c>
+      <c r="V8">
+        <v>1.43</v>
+      </c>
+      <c r="W8">
+        <v>1.07</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>1.22</v>
+      </c>
+      <c r="Z8">
+        <v>3.54</v>
+      </c>
+      <c r="AA8">
+        <v>1.81</v>
+      </c>
+      <c r="AB8">
+        <v>1.97</v>
+      </c>
+      <c r="AC8">
+        <v>2.85</v>
+      </c>
+      <c r="AD8">
+        <v>1.33</v>
+      </c>
+      <c r="AE8">
+        <v>1.1</v>
+      </c>
+      <c r="AF8">
+        <v>1.73</v>
+      </c>
+      <c r="AG8">
         <v>2</v>
       </c>
-      <c r="S8">
-        <v>1.43</v>
-      </c>
-      <c r="T8">
-        <v>2.36</v>
-      </c>
-      <c r="U8">
-        <v>3.3</v>
-      </c>
-      <c r="V8">
-        <v>1.29</v>
-      </c>
-      <c r="W8">
-        <v>1.02</v>
-      </c>
-      <c r="X8">
-        <v>1.05</v>
-      </c>
-      <c r="Y8">
-        <v>1.44</v>
-      </c>
-      <c r="Z8">
-        <v>2.57</v>
-      </c>
-      <c r="AA8">
-        <v>2.25</v>
-      </c>
-      <c r="AB8">
-        <v>1.57</v>
-      </c>
-      <c r="AC8">
-        <v>4.5</v>
-      </c>
-      <c r="AD8">
-        <v>1.16</v>
-      </c>
-      <c r="AE8">
-        <v>1.02</v>
-      </c>
-      <c r="AF8">
-        <v>2</v>
-      </c>
-      <c r="AG8">
-        <v>1.7</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.79</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>4.22</v>
+        <v>1.8</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>5.07</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T10">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="U10">
-        <v>2.51</v>
+        <v>3.34</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z10">
-        <v>3.54</v>
+        <v>2.64</v>
       </c>
       <c r="AA10">
-        <v>1.81</v>
+        <v>2.33</v>
       </c>
       <c r="AB10">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK10">
-        <v>1.91</v>
+        <v>1.21</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O16">
-        <v>3.56</v>
+        <v>3.26</v>
       </c>
       <c r="P16">
-        <v>3.24</v>
+        <v>2.85</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O21">
-        <v>4.05</v>
+        <v>3.81</v>
       </c>
       <c r="P21">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC21">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AD21">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="O22">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
-        <v>3.69</v>
+        <v>3.55</v>
       </c>
       <c r="Q22">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T22">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U22">
         <v>2.99</v>
@@ -3934,16 +3934,16 @@
         <v>2.97</v>
       </c>
       <c r="AA22">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC22">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD22">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
         <v>1.04</v>
@@ -3952,7 +3952,7 @@
         <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.73</v>
+        <v>5.1</v>
       </c>
       <c r="O25">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC25">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD25">
         <v>1.57</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="O26">
-        <v>3.01</v>
+        <v>3.31</v>
       </c>
       <c r="P26">
-        <v>3.11</v>
+        <v>3.41</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>3.28</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA27">
         <v>1.74</v>
@@ -4755,19 +4755,19 @@
         <v>1.94</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P30">
-        <v>4.95</v>
+        <v>4.45</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA30">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
         <v>1.78</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>1.64</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>4.32</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>5.59</v>
+        <v>3.85</v>
       </c>
       <c r="O35">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P35">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>4.58</v>
+        <v>3.9</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="O37">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="P37">
-        <v>5.39</v>
+        <v>4.94</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O38">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P38">
-        <v>7.55</v>
+        <v>6.5</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AC38">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AD38">
         <v>1.66</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="O39">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="P39">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O40">
         <v>3.92</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O41">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="P41">
-        <v>6.68</v>
+        <v>5.4</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC41">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD41">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O42">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>3.76</v>
+        <v>3.88</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC42">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD42">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>2.96</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>4.48</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="O59">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P59">
         <v>2.82</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,34 +10261,34 @@
         <v>4.53</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA61">
         <v>1.83</v>
@@ -10297,19 +10297,19 @@
         <v>1.87</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>3.85</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11239,34 +11239,34 @@
         <v>3.19</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA67">
         <v>1.81</v>
@@ -11275,19 +11275,19 @@
         <v>1.86</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11565,34 +11565,34 @@
         <v>1.88</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA69">
         <v>1.6</v>
@@ -11601,19 +11601,19 @@
         <v>2.2</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,55 +11728,55 @@
         <v>5.4</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G72">
@@ -12217,55 +12217,55 @@
         <v>2.02</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12706,34 +12706,34 @@
         <v>2.12</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA76">
         <v>1.8</v>
@@ -12742,19 +12742,19 @@
         <v>2</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,34 +12869,34 @@
         <v>2.55</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA77">
         <v>2</v>
@@ -12905,19 +12905,19 @@
         <v>1.8</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13195,34 +13195,34 @@
         <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA79">
         <v>1.84</v>
@@ -13231,19 +13231,19 @@
         <v>1.83</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14034,10 +14034,10 @@
         <v>0</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>1.89</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14662,40 +14662,40 @@
         <v>7.4</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC88">
         <v>1.87</v>
@@ -14704,13 +14704,13 @@
         <v>1.79</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,34 +14825,34 @@
         <v>2.78</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA89">
         <v>1.84</v>
@@ -14861,19 +14861,19 @@
         <v>1.86</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>4.78</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17789,10 +17789,10 @@
         <v>0</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC107">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q126">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -1453,22 +1453,22 @@
         <v>3.3</v>
       </c>
       <c r="O7">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q7">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S7">
         <v>1.43</v>
       </c>
       <c r="T7">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="U7">
         <v>3.3</v>
@@ -1477,37 +1477,37 @@
         <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
         <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z7">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AA7">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB7">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC7">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD7">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE7">
         <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG7">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AK7">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,25 +1622,25 @@
         <v>4.22</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>2.89</v>
+        <v>3.18</v>
       </c>
       <c r="U8">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
         <v>1.02</v>
@@ -1652,25 +1652,25 @@
         <v>3.54</v>
       </c>
       <c r="AA8">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB8">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AC8">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="AD8">
         <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P9">
-        <v>4.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q9">
-        <v>2.39</v>
+        <v>5.02</v>
       </c>
       <c r="R9">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="S9">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="U9">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V9">
         <v>1.3</v>
@@ -1806,34 +1806,34 @@
         <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z9">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="AA9">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB9">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF9">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AK9">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>5.07</v>
+        <v>2.38</v>
       </c>
       <c r="R10">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S10">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U10">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
         <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
         <v>1.38</v>
       </c>
       <c r="Z10">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="AA10">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AB10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD10">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AG10">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>1.21</v>
+        <v>1.98</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>3.38</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA11">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB11">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O12">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>3.98</v>
+        <v>3.35</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
         <v>3.5</v>
@@ -2600,55 +2600,55 @@
         <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>2.03</v>
+      </c>
+      <c r="O18">
+        <v>3.92</v>
+      </c>
+      <c r="P18">
+        <v>3.34</v>
+      </c>
+      <c r="Q18">
+        <v>2.48</v>
+      </c>
+      <c r="R18">
+        <v>2.38</v>
+      </c>
+      <c r="S18">
+        <v>1.21</v>
+      </c>
+      <c r="T18">
+        <v>4</v>
+      </c>
+      <c r="U18">
+        <v>2.1</v>
+      </c>
+      <c r="V18">
+        <v>1.65</v>
+      </c>
+      <c r="W18">
+        <v>1.15</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.11</v>
+      </c>
+      <c r="Z18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA18">
+        <v>1.45</v>
+      </c>
+      <c r="AB18">
+        <v>2.82</v>
+      </c>
+      <c r="AC18">
         <v>2.04</v>
       </c>
-      <c r="O18">
-        <v>4</v>
-      </c>
-      <c r="P18">
-        <v>3.26</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G19">
@@ -3409,61 +3409,61 @@
         <v>2.03</v>
       </c>
       <c r="O19">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="P19">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>3.38</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>5.81</v>
+        <v>5.5</v>
       </c>
       <c r="O23">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="P23">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O24">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="P24">
-        <v>6.24</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O28">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>4.76</v>
+        <v>3.75</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O39">
-        <v>3.01</v>
+        <v>3.92</v>
       </c>
       <c r="P39">
-        <v>2.91</v>
+        <v>8.4</v>
       </c>
       <c r="Q39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.44</v>
+        <v>2.56</v>
       </c>
       <c r="O40">
-        <v>3.92</v>
+        <v>3.01</v>
       </c>
       <c r="P40">
-        <v>8.4</v>
+        <v>2.91</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="O43">
-        <v>5.15</v>
+        <v>4.8</v>
       </c>
       <c r="P43">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="O44">
+        <v>3.75</v>
+      </c>
+      <c r="P44">
         <v>3.9</v>
       </c>
-      <c r="P44">
-        <v>4.22</v>
-      </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8459,65 +8459,65 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="O50">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P50">
+        <v>2.25</v>
+      </c>
+      <c r="Q50">
+        <v>3.63</v>
+      </c>
+      <c r="R50">
+        <v>2.11</v>
+      </c>
+      <c r="S50">
+        <v>1.29</v>
+      </c>
+      <c r="T50">
+        <v>2.85</v>
+      </c>
+      <c r="U50">
+        <v>2.64</v>
+      </c>
+      <c r="V50">
+        <v>1.44</v>
+      </c>
+      <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>1.24</v>
+      </c>
+      <c r="Z50">
+        <v>3.5</v>
+      </c>
+      <c r="AA50">
+        <v>1.85</v>
+      </c>
+      <c r="AB50">
+        <v>1.95</v>
+      </c>
+      <c r="AC50">
+        <v>2.95</v>
+      </c>
+      <c r="AD50">
+        <v>1.38</v>
+      </c>
+      <c r="AE50">
+        <v>1.14</v>
+      </c>
+      <c r="AF50">
+        <v>1.62</v>
+      </c>
+      <c r="AG50">
         <v>2.3</v>
       </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
-        <v>0</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>3.93</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.78</v>
+        <v>5.75</v>
       </c>
       <c r="O52">
-        <v>3.69</v>
+        <v>4.6</v>
       </c>
       <c r="P52">
-        <v>2.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>7.07</v>
+        <v>2.98</v>
       </c>
       <c r="O53">
-        <v>5.17</v>
+        <v>3.76</v>
       </c>
       <c r="P53">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC53">
-        <v>1.95</v>
+        <v>2.61</v>
       </c>
       <c r="AD53">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.77</v>
+        <v>2.67</v>
       </c>
       <c r="O54">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>3.69</v>
+        <v>1.93</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC54">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AD54">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.54</v>
+        <v>2.68</v>
       </c>
       <c r="O55">
-        <v>4.05</v>
+        <v>3.47</v>
       </c>
       <c r="P55">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC55">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AD55">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.73</v>
+        <v>1.53</v>
       </c>
       <c r="O56">
         <v>4</v>
       </c>
       <c r="P56">
-        <v>1.8</v>
+        <v>3.58</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="O57">
-        <v>3.85</v>
+        <v>3.49</v>
       </c>
       <c r="P57">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="O58">
-        <v>4.15</v>
+        <v>3.49</v>
       </c>
       <c r="P58">
-        <v>2.57</v>
+        <v>1.95</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10424,34 +10424,34 @@
         <v>1.91</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA62">
         <v>1.83</v>
@@ -10460,19 +10460,19 @@
         <v>1.98</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>3.84</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>4.03</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -13032,55 +13032,55 @@
         <v>1.46</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="O81">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="P81">
-        <v>3.89</v>
+        <v>3.33</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y81">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="Z81">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="O82">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="P82">
-        <v>3.64</v>
+        <v>3.03</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y82">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Z82">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="O83">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="P83">
-        <v>3.33</v>
+        <v>3.64</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Z83">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O84">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="P84">
-        <v>3.03</v>
+        <v>3.89</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y84">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z84">
         <v>2.25</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -15966,28 +15966,28 @@
         <v>6.24</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y96">
         <v>1.47</v>
@@ -15996,25 +15996,25 @@
         <v>2.45</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16292,34 +16292,34 @@
         <v>3.54</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA98">
         <v>2.05</v>
@@ -16328,19 +16328,19 @@
         <v>1.8</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>2.1</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="O106">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="P106">
-        <v>5.69</v>
+        <v>4.7</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17620,16 +17620,16 @@
         <v>0</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA106">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB106">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17759,34 +17759,34 @@
         <v>6.12</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA107">
         <v>1.89</v>
@@ -17795,19 +17795,19 @@
         <v>1.79</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="O108">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="P108">
-        <v>4.7</v>
+        <v>5.69</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y108">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="Z108">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18411,55 +18411,55 @@
         <v>5.13</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19389,34 +19389,34 @@
         <v>4.83</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA117">
         <v>1.75</v>
@@ -19425,19 +19425,19 @@
         <v>1.92</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,43 +19869,43 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="O120">
-        <v>3.83</v>
+        <v>4.27</v>
       </c>
       <c r="P120">
-        <v>5.14</v>
+        <v>6.59</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA120">
         <v>1.93</v>
@@ -19914,19 +19914,19 @@
         <v>1.93</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>2.72</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,43 +20195,43 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="O122">
-        <v>4.27</v>
+        <v>3.83</v>
       </c>
       <c r="P122">
-        <v>6.59</v>
+        <v>5.14</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA122">
         <v>1.93</v>
@@ -20240,19 +20240,19 @@
         <v>1.93</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21019,55 +21019,55 @@
         <v>6.17</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21182,55 +21182,55 @@
         <v>3.29</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21345,55 +21345,55 @@
         <v>4.72</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21834,55 +21834,55 @@
         <v>2.65</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22160,34 +22160,34 @@
         <v>5.07</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA134">
         <v>1.77</v>
@@ -22196,19 +22196,19 @@
         <v>1.89</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL134">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1.33</v>
+      </c>
+      <c r="Z11">
+        <v>3.09</v>
+      </c>
+      <c r="AA11">
+        <v>2.02</v>
+      </c>
+      <c r="AB11">
+        <v>1.71</v>
+      </c>
+      <c r="AC11">
+        <v>3.58</v>
+      </c>
+      <c r="AD11">
+        <v>1.3</v>
+      </c>
+      <c r="AE11">
         <v>1.03</v>
       </c>
-      <c r="Y11">
-        <v>1.27</v>
-      </c>
-      <c r="Z11">
-        <v>3.61</v>
-      </c>
-      <c r="AA11">
-        <v>1.82</v>
-      </c>
-      <c r="AB11">
-        <v>1.88</v>
-      </c>
-      <c r="AC11">
-        <v>2.8</v>
-      </c>
-      <c r="AD11">
-        <v>1.34</v>
-      </c>
-      <c r="AE11">
-        <v>1.12</v>
-      </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="Q12">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
+        <v>2.88</v>
+      </c>
+      <c r="U12">
+        <v>2.62</v>
+      </c>
+      <c r="V12">
+        <v>1.4</v>
+      </c>
+      <c r="W12">
+        <v>1.06</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>1.27</v>
+      </c>
+      <c r="Z12">
+        <v>3.61</v>
+      </c>
+      <c r="AA12">
+        <v>1.82</v>
+      </c>
+      <c r="AB12">
+        <v>1.88</v>
+      </c>
+      <c r="AC12">
         <v>2.8</v>
       </c>
-      <c r="U12">
-        <v>2.55</v>
-      </c>
-      <c r="V12">
-        <v>1.38</v>
-      </c>
-      <c r="W12">
-        <v>1.02</v>
-      </c>
-      <c r="X12">
-        <v>1</v>
-      </c>
-      <c r="Y12">
-        <v>1.33</v>
-      </c>
-      <c r="Z12">
-        <v>3.09</v>
-      </c>
-      <c r="AA12">
-        <v>2.02</v>
-      </c>
-      <c r="AB12">
-        <v>1.71</v>
-      </c>
-      <c r="AC12">
-        <v>3.58</v>
-      </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G18">
@@ -3246,77 +3246,77 @@
         <v>2.03</v>
       </c>
       <c r="O18">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="P18">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="Q18">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="V18">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
         <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>8.800000000000001</v>
+        <v>4.96</v>
       </c>
       <c r="AA18">
+        <v>1.51</v>
+      </c>
+      <c r="AB18">
+        <v>2.46</v>
+      </c>
+      <c r="AC18">
+        <v>2.31</v>
+      </c>
+      <c r="AD18">
+        <v>1.53</v>
+      </c>
+      <c r="AE18">
+        <v>1.2</v>
+      </c>
+      <c r="AF18">
         <v>1.45</v>
       </c>
-      <c r="AB18">
-        <v>2.82</v>
-      </c>
-      <c r="AC18">
-        <v>2.04</v>
-      </c>
-      <c r="AD18">
+      <c r="AG18">
+        <v>2.51</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.25</v>
+      </c>
+      <c r="AK18">
         <v>1.72</v>
-      </c>
-      <c r="AE18">
-        <v>1.25</v>
-      </c>
-      <c r="AF18">
-        <v>1.4</v>
-      </c>
-      <c r="AG18">
-        <v>2.7</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.33</v>
-      </c>
-      <c r="AK18">
-        <v>1.78</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19">
@@ -3409,61 +3409,61 @@
         <v>2.03</v>
       </c>
       <c r="O19">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="P19">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="Q19">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T19">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="V19">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>4.96</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA19">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AB19">
-        <v>2.46</v>
+        <v>2.82</v>
       </c>
       <c r="AC19">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="AD19">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF19">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG19">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>5.5</v>
+        <v>1.45</v>
       </c>
       <c r="O23">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P23">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>4.53</v>
+        <v>1.99</v>
       </c>
       <c r="R23">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="U23">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V23">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>5.25</v>
+        <v>5.88</v>
       </c>
       <c r="AA23">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AB23">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AC23">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AD23">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF23">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>1.1</v>
+        <v>2.59</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.45</v>
+        <v>5.5</v>
       </c>
       <c r="O24">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="Q24">
-        <v>1.99</v>
+        <v>4.53</v>
       </c>
       <c r="R24">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="U24">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V24">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W24">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>5.88</v>
+        <v>5.25</v>
       </c>
       <c r="AA24">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AB24">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AC24">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AD24">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AE24">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG24">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>2.59</v>
+        <v>1.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.86</v>
+        <v>5.75</v>
       </c>
       <c r="O51">
-        <v>3.91</v>
+        <v>4.6</v>
       </c>
       <c r="P51">
-        <v>3.93</v>
+        <v>1.4</v>
       </c>
       <c r="Q51">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="R51">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="S51">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="U51">
-        <v>2.34</v>
+        <v>1.97</v>
       </c>
       <c r="V51">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z51">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA51">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AB51">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="AC51">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="AD51">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="AE51">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF51">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG51">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.24</v>
+        <v>2.82</v>
       </c>
       <c r="AK51">
-        <v>1.8</v>
+        <v>1.12</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>5.75</v>
+        <v>2.98</v>
       </c>
       <c r="O52">
-        <v>4.6</v>
+        <v>3.76</v>
       </c>
       <c r="P52">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q52">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="R52">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S52">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="T52">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="U52">
-        <v>1.97</v>
+        <v>2.44</v>
       </c>
       <c r="V52">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="W52">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z52">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>2.94</v>
+        <v>2.07</v>
       </c>
       <c r="AC52">
-        <v>1.91</v>
+        <v>2.61</v>
       </c>
       <c r="AD52">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="AE52">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AG52">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>2.82</v>
+        <v>1.66</v>
       </c>
       <c r="AK52">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.98</v>
+        <v>1.86</v>
       </c>
       <c r="O53">
-        <v>3.76</v>
+        <v>3.91</v>
       </c>
       <c r="P53">
-        <v>2.21</v>
+        <v>3.93</v>
       </c>
       <c r="Q53">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="R53">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S53">
         <v>1.28</v>
       </c>
       <c r="T53">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U53">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V53">
+        <v>1.53</v>
+      </c>
+      <c r="W53">
+        <v>1.11</v>
+      </c>
+      <c r="X53">
+        <v>1.01</v>
+      </c>
+      <c r="Y53">
+        <v>1.13</v>
+      </c>
+      <c r="Z53">
+        <v>4.6</v>
+      </c>
+      <c r="AA53">
+        <v>1.61</v>
+      </c>
+      <c r="AB53">
+        <v>2.34</v>
+      </c>
+      <c r="AC53">
+        <v>2.34</v>
+      </c>
+      <c r="AD53">
+        <v>1.48</v>
+      </c>
+      <c r="AE53">
+        <v>1.18</v>
+      </c>
+      <c r="AF53">
         <v>1.52</v>
       </c>
-      <c r="W53">
-        <v>1.08</v>
-      </c>
-      <c r="X53">
-        <v>1.02</v>
-      </c>
-      <c r="Y53">
-        <v>1.18</v>
-      </c>
-      <c r="Z53">
-        <v>4.2</v>
-      </c>
-      <c r="AA53">
-        <v>1.65</v>
-      </c>
-      <c r="AB53">
-        <v>2.07</v>
-      </c>
-      <c r="AC53">
-        <v>2.61</v>
-      </c>
-      <c r="AD53">
-        <v>1.39</v>
-      </c>
-      <c r="AE53">
-        <v>1.12</v>
-      </c>
-      <c r="AF53">
-        <v>1.56</v>
-      </c>
       <c r="AG53">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="P54">
         <v>1.93</v>
       </c>
       <c r="Q54">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R54">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S54">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T54">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="U54">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V54">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W54">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z54">
-        <v>5.97</v>
+        <v>5.1</v>
       </c>
       <c r="AA54">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB54">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AC54">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AD54">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AE54">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF54">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AG54">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.77</v>
       </c>
       <c r="AK54">
         <v>1.3</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.68</v>
+        <v>1.53</v>
       </c>
       <c r="O55">
-        <v>3.47</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>1.93</v>
+        <v>3.58</v>
       </c>
       <c r="Q55">
-        <v>3.75</v>
+        <v>2.13</v>
       </c>
       <c r="R55">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="S55">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T55">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U55">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="V55">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="W55">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z55">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AA55">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB55">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="AC55">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AD55">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AE55">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF55">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG55">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.77</v>
+        <v>1.19</v>
       </c>
       <c r="AK55">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.53</v>
+        <v>2.65</v>
       </c>
       <c r="O56">
-        <v>4</v>
+        <v>3.49</v>
       </c>
       <c r="P56">
-        <v>3.58</v>
+        <v>1.95</v>
       </c>
       <c r="Q56">
-        <v>2.13</v>
+        <v>3.7</v>
       </c>
       <c r="R56">
-        <v>2.73</v>
+        <v>2.35</v>
       </c>
       <c r="S56">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T56">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="U56">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="V56">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="W56">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z56">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AA56">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB56">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AC56">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AD56">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AE56">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF56">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG56">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.13</v>
+        <v>2.67</v>
       </c>
       <c r="O57">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="Q57">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="R57">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S57">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>4.8</v>
+        <v>3.82</v>
       </c>
       <c r="U57">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="V57">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="W57">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z57">
-        <v>7</v>
+        <v>5.97</v>
       </c>
       <c r="AA57">
+        <v>1.44</v>
+      </c>
+      <c r="AB57">
+        <v>2.62</v>
+      </c>
+      <c r="AC57">
+        <v>2.04</v>
+      </c>
+      <c r="AD57">
+        <v>1.74</v>
+      </c>
+      <c r="AE57">
+        <v>1.27</v>
+      </c>
+      <c r="AF57">
+        <v>1.36</v>
+      </c>
+      <c r="AG57">
+        <v>2.77</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>1.22</v>
+      </c>
+      <c r="AK57">
         <v>1.3</v>
-      </c>
-      <c r="AB57">
-        <v>3.28</v>
-      </c>
-      <c r="AC57">
-        <v>1.73</v>
-      </c>
-      <c r="AD57">
-        <v>2.07</v>
-      </c>
-      <c r="AE57">
-        <v>1.42</v>
-      </c>
-      <c r="AF57">
-        <v>1.27</v>
-      </c>
-      <c r="AG57">
-        <v>3.3</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.2</v>
-      </c>
-      <c r="AK57">
-        <v>1.62</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="O58">
         <v>3.49</v>
       </c>
       <c r="P58">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="Q58">
-        <v>3.7</v>
+        <v>2.54</v>
       </c>
       <c r="R58">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="S58">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="T58">
-        <v>3.88</v>
+        <v>4.8</v>
       </c>
       <c r="U58">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="V58">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="W58">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z58">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AA58">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB58">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="AC58">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AD58">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="AE58">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AF58">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AG58">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -13512,28 +13512,28 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P81">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="Q81">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="R81">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="S81">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T81">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="U81">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="V81">
         <v>1.2</v>
@@ -13545,13 +13545,13 @@
         <v>1.11</v>
       </c>
       <c r="Y81">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Z81">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AA81">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AB81">
         <v>1.28</v>
@@ -13566,10 +13566,10 @@
         <v>1.02</v>
       </c>
       <c r="AF81">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AG81">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK81">
         <v>1.45</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O82">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="P82">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="Q82">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R82">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="S82">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="T82">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="U82">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="V82">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W82">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X82">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y82">
+        <v>1.64</v>
+      </c>
+      <c r="Z82">
+        <v>2.22</v>
+      </c>
+      <c r="AA82">
+        <v>2.88</v>
+      </c>
+      <c r="AB82">
+        <v>1.32</v>
+      </c>
+      <c r="AC82">
+        <v>6.21</v>
+      </c>
+      <c r="AD82">
+        <v>1.06</v>
+      </c>
+      <c r="AE82">
+        <v>1.02</v>
+      </c>
+      <c r="AF82">
+        <v>2.3</v>
+      </c>
+      <c r="AG82">
+        <v>1.53</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
+        <v>1.29</v>
+      </c>
+      <c r="AK82">
         <v>1.55</v>
-      </c>
-      <c r="Z82">
-        <v>2.25</v>
-      </c>
-      <c r="AA82">
-        <v>2.66</v>
-      </c>
-      <c r="AB82">
-        <v>1.4</v>
-      </c>
-      <c r="AC82">
-        <v>5.83</v>
-      </c>
-      <c r="AD82">
-        <v>1.12</v>
-      </c>
-      <c r="AE82">
-        <v>1.03</v>
-      </c>
-      <c r="AF82">
-        <v>2.19</v>
-      </c>
-      <c r="AG82">
-        <v>1.59</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.32</v>
-      </c>
-      <c r="AK82">
-        <v>1.46</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,31 +13838,31 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="O83">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="P83">
-        <v>3.64</v>
+        <v>4.3</v>
       </c>
       <c r="Q83">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="R83">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="S83">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="T83">
         <v>2.1</v>
       </c>
       <c r="U83">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="V83">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="W83">
         <v>1.03</v>
@@ -13871,19 +13871,19 @@
         <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Z83">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AA83">
         <v>2.88</v>
       </c>
       <c r="AB83">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC83">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="AD83">
         <v>1.06</v>
@@ -13892,10 +13892,10 @@
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG83">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK83">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O84">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="P84">
-        <v>3.89</v>
+        <v>3.03</v>
       </c>
       <c r="Q84">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="R84">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="S84">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="T84">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="U84">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="V84">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W84">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X84">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y84">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Z84">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AA84">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AB84">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AC84">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="AD84">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="AG84">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK84">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G95">
@@ -15797,61 +15797,61 @@
         <v>1.55</v>
       </c>
       <c r="O95">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P95">
-        <v>6.45</v>
+        <v>6.24</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="O96">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P96">
-        <v>6.24</v>
+        <v>6.5</v>
       </c>
       <c r="Q96">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R96">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S96">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T96">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U96">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V96">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W96">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X96">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y96">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z96">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA96">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB96">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC96">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD96">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE96">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF96">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG96">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK96">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O104">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="P104">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="O105">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P105">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,65 +17587,65 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="O106">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="P106">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
+        <v>1.34</v>
+      </c>
+      <c r="Z106">
+        <v>2.78</v>
+      </c>
+      <c r="AA106">
+        <v>2.23</v>
+      </c>
+      <c r="AB106">
+        <v>1.61</v>
+      </c>
+      <c r="AC106">
+        <v>4</v>
+      </c>
+      <c r="AD106">
+        <v>1.21</v>
+      </c>
+      <c r="AE106">
+        <v>1.01</v>
+      </c>
+      <c r="AF106">
+        <v>2.2</v>
+      </c>
+      <c r="AG106">
         <v>1.62</v>
       </c>
-      <c r="Z106">
-        <v>2.15</v>
-      </c>
-      <c r="AA106">
-        <v>0</v>
-      </c>
-      <c r="AB106">
-        <v>0</v>
-      </c>
-      <c r="AC106">
-        <v>0</v>
-      </c>
-      <c r="AD106">
-        <v>0</v>
-      </c>
-      <c r="AE106">
-        <v>0</v>
-      </c>
-      <c r="AF106">
-        <v>0</v>
-      </c>
-      <c r="AG106">
-        <v>0</v>
-      </c>
       <c r="AH106" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="O107">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="P107">
-        <v>6.12</v>
+        <v>5.25</v>
       </c>
       <c r="Q107">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="R107">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="S107">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="T107">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="U107">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="V107">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W107">
         <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y107">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="Z107">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AA107">
-        <v>1.89</v>
+        <v>2.43</v>
       </c>
       <c r="AB107">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AC107">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AD107">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE107">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF107">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AG107">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK107">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="O108">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="P108">
-        <v>5.69</v>
+        <v>4</v>
       </c>
       <c r="Q108">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S108">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T108">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U108">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V108">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W108">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X108">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y108">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="Z108">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="AA108">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB108">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC108">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="AD108">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF108">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG108">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK108">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.73</v>
+        <v>1.71</v>
       </c>
       <c r="O121">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="P121">
-        <v>2.72</v>
+        <v>5.14</v>
       </c>
       <c r="Q121">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="R121">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S121">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T121">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="U121">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="V121">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W121">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X121">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y121">
         <v>1.25</v>
       </c>
       <c r="Z121">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA121">
+        <v>1.93</v>
+      </c>
+      <c r="AB121">
+        <v>1.93</v>
+      </c>
+      <c r="AC121">
+        <v>2.99</v>
+      </c>
+      <c r="AD121">
+        <v>1.3</v>
+      </c>
+      <c r="AE121">
+        <v>1.11</v>
+      </c>
+      <c r="AF121">
         <v>1.84</v>
       </c>
-      <c r="AB121">
-        <v>1.83</v>
-      </c>
-      <c r="AC121">
-        <v>3.3</v>
-      </c>
-      <c r="AD121">
-        <v>1.29</v>
-      </c>
-      <c r="AE121">
-        <v>1.08</v>
-      </c>
-      <c r="AF121">
-        <v>1.67</v>
-      </c>
       <c r="AG121">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AK121">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.71</v>
+        <v>2.73</v>
       </c>
       <c r="O122">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="P122">
-        <v>5.14</v>
+        <v>2.72</v>
       </c>
       <c r="Q122">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="R122">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T122">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="U122">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="V122">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X122">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y122">
         <v>1.25</v>
       </c>
       <c r="Z122">
+        <v>3.5</v>
+      </c>
+      <c r="AA122">
+        <v>1.84</v>
+      </c>
+      <c r="AB122">
+        <v>1.83</v>
+      </c>
+      <c r="AC122">
         <v>3.3</v>
       </c>
-      <c r="AA122">
-        <v>1.93</v>
-      </c>
-      <c r="AB122">
-        <v>1.93</v>
-      </c>
-      <c r="AC122">
-        <v>2.99</v>
-      </c>
       <c r="AD122">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE122">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AG122">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AK122">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AL122">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="Q11">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
+        <v>2.88</v>
+      </c>
+      <c r="U11">
+        <v>2.62</v>
+      </c>
+      <c r="V11">
+        <v>1.4</v>
+      </c>
+      <c r="W11">
+        <v>1.06</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.27</v>
+      </c>
+      <c r="Z11">
+        <v>3.61</v>
+      </c>
+      <c r="AA11">
+        <v>1.82</v>
+      </c>
+      <c r="AB11">
+        <v>1.88</v>
+      </c>
+      <c r="AC11">
         <v>2.8</v>
       </c>
-      <c r="U11">
-        <v>2.55</v>
-      </c>
-      <c r="V11">
-        <v>1.38</v>
-      </c>
-      <c r="W11">
-        <v>1.02</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1.33</v>
-      </c>
-      <c r="Z11">
-        <v>3.09</v>
-      </c>
-      <c r="AA11">
-        <v>2.02</v>
-      </c>
-      <c r="AB11">
-        <v>1.71</v>
-      </c>
-      <c r="AC11">
-        <v>3.58</v>
-      </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="Q12">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="R12">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1.33</v>
+      </c>
+      <c r="Z12">
+        <v>3.09</v>
+      </c>
+      <c r="AA12">
+        <v>2.02</v>
+      </c>
+      <c r="AB12">
+        <v>1.71</v>
+      </c>
+      <c r="AC12">
+        <v>3.58</v>
+      </c>
+      <c r="AD12">
+        <v>1.3</v>
+      </c>
+      <c r="AE12">
         <v>1.03</v>
       </c>
-      <c r="Y12">
-        <v>1.27</v>
-      </c>
-      <c r="Z12">
-        <v>3.61</v>
-      </c>
-      <c r="AA12">
-        <v>1.82</v>
-      </c>
-      <c r="AB12">
-        <v>1.88</v>
-      </c>
-      <c r="AC12">
-        <v>2.8</v>
-      </c>
-      <c r="AD12">
-        <v>1.34</v>
-      </c>
-      <c r="AE12">
-        <v>1.12</v>
-      </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O81">
         <v>2.62</v>
@@ -13521,7 +13521,7 @@
         <v>3.25</v>
       </c>
       <c r="Q81">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="R81">
         <v>1.68</v>
@@ -13545,10 +13545,10 @@
         <v>1.11</v>
       </c>
       <c r="Y81">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Z81">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AA81">
         <v>3.28</v>
@@ -13585,7 +13585,7 @@
         <v>1.36</v>
       </c>
       <c r="AK81">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O82">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P82">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q82">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="R82">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="S82">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="T82">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U82">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="V82">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="W82">
         <v>1.03</v>
@@ -13708,10 +13708,10 @@
         <v>1.08</v>
       </c>
       <c r="Y82">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z82">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AA82">
         <v>2.88</v>
@@ -13720,19 +13720,19 @@
         <v>1.32</v>
       </c>
       <c r="AC82">
-        <v>6.21</v>
+        <v>6.25</v>
       </c>
       <c r="AD82">
         <v>1.06</v>
       </c>
       <c r="AE82">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF82">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG82">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK82">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O83">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="P83">
-        <v>4.3</v>
+        <v>3.03</v>
       </c>
       <c r="Q83">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="R83">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="S83">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="T83">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U83">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="V83">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
         <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Z83">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AA83">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AB83">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AC83">
-        <v>6.25</v>
+        <v>5.3</v>
       </c>
       <c r="AD83">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AG83">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AK83">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="O84">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="P84">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="Q84">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R84">
         <v>1.85</v>
       </c>
       <c r="S84">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="T84">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U84">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="V84">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W84">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
         <v>1.08</v>
       </c>
       <c r="Y84">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Z84">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="AA84">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AB84">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AC84">
-        <v>5.3</v>
+        <v>6.21</v>
       </c>
       <c r="AD84">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE84">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF84">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AG84">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15815,10 +15815,10 @@
         <v>2.31</v>
       </c>
       <c r="U95">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V95">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W95">
         <v>1</v>
@@ -15867,7 +15867,7 @@
         <v>1.25</v>
       </c>
       <c r="AK95">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="O97">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="P97">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         <v>1.95</v>
       </c>
       <c r="AB97">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O98">
         <v>3.4</v>
       </c>
       <c r="P98">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -16322,10 +16322,10 @@
         <v>3.45</v>
       </c>
       <c r="AA98">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB98">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC98">
         <v>3.3</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="O104">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P104">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17294,16 +17294,16 @@
         <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z104">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.31</v>
+        <v>1.56</v>
       </c>
       <c r="O105">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="P105">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="Z105">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="AA105">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="AB105">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="O106">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="P106">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="Q106">
-        <v>2.13</v>
+        <v>2.68</v>
       </c>
       <c r="R106">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="S106">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="T106">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="U106">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="V106">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W106">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Y106">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="Z106">
-        <v>2.78</v>
+        <v>2.14</v>
       </c>
       <c r="AA106">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="AB106">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AC106">
-        <v>4</v>
+        <v>6.05</v>
       </c>
       <c r="AD106">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AE106">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF106">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AG106">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK106">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17783,10 +17783,10 @@
         <v>1.06</v>
       </c>
       <c r="Y107">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z107">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AA107">
         <v>2.43</v>
@@ -17795,7 +17795,7 @@
         <v>1.5</v>
       </c>
       <c r="AC107">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AD107">
         <v>1.12</v>
@@ -17823,7 +17823,7 @@
         <v>1.24</v>
       </c>
       <c r="AK107">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="O108">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P108">
+        <v>4.8</v>
+      </c>
+      <c r="Q108">
+        <v>2.46</v>
+      </c>
+      <c r="R108">
+        <v>1.82</v>
+      </c>
+      <c r="S108">
+        <v>1.63</v>
+      </c>
+      <c r="T108">
+        <v>2.13</v>
+      </c>
+      <c r="U108">
         <v>4</v>
       </c>
-      <c r="Q108">
-        <v>0</v>
-      </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108">
-        <v>0</v>
-      </c>
-      <c r="T108">
-        <v>0</v>
-      </c>
-      <c r="U108">
-        <v>0</v>
-      </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y108">
         <v>1.62</v>
       </c>
       <c r="Z108">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O113">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P113">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>2.45</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O115">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>4.19</v>
+        <v>3.9</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA115">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AB115">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19872,10 +19872,10 @@
         <v>1.52</v>
       </c>
       <c r="O120">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="P120">
-        <v>6.59</v>
+        <v>6.5</v>
       </c>
       <c r="Q120">
         <v>2.02</v>
@@ -19908,10 +19908,10 @@
         <v>3.38</v>
       </c>
       <c r="AA120">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB120">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC120">
         <v>3.12</v>
@@ -20047,49 +20047,49 @@
         <v>2.28</v>
       </c>
       <c r="S121">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T121">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="U121">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="V121">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W121">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X121">
         <v>1.05</v>
       </c>
       <c r="Y121">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z121">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA121">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB121">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC121">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AD121">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE121">
         <v>1.11</v>
       </c>
       <c r="AF121">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG121">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK121">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="O122">
         <v>3.25</v>
       </c>
       <c r="P122">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="Q122">
         <v>2.9</v>
@@ -20228,16 +20228,16 @@
         <v>1</v>
       </c>
       <c r="Y122">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z122">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AA122">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AB122">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC122">
         <v>3.3</v>
@@ -20246,13 +20246,13 @@
         <v>1.29</v>
       </c>
       <c r="AE122">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF122">
         <v>1.67</v>
       </c>
       <c r="AG122">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="O127">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="P127">
-        <v>6.17</v>
+        <v>5.25</v>
       </c>
       <c r="Q127">
         <v>2.1</v>
@@ -21025,49 +21025,49 @@
         <v>2.23</v>
       </c>
       <c r="S127">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T127">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U127">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="V127">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W127">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z127">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="AA127">
         <v>2.07</v>
       </c>
       <c r="AB127">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC127">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="AD127">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE127">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF127">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AG127">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>1.24</v>
       </c>
       <c r="AK127">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21209,7 +21209,7 @@
         <v>1.28</v>
       </c>
       <c r="Z128">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AA128">
         <v>2</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -970,13 +970,13 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
         <v>2.97</v>
@@ -988,7 +988,7 @@
         <v>1.47</v>
       </c>
       <c r="W4">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -997,13 +997,13 @@
         <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AA4">
         <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC4">
         <v>2.52</v>
@@ -1018,7 +1018,7 @@
         <v>1.55</v>
       </c>
       <c r="AG4">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
         <v>1.65</v>
@@ -1133,7 +1133,7 @@
         <v>3.65</v>
       </c>
       <c r="Q5">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="R5">
         <v>1.96</v>
@@ -1163,7 +1163,7 @@
         <v>2.74</v>
       </c>
       <c r="AA5">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AB5">
         <v>1.67</v>
@@ -1178,10 +1178,10 @@
         <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="O16">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="Q16">
         <v>3.12</v>
@@ -2938,7 +2938,7 @@
         <v>2.6</v>
       </c>
       <c r="U16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
         <v>1.33</v>
@@ -2962,7 +2962,7 @@
         <v>1.68</v>
       </c>
       <c r="AC16">
-        <v>3.94</v>
+        <v>4.09</v>
       </c>
       <c r="AD16">
         <v>1.21</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AK16">
         <v>1.58</v>
@@ -3732,55 +3732,55 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="P21">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R21">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="S21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T21">
         <v>3.9</v>
       </c>
       <c r="U21">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="V21">
         <v>1.72</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AA21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AC21">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AD21">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AE21">
         <v>1.26</v>
@@ -3789,7 +3789,7 @@
         <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
         <v>1.91</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O22">
         <v>3.25</v>
@@ -3910,16 +3910,16 @@
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U22">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="V22">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
         <v>1.03</v>
@@ -3928,13 +3928,13 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB22">
         <v>1.75</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O25">
         <v>4</v>
       </c>
       <c r="P25">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Q25">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="R25">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="S25">
         <v>1.22</v>
@@ -4405,16 +4405,16 @@
         <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V25">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
         <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
         <v>1.14</v>
@@ -4441,7 +4441,7 @@
         <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.16</v>
+        <v>2.38</v>
       </c>
       <c r="AK25">
         <v>1.14</v>
@@ -4562,40 +4562,40 @@
         <v>2.22</v>
       </c>
       <c r="S26">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U26">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z26">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA26">
         <v>1.81</v>
       </c>
       <c r="AB26">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AC26">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="AD26">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
         <v>1.1</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK26">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O27">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="Q27">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
         <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z27">
-        <v>4.32</v>
+        <v>4.1</v>
       </c>
       <c r="AA27">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AB27">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AC27">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
         <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK27">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="O30">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P30">
-        <v>4.45</v>
+        <v>5.35</v>
       </c>
       <c r="Q30">
         <v>2.14</v>
@@ -5220,7 +5220,7 @@
         <v>3</v>
       </c>
       <c r="U30">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V30">
         <v>1.38</v>
@@ -5232,31 +5232,31 @@
         <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z30">
         <v>3.3</v>
       </c>
       <c r="AA30">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB30">
         <v>1.78</v>
       </c>
       <c r="AC30">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD30">
         <v>1.29</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AG30">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK30">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
         <v>1.13</v>
@@ -5525,61 +5525,61 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="Q32">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R32">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="S32">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="U32">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="V32">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W32">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z32">
-        <v>5.13</v>
+        <v>5.05</v>
       </c>
       <c r="AA32">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB32">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AC32">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AD32">
         <v>1.69</v>
       </c>
       <c r="AE32">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF32">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG32">
         <v>1.63</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK32">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5869,16 +5869,16 @@
         <v>1.34</v>
       </c>
       <c r="T34">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5887,25 +5887,25 @@
         <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA34">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AB34">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
         <v>3.3</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
         <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG34">
         <v>1.75</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O35">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P35">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q35">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.32</v>
@@ -6035,7 +6035,7 @@
         <v>3.25</v>
       </c>
       <c r="U35">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V35">
         <v>1.5</v>
@@ -6044,22 +6044,22 @@
         <v>1.13</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AA35">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB35">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AC35">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AD35">
         <v>1.42</v>
@@ -6071,7 +6071,7 @@
         <v>1.61</v>
       </c>
       <c r="AG35">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="O36">
         <v>3.4</v>
       </c>
       <c r="P36">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -6219,10 +6219,10 @@
         <v>2.19</v>
       </c>
       <c r="AB36">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC36">
-        <v>3.84</v>
+        <v>3.91</v>
       </c>
       <c r="AD36">
         <v>1.18</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
         <v>1.96</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
         <v>3.85</v>
       </c>
       <c r="P37">
-        <v>4.94</v>
+        <v>4.65</v>
       </c>
       <c r="Q37">
         <v>2.06</v>
       </c>
       <c r="R37">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="S37">
         <v>1.36</v>
@@ -6361,7 +6361,7 @@
         <v>3.04</v>
       </c>
       <c r="U37">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="V37">
         <v>1.45</v>
@@ -6379,16 +6379,16 @@
         <v>3.65</v>
       </c>
       <c r="AA37">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC37">
         <v>2.95</v>
       </c>
       <c r="AD37">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE37">
         <v>1.1</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O38">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R38">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="S38">
         <v>1.22</v>
@@ -6527,13 +6527,13 @@
         <v>2.1</v>
       </c>
       <c r="V38">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W38">
         <v>1.14</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
         <v>1.1</v>
@@ -6542,25 +6542,25 @@
         <v>5.2</v>
       </c>
       <c r="AA38">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB38">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AC38">
         <v>2.18</v>
       </c>
       <c r="AD38">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE38">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF38">
         <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.15</v>
       </c>
       <c r="AK38">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,10 +6669,10 @@
         <v>1.44</v>
       </c>
       <c r="O39">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="P39">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6841,40 +6841,40 @@
         <v>3</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S40">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T40">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V40">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA40">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AB40">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD40">
         <v>1.39</v>
@@ -6883,10 +6883,10 @@
         <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AG40">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O41">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P41">
         <v>5.4</v>
       </c>
       <c r="Q41">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="R41">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="S41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="U41">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V41">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
         <v>1.13</v>
@@ -7025,25 +7025,25 @@
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA41">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB41">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AC41">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AD41">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE41">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF41">
         <v>1.62</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK41">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P42">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="Q42">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="R42">
         <v>2.5</v>
@@ -7188,22 +7188,22 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA42">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB42">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC42">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD42">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AE42">
         <v>1.28</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.52</v>
+        <v>2.8</v>
       </c>
       <c r="O45">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P45">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q45">
         <v>3.72</v>
       </c>
       <c r="R45">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S45">
         <v>1.46</v>
       </c>
       <c r="T45">
+        <v>2.5</v>
+      </c>
+      <c r="U45">
         <v>2.8</v>
       </c>
-      <c r="U45">
-        <v>2.99</v>
-      </c>
       <c r="V45">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W45">
         <v>1.07</v>
@@ -7683,25 +7683,25 @@
         <v>2.92</v>
       </c>
       <c r="AA45">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AB45">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC45">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD45">
         <v>1.23</v>
       </c>
       <c r="AE45">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG45">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK45">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>2.14</v>
       </c>
       <c r="O46">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P46">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q46">
         <v>2.68</v>
@@ -7822,19 +7822,19 @@
         <v>2.21</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U46">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,13 +7843,13 @@
         <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB46">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AC46">
         <v>2.49</v>
@@ -7864,7 +7864,7 @@
         <v>1.51</v>
       </c>
       <c r="AG46">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>4.48</v>
       </c>
       <c r="Q48">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="R48">
         <v>1.96</v>
@@ -8190,7 +8190,7 @@
         <v>1.97</v>
       </c>
       <c r="AG48">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -9935,16 +9935,16 @@
         <v>2.82</v>
       </c>
       <c r="Q59">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R59">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S59">
         <v>1.4</v>
       </c>
       <c r="T59">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U59">
         <v>2.65</v>
@@ -9962,7 +9962,7 @@
         <v>1.27</v>
       </c>
       <c r="Z59">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA59">
         <v>1.93</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AK59">
         <v>1.41</v>
@@ -10098,49 +10098,49 @@
         <v>2.9</v>
       </c>
       <c r="Q60">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R60">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S60">
         <v>1.34</v>
       </c>
       <c r="T60">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="U60">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V60">
         <v>1.43</v>
       </c>
       <c r="W60">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z60">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="AA60">
         <v>1.77</v>
       </c>
       <c r="AB60">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC60">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AD60">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE60">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
         <v>1.6</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK60">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,40 +10252,40 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="O61">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="P61">
-        <v>4.53</v>
+        <v>4.8</v>
       </c>
       <c r="Q61">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="R61">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="S61">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T61">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U61">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V61">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W61">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z61">
         <v>3.5</v>
@@ -10294,22 +10294,22 @@
         <v>1.83</v>
       </c>
       <c r="AB61">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AC61">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AD61">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE61">
         <v>1.08</v>
       </c>
       <c r="AF61">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG61">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK61">
         <v>2.1</v>
@@ -10424,7 +10424,7 @@
         <v>1.91</v>
       </c>
       <c r="Q62">
-        <v>4.13</v>
+        <v>3.96</v>
       </c>
       <c r="R62">
         <v>2.15</v>
@@ -10433,16 +10433,16 @@
         <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U62">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="V62">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W62">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.01</v>
@@ -10454,10 +10454,10 @@
         <v>3.96</v>
       </c>
       <c r="AA62">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AB62">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AC62">
         <v>2.69</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
         <v>1.22</v>
@@ -10590,16 +10590,16 @@
         <v>2.52</v>
       </c>
       <c r="R63">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S63">
         <v>1.4</v>
       </c>
       <c r="T63">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U63">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V63">
         <v>1.33</v>
@@ -10614,16 +10614,16 @@
         <v>1.3</v>
       </c>
       <c r="Z63">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="AA63">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB63">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC63">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD63">
         <v>1.23</v>
@@ -10635,7 +10635,7 @@
         <v>1.82</v>
       </c>
       <c r="AG63">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="O67">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="Q67">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="R67">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S67">
         <v>1.3</v>
@@ -11251,34 +11251,34 @@
         <v>3.02</v>
       </c>
       <c r="U67">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V67">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
         <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y67">
         <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="AA67">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AB67">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AC67">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="AD67">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE67">
         <v>1.11</v>
@@ -11303,7 +11303,7 @@
         <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O68">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P68">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="Q68">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R68">
         <v>2.35</v>
@@ -11429,13 +11429,13 @@
         <v>1.13</v>
       </c>
       <c r="Z68">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA68">
         <v>1.61</v>
       </c>
       <c r="AB68">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC68">
         <v>2.28</v>
@@ -11450,7 +11450,7 @@
         <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="O69">
+        <v>3.5</v>
+      </c>
+      <c r="P69">
+        <v>1.95</v>
+      </c>
+      <c r="Q69">
         <v>3.75</v>
       </c>
-      <c r="P69">
-        <v>1.88</v>
-      </c>
-      <c r="Q69">
-        <v>4.2</v>
-      </c>
       <c r="R69">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S69">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T69">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U69">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="V69">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W69">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
         <v>1.04</v>
       </c>
       <c r="Y69">
+        <v>1.21</v>
+      </c>
+      <c r="Z69">
+        <v>4.8</v>
+      </c>
+      <c r="AA69">
+        <v>1.67</v>
+      </c>
+      <c r="AB69">
+        <v>2.17</v>
+      </c>
+      <c r="AC69">
+        <v>2.6</v>
+      </c>
+      <c r="AD69">
+        <v>1.4</v>
+      </c>
+      <c r="AE69">
+        <v>1.13</v>
+      </c>
+      <c r="AF69">
+        <v>1.49</v>
+      </c>
+      <c r="AG69">
+        <v>2.38</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.21</v>
+      </c>
+      <c r="AK69">
         <v>1.2</v>
-      </c>
-      <c r="Z69">
-        <v>4.2</v>
-      </c>
-      <c r="AA69">
-        <v>1.6</v>
-      </c>
-      <c r="AB69">
-        <v>2.2</v>
-      </c>
-      <c r="AC69">
-        <v>2.7</v>
-      </c>
-      <c r="AD69">
-        <v>1.42</v>
-      </c>
-      <c r="AE69">
-        <v>1.17</v>
-      </c>
-      <c r="AF69">
-        <v>1.57</v>
-      </c>
-      <c r="AG69">
-        <v>2.3</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.83</v>
-      </c>
-      <c r="AK69">
-        <v>1.25</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,46 +11728,46 @@
         <v>5.4</v>
       </c>
       <c r="Q70">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="R70">
         <v>1.98</v>
       </c>
       <c r="S70">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T70">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="U70">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="V70">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W70">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X70">
         <v>1.05</v>
       </c>
       <c r="Y70">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z70">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA70">
         <v>2.17</v>
       </c>
       <c r="AB70">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC70">
         <v>3.95</v>
       </c>
       <c r="AD70">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE70">
         <v>1.02</v>
@@ -11776,7 +11776,7 @@
         <v>2</v>
       </c>
       <c r="AG70">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -12208,28 +12208,28 @@
         </is>
       </c>
       <c r="N73">
-        <v>4.08</v>
+        <v>3.05</v>
       </c>
       <c r="O73">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q73">
         <v>4.45</v>
       </c>
       <c r="R73">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="S73">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T73">
         <v>2.6</v>
       </c>
       <c r="U73">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="V73">
         <v>1.31</v>
@@ -12247,10 +12247,10 @@
         <v>2.74</v>
       </c>
       <c r="AA73">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AB73">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AC73">
         <v>4.15</v>
@@ -12281,7 +12281,7 @@
         <v>1.27</v>
       </c>
       <c r="AK73">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,25 +12380,25 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R74">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="S74">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T74">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="U74">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V74">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W74">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X74">
         <v>1</v>
@@ -12407,13 +12407,13 @@
         <v>1.06</v>
       </c>
       <c r="Z74">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="AA74">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB74">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AC74">
         <v>1.93</v>
@@ -12428,7 +12428,7 @@
         <v>1.73</v>
       </c>
       <c r="AG74">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>1.07</v>
       </c>
       <c r="AK74">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12706,19 +12706,19 @@
         <v>2.12</v>
       </c>
       <c r="Q76">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="R76">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S76">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="U76">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V76">
         <v>1.41</v>
@@ -12736,7 +12736,7 @@
         <v>3.72</v>
       </c>
       <c r="AA76">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB76">
         <v>2</v>
@@ -12754,7 +12754,7 @@
         <v>1.6</v>
       </c>
       <c r="AG76">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.24</v>
       </c>
       <c r="AK76">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>2.55</v>
       </c>
       <c r="Q77">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S77">
         <v>1.36</v>
@@ -12884,7 +12884,7 @@
         <v>2.86</v>
       </c>
       <c r="V77">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
         <v>1.07</v>
@@ -12899,10 +12899,10 @@
         <v>3.14</v>
       </c>
       <c r="AA77">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB77">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC77">
         <v>3.34</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK77">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13195,22 +13195,22 @@
         <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="R79">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S79">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T79">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U79">
         <v>2.88</v>
       </c>
       <c r="V79">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
         <v>1.05</v>
@@ -13222,25 +13222,25 @@
         <v>1.3</v>
       </c>
       <c r="Z79">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AA79">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AB79">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC79">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD79">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE79">
         <v>1.05</v>
       </c>
       <c r="AF79">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG79">
         <v>1.95</v>
@@ -13259,7 +13259,7 @@
         <v>1.29</v>
       </c>
       <c r="AK79">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,25 +13349,25 @@
         </is>
       </c>
       <c r="N80">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="O80">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="P80">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="Q80">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="R80">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S80">
         <v>1.35</v>
       </c>
       <c r="T80">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="U80">
         <v>2.75</v>
@@ -13376,19 +13376,19 @@
         <v>1.41</v>
       </c>
       <c r="W80">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X80">
         <v>1</v>
       </c>
       <c r="Y80">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z80">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA80">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB80">
         <v>1.92</v>
@@ -13397,16 +13397,16 @@
         <v>2.92</v>
       </c>
       <c r="AD80">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE80">
         <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG80">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK80">
         <v>1.15</v>
@@ -14167,19 +14167,19 @@
         <v>1.83</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="Q85">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="R85">
         <v>2.14</v>
       </c>
       <c r="S85">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T85">
         <v>2.85</v>
@@ -14194,25 +14194,25 @@
         <v>1.05</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y85">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z85">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="AA85">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB85">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC85">
         <v>3.25</v>
       </c>
       <c r="AD85">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE85">
         <v>1.08</v>
@@ -14221,7 +14221,7 @@
         <v>1.78</v>
       </c>
       <c r="AG85">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
         <v>1.85</v>
@@ -14336,10 +14336,10 @@
         <v>1.89</v>
       </c>
       <c r="Q86">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="R86">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S86">
         <v>1.22</v>
@@ -14351,7 +14351,7 @@
         <v>2.19</v>
       </c>
       <c r="V86">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W86">
         <v>1.13</v>
@@ -14363,28 +14363,28 @@
         <v>1.11</v>
       </c>
       <c r="Z86">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA86">
         <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AC86">
         <v>2.16</v>
       </c>
       <c r="AD86">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE86">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF86">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG86">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK86">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="O88">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="P88">
-        <v>7.4</v>
+        <v>5.05</v>
       </c>
       <c r="Q88">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R88">
         <v>2.72</v>
       </c>
       <c r="S88">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U88">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="V88">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W88">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z88">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AA88">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB88">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AC88">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AD88">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AE88">
         <v>1.27</v>
       </c>
       <c r="AF88">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG88">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK88">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,22 +14816,22 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P89">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="Q89">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="R89">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S89">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T89">
         <v>2.85</v>
@@ -14840,40 +14840,40 @@
         <v>2.69</v>
       </c>
       <c r="V89">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W89">
         <v>1.04</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA89">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AB89">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AC89">
         <v>2.97</v>
       </c>
       <c r="AD89">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE89">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG89">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15305,49 +15305,49 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O92">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="P92">
-        <v>4.78</v>
+        <v>4.59</v>
       </c>
       <c r="Q92">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R92">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S92">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T92">
+        <v>2.59</v>
+      </c>
+      <c r="U92">
         <v>2.69</v>
       </c>
-      <c r="U92">
-        <v>2.64</v>
-      </c>
       <c r="V92">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W92">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X92">
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z92">
         <v>3.28</v>
       </c>
       <c r="AA92">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AB92">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC92">
         <v>2.97</v>
@@ -15356,10 +15356,10 @@
         <v>1.3</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF92">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG92">
         <v>1.9</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK92">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15640,10 +15640,10 @@
         <v>2.49</v>
       </c>
       <c r="Q94">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R94">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S94">
         <v>1.36</v>
@@ -15655,10 +15655,10 @@
         <v>2.82</v>
       </c>
       <c r="V94">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W94">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
         <v>1.01</v>
@@ -15670,10 +15670,10 @@
         <v>3.2</v>
       </c>
       <c r="AA94">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB94">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC94">
         <v>3.34</v>
@@ -17107,16 +17107,16 @@
         <v>1.45</v>
       </c>
       <c r="Q103">
-        <v>5.64</v>
+        <v>8</v>
       </c>
       <c r="R103">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="S103">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T103">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U103">
         <v>2.25</v>
@@ -17125,37 +17125,37 @@
         <v>1.57</v>
       </c>
       <c r="W103">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z103">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA103">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AB103">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AC103">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="AD103">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AE103">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF103">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG103">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK103">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
+        <v>1.75</v>
+      </c>
+      <c r="O107">
+        <v>3.1</v>
+      </c>
+      <c r="P107">
+        <v>4.8</v>
+      </c>
+      <c r="Q107">
+        <v>2.46</v>
+      </c>
+      <c r="R107">
+        <v>1.82</v>
+      </c>
+      <c r="S107">
         <v>1.63</v>
       </c>
-      <c r="O107">
-        <v>3.4</v>
-      </c>
-      <c r="P107">
-        <v>5.25</v>
-      </c>
-      <c r="Q107">
-        <v>2.29</v>
-      </c>
-      <c r="R107">
-        <v>1.94</v>
-      </c>
-      <c r="S107">
-        <v>1.54</v>
-      </c>
       <c r="T107">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="U107">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="V107">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W107">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X107">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y107">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z107">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="AA107">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="AB107">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC107">
-        <v>4.75</v>
+        <v>5.95</v>
       </c>
       <c r="AD107">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE107">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF107">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AG107">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AK107">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="O108">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q108">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="R108">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="S108">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="T108">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="U108">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="V108">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W108">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y108">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z108">
-        <v>2.16</v>
+        <v>2.41</v>
       </c>
       <c r="AA108">
-        <v>2.97</v>
+        <v>2.43</v>
       </c>
       <c r="AB108">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC108">
-        <v>5.95</v>
+        <v>4.75</v>
       </c>
       <c r="AD108">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE108">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF108">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG108">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O126">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P126">
         <v>2.6</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL126">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -798,40 +798,40 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE3">
         <v>0</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q7">
-        <v>3.7</v>
+        <v>4.64</v>
       </c>
       <c r="R7">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S7">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="T7">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="U7">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
         <v>1.01</v>
@@ -1486,25 +1486,25 @@
         <v>1.4</v>
       </c>
       <c r="Z7">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AA7">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AB7">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC7">
         <v>4.3</v>
       </c>
       <c r="AD7">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
         <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG7">
         <v>1.67</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,25 +1622,25 @@
         <v>4.22</v>
       </c>
       <c r="Q8">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="R8">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="U8">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.02</v>
@@ -1652,41 +1652,41 @@
         <v>3.54</v>
       </c>
       <c r="AA8">
+        <v>1.82</v>
+      </c>
+      <c r="AB8">
+        <v>2.02</v>
+      </c>
+      <c r="AC8">
+        <v>3.02</v>
+      </c>
+      <c r="AD8">
+        <v>1.34</v>
+      </c>
+      <c r="AE8">
+        <v>1.1</v>
+      </c>
+      <c r="AF8">
+        <v>1.67</v>
+      </c>
+      <c r="AG8">
+        <v>2.05</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.25</v>
+      </c>
+      <c r="AK8">
         <v>1.83</v>
-      </c>
-      <c r="AB8">
-        <v>2.01</v>
-      </c>
-      <c r="AC8">
-        <v>3.04</v>
-      </c>
-      <c r="AD8">
-        <v>1.33</v>
-      </c>
-      <c r="AE8">
-        <v>1.14</v>
-      </c>
-      <c r="AF8">
-        <v>1.7</v>
-      </c>
-      <c r="AG8">
-        <v>1.92</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.22</v>
-      </c>
-      <c r="AK8">
-        <v>1.85</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
         <v>1.95</v>
@@ -1791,37 +1791,37 @@
         <v>1.93</v>
       </c>
       <c r="S9">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T9">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="U9">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z9">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="AA9">
         <v>2.35</v>
       </c>
       <c r="AB9">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC9">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AD9">
         <v>1.17</v>
@@ -1833,7 +1833,7 @@
         <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S10">
         <v>1.43</v>
@@ -1960,10 +1960,10 @@
         <v>2.45</v>
       </c>
       <c r="U10">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
         <v>1.03</v>
@@ -1972,10 +1972,10 @@
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z10">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA10">
         <v>2.25</v>
@@ -1993,10 +1993,10 @@
         <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AG10">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.61</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AC11">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="Q12">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U12">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.09</v>
+        <v>3.6</v>
       </c>
       <c r="AA12">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AB12">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="R13">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="S13">
         <v>1.2</v>
@@ -2455,7 +2455,7 @@
         <v>1.76</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2473,19 +2473,19 @@
         <v>2.55</v>
       </c>
       <c r="AC13">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AD13">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AE13">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG13">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
         <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>3.96</v>
+        <v>3.66</v>
       </c>
       <c r="R14">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S14">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="V14">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W14">
         <v>1.08</v>
@@ -2624,31 +2624,31 @@
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="AA14">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB14">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC14">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AD14">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="O18">
         <v>3.98</v>
       </c>
       <c r="P18">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
       </c>
       <c r="R18">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W18">
         <v>1.13</v>
@@ -3279,28 +3279,28 @@
         <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="AA18">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AB18">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AC18">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG18">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,13 +3415,13 @@
         <v>3.34</v>
       </c>
       <c r="Q19">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T19">
         <v>4</v>
@@ -3442,22 +3442,22 @@
         <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>8.800000000000001</v>
+        <v>5.35</v>
       </c>
       <c r="AA19">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="AC19">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AD19">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AE19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF19">
         <v>1.4</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
         <v>1.78</v>
@@ -3578,10 +3578,10 @@
         <v>3.38</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R20">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="S20">
         <v>1.21</v>
@@ -3590,25 +3590,25 @@
         <v>3.68</v>
       </c>
       <c r="U20">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="V20">
         <v>1.68</v>
       </c>
       <c r="W20">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA20">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB20">
         <v>2.75</v>
@@ -3617,16 +3617,16 @@
         <v>2.02</v>
       </c>
       <c r="AD20">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE20">
         <v>1.26</v>
       </c>
       <c r="AF20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG20">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O23">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="Q23">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="R23">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="S23">
         <v>1.2</v>
       </c>
       <c r="T23">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="U23">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="V23">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="W23">
         <v>1.16</v>
@@ -4091,31 +4091,31 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z23">
-        <v>5.88</v>
+        <v>5.5</v>
       </c>
       <c r="AA23">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB23">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AC23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD23">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE23">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF23">
         <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4224,28 +4224,28 @@
         <v>5.5</v>
       </c>
       <c r="O24">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P24">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Q24">
-        <v>4.53</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="S24">
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="U24">
         <v>2.14</v>
       </c>
       <c r="V24">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W24">
         <v>1.14</v>
@@ -4260,7 +4260,7 @@
         <v>5.25</v>
       </c>
       <c r="AA24">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB24">
         <v>2.63</v>
@@ -4269,10 +4269,10 @@
         <v>2.07</v>
       </c>
       <c r="AD24">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF24">
         <v>1.58</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK24">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4873,43 +4873,43 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O28">
         <v>3.8</v>
       </c>
       <c r="P28">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q28">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R28">
         <v>2.55</v>
       </c>
       <c r="S28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U28">
         <v>2.08</v>
       </c>
       <c r="V28">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="W28">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z28">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA28">
         <v>1.46</v>
@@ -4924,13 +4924,13 @@
         <v>1.69</v>
       </c>
       <c r="AE28">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AF28">
         <v>1.45</v>
       </c>
       <c r="AG28">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5688,22 +5688,22 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="O33">
         <v>3.7</v>
       </c>
       <c r="P33">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q33">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T33">
         <v>3.3</v>
@@ -5712,7 +5712,7 @@
         <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.12</v>
@@ -5721,25 +5721,25 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB33">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC33">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD33">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE33">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
         <v>1.47</v>
@@ -5761,7 +5761,7 @@
         <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7321,58 +7321,58 @@
         <v>1.3</v>
       </c>
       <c r="O43">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P43">
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R43">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="S43">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U43">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V43">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W43">
         <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB43">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AC43">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AD43">
         <v>1.46</v>
       </c>
       <c r="AE43">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG43">
         <v>1.8</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK43">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O44">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="P44">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="Q44">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="R44">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
         <v>1.28</v>
@@ -7502,43 +7502,43 @@
         <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V44">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
         <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z44">
         <v>4.15</v>
       </c>
       <c r="AA44">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB44">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC44">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE44">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AG44">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.23</v>
       </c>
       <c r="AK44">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8471,28 +8471,28 @@
         <v>3.63</v>
       </c>
       <c r="R50">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
         <v>1.29</v>
       </c>
       <c r="T50">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W50">
         <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
         <v>3.5</v>
@@ -8501,13 +8501,13 @@
         <v>1.85</v>
       </c>
       <c r="AB50">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC50">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="AD50">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
         <v>1.14</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AK50">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>5.75</v>
+        <v>1.86</v>
       </c>
       <c r="O51">
-        <v>4.6</v>
+        <v>3.91</v>
       </c>
       <c r="P51">
-        <v>1.4</v>
+        <v>3.93</v>
       </c>
       <c r="Q51">
-        <v>5.7</v>
+        <v>2.24</v>
       </c>
       <c r="R51">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S51">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="T51">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="U51">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="V51">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="W51">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>6.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA51">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AB51">
-        <v>2.94</v>
+        <v>2.31</v>
       </c>
       <c r="AC51">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AD51">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AE51">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF51">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG51">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>2.82</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O52">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
       </c>
       <c r="R52">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S52">
         <v>1.28</v>
@@ -8809,10 +8809,10 @@
         <v>2.44</v>
       </c>
       <c r="V52">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1.02</v>
@@ -8836,13 +8836,13 @@
         <v>1.39</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AG52">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.86</v>
+        <v>6.25</v>
       </c>
       <c r="O53">
-        <v>3.91</v>
+        <v>5.4</v>
       </c>
       <c r="P53">
-        <v>3.93</v>
+        <v>1.36</v>
       </c>
       <c r="Q53">
-        <v>2.38</v>
+        <v>5.2</v>
       </c>
       <c r="R53">
-        <v>2.23</v>
+        <v>2.68</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T53">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U53">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="V53">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z53">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AA53">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AB53">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="AC53">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="AD53">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="AE53">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AF53">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG53">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.24</v>
+        <v>2.63</v>
       </c>
       <c r="AK53">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="P57">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="Q57">
+        <v>2.54</v>
+      </c>
+      <c r="R57">
+        <v>2.54</v>
+      </c>
+      <c r="S57">
+        <v>1.15</v>
+      </c>
+      <c r="T57">
+        <v>4.8</v>
+      </c>
+      <c r="U57">
+        <v>1.83</v>
+      </c>
+      <c r="V57">
+        <v>1.89</v>
+      </c>
+      <c r="W57">
+        <v>1.24</v>
+      </c>
+      <c r="X57">
+        <v>1.01</v>
+      </c>
+      <c r="Y57">
+        <v>1.04</v>
+      </c>
+      <c r="Z57">
+        <v>7</v>
+      </c>
+      <c r="AA57">
+        <v>1.3</v>
+      </c>
+      <c r="AB57">
+        <v>3.28</v>
+      </c>
+      <c r="AC57">
+        <v>1.73</v>
+      </c>
+      <c r="AD57">
+        <v>2.07</v>
+      </c>
+      <c r="AE57">
+        <v>1.42</v>
+      </c>
+      <c r="AF57">
+        <v>1.27</v>
+      </c>
+      <c r="AG57">
         <v>3.3</v>
       </c>
-      <c r="R57">
-        <v>2.6</v>
-      </c>
-      <c r="S57">
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.2</v>
       </c>
-      <c r="T57">
-        <v>3.82</v>
-      </c>
-      <c r="U57">
-        <v>2.06</v>
-      </c>
-      <c r="V57">
-        <v>1.69</v>
-      </c>
-      <c r="W57">
-        <v>1.17</v>
-      </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>1.08</v>
-      </c>
-      <c r="Z57">
-        <v>5.97</v>
-      </c>
-      <c r="AA57">
-        <v>1.44</v>
-      </c>
-      <c r="AB57">
-        <v>2.62</v>
-      </c>
-      <c r="AC57">
-        <v>2.04</v>
-      </c>
-      <c r="AD57">
-        <v>1.74</v>
-      </c>
-      <c r="AE57">
-        <v>1.27</v>
-      </c>
-      <c r="AF57">
-        <v>1.36</v>
-      </c>
-      <c r="AG57">
-        <v>2.77</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.22</v>
-      </c>
       <c r="AK57">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.13</v>
+        <v>2.67</v>
       </c>
       <c r="O58">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="Q58">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="R58">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S58">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T58">
-        <v>4.8</v>
+        <v>3.82</v>
       </c>
       <c r="U58">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="V58">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="W58">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z58">
-        <v>7</v>
+        <v>5.97</v>
       </c>
       <c r="AA58">
+        <v>1.44</v>
+      </c>
+      <c r="AB58">
+        <v>2.62</v>
+      </c>
+      <c r="AC58">
+        <v>2.04</v>
+      </c>
+      <c r="AD58">
+        <v>1.74</v>
+      </c>
+      <c r="AE58">
+        <v>1.27</v>
+      </c>
+      <c r="AF58">
+        <v>1.36</v>
+      </c>
+      <c r="AG58">
+        <v>2.77</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>1.22</v>
+      </c>
+      <c r="AK58">
         <v>1.3</v>
-      </c>
-      <c r="AB58">
-        <v>3.28</v>
-      </c>
-      <c r="AC58">
-        <v>1.73</v>
-      </c>
-      <c r="AD58">
-        <v>2.07</v>
-      </c>
-      <c r="AE58">
-        <v>1.42</v>
-      </c>
-      <c r="AF58">
-        <v>1.27</v>
-      </c>
-      <c r="AG58">
-        <v>3.3</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.2</v>
-      </c>
-      <c r="AK58">
-        <v>1.62</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10472,7 +10472,7 @@
         <v>1.58</v>
       </c>
       <c r="AG62">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10741,34 +10741,34 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="Q64">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="R64">
         <v>2.12</v>
       </c>
       <c r="S64">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T64">
         <v>2.92</v>
       </c>
       <c r="U64">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V64">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W64">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X64">
         <v>1.01</v>
@@ -10777,13 +10777,13 @@
         <v>1.21</v>
       </c>
       <c r="Z64">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AA64">
         <v>1.77</v>
       </c>
       <c r="AB64">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC64">
         <v>2.83</v>
@@ -10798,7 +10798,7 @@
         <v>1.64</v>
       </c>
       <c r="AG64">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O68">
         <v>3.8</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="O78">
-        <v>4.76</v>
+        <v>4.33</v>
       </c>
       <c r="P78">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q78">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R78">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="S78">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T78">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="U78">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="V78">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W78">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X78">
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z78">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AA78">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB78">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AC78">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AD78">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AE78">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF78">
         <v>1.5</v>
       </c>
       <c r="AG78">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13512,16 +13512,16 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="O81">
         <v>2.62</v>
       </c>
       <c r="P81">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q81">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="R81">
         <v>1.68</v>
@@ -13545,16 +13545,16 @@
         <v>1.11</v>
       </c>
       <c r="Y81">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Z81">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AA81">
         <v>3.28</v>
       </c>
       <c r="AB81">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC81">
         <v>6.8</v>
@@ -13585,7 +13585,7 @@
         <v>1.36</v>
       </c>
       <c r="AK81">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13681,7 +13681,7 @@
         <v>2.8</v>
       </c>
       <c r="P82">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q82">
         <v>2.82</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O84">
         <v>2.8</v>
@@ -14022,7 +14022,7 @@
         <v>2.08</v>
       </c>
       <c r="U84">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="V84">
         <v>1.16</v>
@@ -14052,7 +14052,7 @@
         <v>1.06</v>
       </c>
       <c r="AE84">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF84">
         <v>2.3</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="O87">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="P87">
-        <v>6.66</v>
+        <v>4.6</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK95">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="O96">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P96">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16123,7 +16123,7 @@
         <v>1.8</v>
       </c>
       <c r="O97">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="P97">
         <v>4.25</v>
@@ -16292,10 +16292,10 @@
         <v>3.4</v>
       </c>
       <c r="Q98">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R98">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S98">
         <v>1.41</v>
@@ -16316,10 +16316,10 @@
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z98">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="AA98">
         <v>2.03</v>
@@ -16772,22 +16772,22 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O101">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Q101">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R101">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="S101">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T101">
         <v>2.56</v>
@@ -16796,13 +16796,13 @@
         <v>2.95</v>
       </c>
       <c r="V101">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W101">
+        <v>1.05</v>
+      </c>
+      <c r="X101">
         <v>1.06</v>
-      </c>
-      <c r="X101">
-        <v>1.02</v>
       </c>
       <c r="Y101">
         <v>1.29</v>
@@ -16811,13 +16811,13 @@
         <v>3.04</v>
       </c>
       <c r="AA101">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB101">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC101">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD101">
         <v>1.25</v>
@@ -16826,10 +16826,10 @@
         <v>1.05</v>
       </c>
       <c r="AF101">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG101">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK101">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17424,19 +17424,19 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O105">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P105">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q105">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R105">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S105">
         <v>1.43</v>
@@ -17454,22 +17454,22 @@
         <v>1.05</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z105">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA105">
         <v>2.23</v>
       </c>
       <c r="AB105">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC105">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD105">
         <v>1.21</v>
@@ -17497,7 +17497,7 @@
         <v>1.2</v>
       </c>
       <c r="AK105">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="O106">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P106">
+        <v>4.8</v>
+      </c>
+      <c r="Q106">
+        <v>2.45</v>
+      </c>
+      <c r="R106">
+        <v>1.82</v>
+      </c>
+      <c r="S106">
+        <v>1.64</v>
+      </c>
+      <c r="T106">
+        <v>2.2</v>
+      </c>
+      <c r="U106">
         <v>4</v>
       </c>
-      <c r="Q106">
-        <v>2.68</v>
-      </c>
-      <c r="R106">
-        <v>1.87</v>
-      </c>
-      <c r="S106">
-        <v>1.65</v>
-      </c>
-      <c r="T106">
-        <v>2.1</v>
-      </c>
-      <c r="U106">
-        <v>4.1</v>
-      </c>
       <c r="V106">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W106">
         <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y106">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Z106">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AA106">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AB106">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC106">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="AD106">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE106">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF106">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AG106">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AK106">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O107">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P107">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q107">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="R107">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="S107">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="T107">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="U107">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V107">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W107">
         <v>1.03</v>
       </c>
       <c r="X107">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y107">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Z107">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AA107">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AB107">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC107">
-        <v>5.95</v>
+        <v>6.05</v>
       </c>
       <c r="AD107">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF107">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AG107">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AK107">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17919,7 +17919,7 @@
         <v>3.4</v>
       </c>
       <c r="P108">
-        <v>5.25</v>
+        <v>5.85</v>
       </c>
       <c r="Q108">
         <v>2.29</v>
@@ -17946,10 +17946,10 @@
         <v>1.06</v>
       </c>
       <c r="Y108">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z108">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AA108">
         <v>2.43</v>
@@ -17958,7 +17958,7 @@
         <v>1.5</v>
       </c>
       <c r="AC108">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AD108">
         <v>1.12</v>
@@ -17986,7 +17986,7 @@
         <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18402,31 +18402,31 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="O111">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="P111">
-        <v>5.13</v>
+        <v>4.4</v>
       </c>
       <c r="Q111">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="R111">
-        <v>2.54</v>
+        <v>2.85</v>
       </c>
       <c r="S111">
         <v>1.12</v>
       </c>
       <c r="T111">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="U111">
         <v>1.79</v>
       </c>
       <c r="V111">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="W111">
         <v>1.25</v>
@@ -18435,31 +18435,31 @@
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z111">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AA111">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AB111">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC111">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD111">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AE111">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AF111">
         <v>1.36</v>
       </c>
       <c r="AG111">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="O112">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P112">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
       </c>
       <c r="R112">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="S112">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T112">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="U112">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="V112">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="W112">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Z112">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="AA112">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AB112">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="AC112">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD112">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AE112">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AF112">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AG112">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O113">
         <v>3.3</v>
       </c>
       <c r="P113">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -19063,7 +19063,7 @@
         <v>3.9</v>
       </c>
       <c r="Q115">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="R115">
         <v>2</v>
@@ -19096,10 +19096,10 @@
         <v>2.41</v>
       </c>
       <c r="AB115">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC115">
-        <v>4.55</v>
+        <v>4.72</v>
       </c>
       <c r="AD115">
         <v>1.13</v>
@@ -19108,10 +19108,10 @@
         <v>1</v>
       </c>
       <c r="AF115">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AG115">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK115">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19389,22 +19389,22 @@
         <v>4.83</v>
       </c>
       <c r="Q117">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R117">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S117">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T117">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="U117">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="V117">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W117">
         <v>1.09</v>
@@ -19416,28 +19416,28 @@
         <v>1.22</v>
       </c>
       <c r="Z117">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA117">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB117">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AC117">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD117">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AE117">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF117">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG117">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK117">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19869,28 +19869,28 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="O120">
-        <v>4.22</v>
+        <v>3.98</v>
       </c>
       <c r="P120">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q120">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="R120">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S120">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T120">
         <v>2.9</v>
       </c>
       <c r="U120">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="V120">
         <v>1.4</v>
@@ -19899,34 +19899,34 @@
         <v>1.1</v>
       </c>
       <c r="X120">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y120">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z120">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA120">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB120">
         <v>1.9</v>
       </c>
       <c r="AC120">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AD120">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE120">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF120">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG120">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK120">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20050,19 +20050,19 @@
         <v>1.36</v>
       </c>
       <c r="T121">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="U121">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="V121">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W121">
         <v>1.06</v>
       </c>
       <c r="X121">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
         <v>1.24</v>
@@ -20198,10 +20198,10 @@
         <v>2.6</v>
       </c>
       <c r="O122">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="P122">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q122">
         <v>2.9</v>
@@ -20225,28 +20225,28 @@
         <v>1.09</v>
       </c>
       <c r="X122">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z122">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="AA122">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB122">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC122">
         <v>3.3</v>
       </c>
       <c r="AD122">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE122">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF122">
         <v>1.67</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="O124">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P124">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q124">
-        <v>3.38</v>
+        <v>3.93</v>
       </c>
       <c r="R124">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S124">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T124">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U124">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="V124">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W124">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X124">
         <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z124">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AA124">
         <v>2.1</v>
       </c>
       <c r="AB124">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC124">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AD124">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE124">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF124">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG124">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="AK124">
         <v>1.33</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q126">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R126">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S126">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T126">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U126">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V126">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W126">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y126">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z126">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA126">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB126">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC126">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD126">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE126">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF126">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG126">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK126">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,10 +21010,10 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O127">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P127">
         <v>5.25</v>
@@ -21022,13 +21022,13 @@
         <v>2.1</v>
       </c>
       <c r="R127">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="S127">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T127">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U127">
         <v>2.85</v>
@@ -21049,16 +21049,16 @@
         <v>3.12</v>
       </c>
       <c r="AA127">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB127">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC127">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="AD127">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE127">
         <v>1.06</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK127">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21188,19 +21188,19 @@
         <v>2.1</v>
       </c>
       <c r="S128">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T128">
         <v>2.73</v>
       </c>
       <c r="U128">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V128">
         <v>1.36</v>
       </c>
       <c r="W128">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X128">
         <v>1.04</v>
@@ -21218,7 +21218,7 @@
         <v>1.79</v>
       </c>
       <c r="AC128">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AD128">
         <v>1.25</v>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK128">
         <v>1.62</v>
@@ -21345,40 +21345,40 @@
         <v>4.72</v>
       </c>
       <c r="Q129">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R129">
         <v>2.4</v>
       </c>
       <c r="S129">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T129">
         <v>3.28</v>
       </c>
       <c r="U129">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V129">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W129">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X129">
         <v>1.03</v>
       </c>
       <c r="Y129">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z129">
         <v>4.2</v>
       </c>
       <c r="AA129">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB129">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AC129">
         <v>2.56</v>
@@ -21387,13 +21387,13 @@
         <v>1.4</v>
       </c>
       <c r="AE129">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF129">
         <v>1.55</v>
       </c>
       <c r="AG129">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK129">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21825,80 +21825,80 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O132">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P132">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="Q132">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="R132">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S132">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T132">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U132">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="V132">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W132">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X132">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y132">
+        <v>1.45</v>
+      </c>
+      <c r="Z132">
+        <v>2.87</v>
+      </c>
+      <c r="AA132">
+        <v>2.26</v>
+      </c>
+      <c r="AB132">
+        <v>1.6</v>
+      </c>
+      <c r="AC132">
+        <v>4.7</v>
+      </c>
+      <c r="AD132">
+        <v>1.21</v>
+      </c>
+      <c r="AE132">
+        <v>1.03</v>
+      </c>
+      <c r="AF132">
+        <v>1.9</v>
+      </c>
+      <c r="AG132">
+        <v>1.75</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
         <v>1.36</v>
       </c>
-      <c r="Z132">
-        <v>2.8</v>
-      </c>
-      <c r="AA132">
-        <v>2.2</v>
-      </c>
-      <c r="AB132">
-        <v>1.62</v>
-      </c>
-      <c r="AC132">
-        <v>3.81</v>
-      </c>
-      <c r="AD132">
-        <v>1.24</v>
-      </c>
-      <c r="AE132">
-        <v>1.07</v>
-      </c>
-      <c r="AF132">
-        <v>1.85</v>
-      </c>
-      <c r="AG132">
-        <v>1.87</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>1.33</v>
-      </c>
       <c r="AK132">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>3.06</v>
+        <v>2.4</v>
       </c>
       <c r="O133">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="P133">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="Q133">
-        <v>4.2</v>
+        <v>3.09</v>
       </c>
       <c r="R133">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S133">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T133">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="U133">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V133">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W133">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X133">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z133">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="AA133">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB133">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC133">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD133">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE133">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF133">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG133">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AK133">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22160,10 +22160,10 @@
         <v>5.07</v>
       </c>
       <c r="Q134">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="R134">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S134">
         <v>1.29</v>
@@ -22172,43 +22172,43 @@
         <v>3.08</v>
       </c>
       <c r="U134">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="V134">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W134">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
         <v>1.04</v>
       </c>
       <c r="Y134">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z134">
-        <v>2.9</v>
+        <v>3.76</v>
       </c>
       <c r="AA134">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB134">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AC134">
         <v>2.74</v>
       </c>
       <c r="AD134">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE134">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF134">
         <v>1.67</v>
       </c>
       <c r="AG134">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK134">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AL134">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="Q11">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U11">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -2138,28 +2138,28 @@
         <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA11">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AB11">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC11">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="Q12">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -2301,28 +2301,28 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA12">
+        <v>2.1</v>
+      </c>
+      <c r="AB12">
         <v>1.72</v>
       </c>
-      <c r="AB12">
-        <v>1.92</v>
-      </c>
       <c r="AC12">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD12">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="O46">
         <v>3.45</v>
       </c>
       <c r="P46">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q46">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R46">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="S46">
         <v>1.29</v>
@@ -13213,22 +13213,22 @@
         <v>1.36</v>
       </c>
       <c r="W79">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z79">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AA79">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB79">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC79">
         <v>3.2</v>
@@ -13355,7 +13355,7 @@
         <v>3.34</v>
       </c>
       <c r="P80">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q80">
         <v>4.75</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O83">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="P83">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="Q83">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R83">
         <v>1.85</v>
       </c>
       <c r="S83">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="T83">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U83">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="V83">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W83">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
         <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Z83">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="AA83">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AB83">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AC83">
-        <v>5.3</v>
+        <v>6.21</v>
       </c>
       <c r="AD83">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AG83">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O84">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="P84">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="Q84">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R84">
         <v>1.85</v>
       </c>
       <c r="S84">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="T84">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U84">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="V84">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W84">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X84">
         <v>1.08</v>
       </c>
       <c r="Y84">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="Z84">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="AA84">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AB84">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AC84">
-        <v>6.21</v>
+        <v>5.3</v>
       </c>
       <c r="AD84">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AG84">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK84">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -16778,7 +16778,7 @@
         <v>3.3</v>
       </c>
       <c r="P101">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q101">
         <v>2.7</v>
@@ -16802,13 +16802,13 @@
         <v>1.05</v>
       </c>
       <c r="X101">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
         <v>1.29</v>
       </c>
       <c r="Z101">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="AA101">
         <v>2.06</v>
@@ -16820,7 +16820,7 @@
         <v>3.58</v>
       </c>
       <c r="AD101">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE101">
         <v>1.05</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="O106">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
-        <v>4.8</v>
+        <v>5.85</v>
       </c>
       <c r="Q106">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="R106">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="S106">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="T106">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="U106">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="V106">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W106">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X106">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y106">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z106">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="AA106">
-        <v>2.97</v>
+        <v>2.43</v>
       </c>
       <c r="AB106">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC106">
-        <v>5.95</v>
+        <v>4.7</v>
       </c>
       <c r="AD106">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE106">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF106">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG106">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AK106">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="O107">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P107">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q107">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="R107">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="S107">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="T107">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U107">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V107">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W107">
         <v>1.03</v>
       </c>
       <c r="X107">
+        <v>1.08</v>
+      </c>
+      <c r="Y107">
+        <v>1.62</v>
+      </c>
+      <c r="Z107">
+        <v>2.16</v>
+      </c>
+      <c r="AA107">
+        <v>2.97</v>
+      </c>
+      <c r="AB107">
+        <v>1.36</v>
+      </c>
+      <c r="AC107">
+        <v>5.95</v>
+      </c>
+      <c r="AD107">
+        <v>1.07</v>
+      </c>
+      <c r="AE107">
+        <v>1.03</v>
+      </c>
+      <c r="AF107">
+        <v>2.6</v>
+      </c>
+      <c r="AG107">
+        <v>1.43</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.09</v>
       </c>
-      <c r="Y107">
-        <v>1.66</v>
-      </c>
-      <c r="Z107">
-        <v>2.12</v>
-      </c>
-      <c r="AA107">
-        <v>2.88</v>
-      </c>
-      <c r="AB107">
-        <v>1.32</v>
-      </c>
-      <c r="AC107">
-        <v>6.05</v>
-      </c>
-      <c r="AD107">
-        <v>1.06</v>
-      </c>
-      <c r="AE107">
-        <v>1.02</v>
-      </c>
-      <c r="AF107">
-        <v>2.45</v>
-      </c>
-      <c r="AG107">
-        <v>1.44</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.31</v>
-      </c>
       <c r="AK107">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="O108">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P108">
-        <v>5.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q108">
-        <v>2.29</v>
+        <v>2.68</v>
       </c>
       <c r="R108">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="S108">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="T108">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="U108">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="V108">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W108">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X108">
+        <v>1.09</v>
+      </c>
+      <c r="Y108">
+        <v>1.66</v>
+      </c>
+      <c r="Z108">
+        <v>2.12</v>
+      </c>
+      <c r="AA108">
+        <v>2.88</v>
+      </c>
+      <c r="AB108">
+        <v>1.32</v>
+      </c>
+      <c r="AC108">
+        <v>6.05</v>
+      </c>
+      <c r="AD108">
         <v>1.06</v>
       </c>
-      <c r="Y108">
-        <v>1.49</v>
-      </c>
-      <c r="Z108">
-        <v>2.44</v>
-      </c>
-      <c r="AA108">
-        <v>2.43</v>
-      </c>
-      <c r="AB108">
-        <v>1.5</v>
-      </c>
-      <c r="AC108">
-        <v>4.7</v>
-      </c>
-      <c r="AD108">
-        <v>1.12</v>
-      </c>
       <c r="AE108">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF108">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG108">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK108">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18405,13 +18405,13 @@
         <v>1.38</v>
       </c>
       <c r="O111">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="P111">
         <v>4.4</v>
       </c>
       <c r="Q111">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R111">
         <v>2.85</v>
@@ -18574,16 +18574,16 @@
         <v>2.5</v>
       </c>
       <c r="Q112">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R112">
         <v>2.62</v>
       </c>
       <c r="S112">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T112">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U112">
         <v>1.78</v>
@@ -18619,7 +18619,7 @@
         <v>1.43</v>
       </c>
       <c r="AF112">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AG112">
         <v>2.8</v>
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O124">
         <v>3.3</v>
@@ -20539,7 +20539,7 @@
         <v>1.44</v>
       </c>
       <c r="T124">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U124">
         <v>3.05</v>
@@ -20548,7 +20548,7 @@
         <v>1.32</v>
       </c>
       <c r="W124">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X124">
         <v>1.01</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AK124">
         <v>1.33</v>
@@ -21994,13 +21994,13 @@
         <v>3.32</v>
       </c>
       <c r="P133">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="Q133">
         <v>3.09</v>
       </c>
       <c r="R133">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S133">
         <v>1.37</v>
@@ -22009,10 +22009,10 @@
         <v>3</v>
       </c>
       <c r="U133">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="V133">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W133">
         <v>1.08</v>
@@ -22039,7 +22039,7 @@
         <v>1.26</v>
       </c>
       <c r="AE133">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF133">
         <v>1.73</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -1456,58 +1456,58 @@
         <v>3.1</v>
       </c>
       <c r="P7">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q7">
-        <v>4.64</v>
+        <v>5.01</v>
       </c>
       <c r="R7">
         <v>1.95</v>
       </c>
       <c r="S7">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="T7">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="U7">
         <v>3.34</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z7">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AA7">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AB7">
         <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AD7">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG7">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AK7">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,22 +1622,22 @@
         <v>4.22</v>
       </c>
       <c r="Q8">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R8">
         <v>2.16</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="U8">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
         <v>1.07</v>
@@ -1652,16 +1652,16 @@
         <v>3.54</v>
       </c>
       <c r="AA8">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AC8">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="AD8">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
         <v>1.1</v>
@@ -1785,46 +1785,46 @@
         <v>1.95</v>
       </c>
       <c r="Q9">
-        <v>5.02</v>
+        <v>4.85</v>
       </c>
       <c r="R9">
         <v>1.93</v>
       </c>
       <c r="S9">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T9">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="U9">
         <v>3.3</v>
       </c>
       <c r="V9">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
         <v>1.03</v>
       </c>
-      <c r="X9">
-        <v>1.05</v>
-      </c>
       <c r="Y9">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z9">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AA9">
         <v>2.35</v>
       </c>
       <c r="AB9">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AD9">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
         <v>1</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,28 +1942,28 @@
         <v>1.7</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="R10">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T10">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="U10">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
         <v>1.03</v>
@@ -1975,19 +1975,19 @@
         <v>1.44</v>
       </c>
       <c r="Z10">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AA10">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB10">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD10">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE10">
         <v>1.01</v>
@@ -1996,7 +1996,7 @@
         <v>2.18</v>
       </c>
       <c r="AG10">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="O18">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="P18">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="Q18">
+        <v>2.45</v>
+      </c>
+      <c r="R18">
         <v>2.4</v>
       </c>
-      <c r="R18">
-        <v>2.35</v>
-      </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
         <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>4.95</v>
+        <v>5.35</v>
       </c>
       <c r="AA18">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AC18">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="AD18">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AE18">
+        <v>1.26</v>
+      </c>
+      <c r="AF18">
+        <v>1.4</v>
+      </c>
+      <c r="AG18">
+        <v>2.7</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.22</v>
       </c>
-      <c r="AF18">
-        <v>1.44</v>
-      </c>
-      <c r="AG18">
-        <v>2.55</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.25</v>
-      </c>
       <c r="AK18">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="O19">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="P19">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="Q19">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U19">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="V19">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>5.35</v>
+        <v>4.95</v>
       </c>
       <c r="AA19">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AB19">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AC19">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AD19">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AE19">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.48</v>
+        <v>5.5</v>
       </c>
       <c r="O23">
         <v>4.7</v>
       </c>
       <c r="P23">
-        <v>5.65</v>
+        <v>1.38</v>
       </c>
       <c r="Q23">
-        <v>1.92</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="S23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="U23">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="V23">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W23">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
+        <v>1.11</v>
+      </c>
+      <c r="Z23">
+        <v>5.25</v>
+      </c>
+      <c r="AA23">
+        <v>1.48</v>
+      </c>
+      <c r="AB23">
+        <v>2.63</v>
+      </c>
+      <c r="AC23">
+        <v>2.07</v>
+      </c>
+      <c r="AD23">
+        <v>1.7</v>
+      </c>
+      <c r="AE23">
+        <v>1.28</v>
+      </c>
+      <c r="AF23">
+        <v>1.58</v>
+      </c>
+      <c r="AG23">
+        <v>2.25</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.14</v>
+      </c>
+      <c r="AK23">
         <v>1.08</v>
-      </c>
-      <c r="Z23">
-        <v>5.5</v>
-      </c>
-      <c r="AA23">
-        <v>1.44</v>
-      </c>
-      <c r="AB23">
-        <v>2.6</v>
-      </c>
-      <c r="AC23">
-        <v>2.1</v>
-      </c>
-      <c r="AD23">
-        <v>1.75</v>
-      </c>
-      <c r="AE23">
-        <v>1.33</v>
-      </c>
-      <c r="AF23">
-        <v>1.53</v>
-      </c>
-      <c r="AG23">
-        <v>2.31</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.16</v>
-      </c>
-      <c r="AK23">
-        <v>2.59</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>5.5</v>
+        <v>1.48</v>
       </c>
       <c r="O24">
         <v>4.7</v>
       </c>
       <c r="P24">
-        <v>1.38</v>
+        <v>5.65</v>
       </c>
       <c r="Q24">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="R24">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T24">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="U24">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="V24">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z24">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA24">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB24">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC24">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AD24">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE24">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF24">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>1.08</v>
+        <v>2.59</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="O51">
-        <v>3.91</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>3.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q51">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="R51">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S51">
         <v>1.28</v>
       </c>
       <c r="T51">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U51">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="V51">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA51">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB51">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="AC51">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="AD51">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AE51">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.91</v>
       </c>
       <c r="P52">
-        <v>2.1</v>
+        <v>3.93</v>
       </c>
       <c r="Q52">
-        <v>3.4</v>
+        <v>2.24</v>
       </c>
       <c r="R52">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S52">
         <v>1.28</v>
       </c>
       <c r="T52">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U52">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
+        <v>1.17</v>
+      </c>
+      <c r="Z52">
+        <v>4.3</v>
+      </c>
+      <c r="AA52">
+        <v>1.6</v>
+      </c>
+      <c r="AB52">
+        <v>2.31</v>
+      </c>
+      <c r="AC52">
+        <v>2.4</v>
+      </c>
+      <c r="AD52">
+        <v>1.49</v>
+      </c>
+      <c r="AE52">
         <v>1.18</v>
       </c>
-      <c r="Z52">
-        <v>4.2</v>
-      </c>
-      <c r="AA52">
-        <v>1.65</v>
-      </c>
-      <c r="AB52">
-        <v>2.07</v>
-      </c>
-      <c r="AC52">
-        <v>2.61</v>
-      </c>
-      <c r="AD52">
-        <v>1.39</v>
-      </c>
-      <c r="AE52">
-        <v>1.13</v>
-      </c>
       <c r="AF52">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG52">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.13</v>
+        <v>2.67</v>
       </c>
       <c r="O57">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="Q57">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="R57">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S57">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>4.8</v>
+        <v>3.82</v>
       </c>
       <c r="U57">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="V57">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="W57">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z57">
-        <v>7</v>
+        <v>5.97</v>
       </c>
       <c r="AA57">
+        <v>1.44</v>
+      </c>
+      <c r="AB57">
+        <v>2.62</v>
+      </c>
+      <c r="AC57">
+        <v>2.04</v>
+      </c>
+      <c r="AD57">
+        <v>1.74</v>
+      </c>
+      <c r="AE57">
+        <v>1.27</v>
+      </c>
+      <c r="AF57">
+        <v>1.36</v>
+      </c>
+      <c r="AG57">
+        <v>2.77</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>1.22</v>
+      </c>
+      <c r="AK57">
         <v>1.3</v>
-      </c>
-      <c r="AB57">
-        <v>3.28</v>
-      </c>
-      <c r="AC57">
-        <v>1.73</v>
-      </c>
-      <c r="AD57">
-        <v>2.07</v>
-      </c>
-      <c r="AE57">
-        <v>1.42</v>
-      </c>
-      <c r="AF57">
-        <v>1.27</v>
-      </c>
-      <c r="AG57">
-        <v>3.3</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.2</v>
-      </c>
-      <c r="AK57">
-        <v>1.62</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="P58">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="Q58">
+        <v>2.54</v>
+      </c>
+      <c r="R58">
+        <v>2.54</v>
+      </c>
+      <c r="S58">
+        <v>1.15</v>
+      </c>
+      <c r="T58">
+        <v>4.8</v>
+      </c>
+      <c r="U58">
+        <v>1.83</v>
+      </c>
+      <c r="V58">
+        <v>1.89</v>
+      </c>
+      <c r="W58">
+        <v>1.24</v>
+      </c>
+      <c r="X58">
+        <v>1.01</v>
+      </c>
+      <c r="Y58">
+        <v>1.04</v>
+      </c>
+      <c r="Z58">
+        <v>7</v>
+      </c>
+      <c r="AA58">
+        <v>1.3</v>
+      </c>
+      <c r="AB58">
+        <v>3.28</v>
+      </c>
+      <c r="AC58">
+        <v>1.73</v>
+      </c>
+      <c r="AD58">
+        <v>2.07</v>
+      </c>
+      <c r="AE58">
+        <v>1.42</v>
+      </c>
+      <c r="AF58">
+        <v>1.27</v>
+      </c>
+      <c r="AG58">
         <v>3.3</v>
       </c>
-      <c r="R58">
-        <v>2.6</v>
-      </c>
-      <c r="S58">
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.2</v>
       </c>
-      <c r="T58">
-        <v>3.82</v>
-      </c>
-      <c r="U58">
-        <v>2.06</v>
-      </c>
-      <c r="V58">
-        <v>1.69</v>
-      </c>
-      <c r="W58">
-        <v>1.17</v>
-      </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.08</v>
-      </c>
-      <c r="Z58">
-        <v>5.97</v>
-      </c>
-      <c r="AA58">
-        <v>1.44</v>
-      </c>
-      <c r="AB58">
-        <v>2.62</v>
-      </c>
-      <c r="AC58">
-        <v>2.04</v>
-      </c>
-      <c r="AD58">
-        <v>1.74</v>
-      </c>
-      <c r="AE58">
-        <v>1.27</v>
-      </c>
-      <c r="AF58">
-        <v>1.36</v>
-      </c>
-      <c r="AG58">
-        <v>2.77</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.22</v>
-      </c>
       <c r="AK58">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="O106">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P106">
-        <v>5.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q106">
-        <v>2.29</v>
+        <v>2.68</v>
       </c>
       <c r="R106">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="S106">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="T106">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="U106">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="V106">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W106">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X106">
+        <v>1.09</v>
+      </c>
+      <c r="Y106">
+        <v>1.66</v>
+      </c>
+      <c r="Z106">
+        <v>2.12</v>
+      </c>
+      <c r="AA106">
+        <v>2.88</v>
+      </c>
+      <c r="AB106">
+        <v>1.32</v>
+      </c>
+      <c r="AC106">
+        <v>6.05</v>
+      </c>
+      <c r="AD106">
         <v>1.06</v>
       </c>
-      <c r="Y106">
-        <v>1.49</v>
-      </c>
-      <c r="Z106">
-        <v>2.44</v>
-      </c>
-      <c r="AA106">
-        <v>2.43</v>
-      </c>
-      <c r="AB106">
-        <v>1.5</v>
-      </c>
-      <c r="AC106">
-        <v>4.7</v>
-      </c>
-      <c r="AD106">
-        <v>1.12</v>
-      </c>
       <c r="AE106">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF106">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG106">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK106">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="O108">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>4.2</v>
+        <v>5.85</v>
       </c>
       <c r="Q108">
-        <v>2.68</v>
+        <v>2.29</v>
       </c>
       <c r="R108">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="S108">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="T108">
-        <v>2.17</v>
+        <v>2.39</v>
       </c>
       <c r="U108">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="V108">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W108">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y108">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="Z108">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AA108">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AB108">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AC108">
-        <v>6.05</v>
+        <v>4.7</v>
       </c>
       <c r="AD108">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AE108">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF108">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AG108">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AL108">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="O3">
+        <v>3.75</v>
+      </c>
+      <c r="P3">
         <v>4</v>
       </c>
-      <c r="P3">
-        <v>4.2</v>
-      </c>
       <c r="Q3">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="R3">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T3">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V3">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC3">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AD3">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q4">
+        <v>2.41</v>
+      </c>
+      <c r="R4">
+        <v>2.13</v>
+      </c>
+      <c r="S4">
+        <v>1.32</v>
+      </c>
+      <c r="T4">
+        <v>2.92</v>
+      </c>
+      <c r="U4">
         <v>2.5</v>
       </c>
-      <c r="R4">
-        <v>2.3</v>
-      </c>
-      <c r="S4">
-        <v>1.29</v>
-      </c>
-      <c r="T4">
-        <v>2.97</v>
-      </c>
-      <c r="U4">
-        <v>2.39</v>
-      </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="AA4">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB4">
+        <v>1.97</v>
+      </c>
+      <c r="AC4">
+        <v>2.7</v>
+      </c>
+      <c r="AD4">
+        <v>1.36</v>
+      </c>
+      <c r="AE4">
+        <v>1.11</v>
+      </c>
+      <c r="AF4">
+        <v>1.6</v>
+      </c>
+      <c r="AG4">
         <v>2.15</v>
       </c>
-      <c r="AC4">
-        <v>2.52</v>
-      </c>
-      <c r="AD4">
-        <v>1.41</v>
-      </c>
-      <c r="AE4">
-        <v>1.14</v>
-      </c>
-      <c r="AF4">
-        <v>1.55</v>
-      </c>
-      <c r="AG4">
-        <v>2.2</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>3.65</v>
       </c>
       <c r="Q5">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="R5">
         <v>1.96</v>
@@ -1163,7 +1163,7 @@
         <v>2.74</v>
       </c>
       <c r="AA5">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AB5">
         <v>1.67</v>
@@ -1197,7 +1197,7 @@
         <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,43 +1776,43 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="Q9">
-        <v>4.85</v>
+        <v>2.31</v>
       </c>
       <c r="R9">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="S9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="U9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z9">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AA9">
         <v>2.35</v>
@@ -1821,35 +1821,35 @@
         <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD9">
+        <v>1.14</v>
+      </c>
+      <c r="AE9">
+        <v>1.01</v>
+      </c>
+      <c r="AF9">
+        <v>2.18</v>
+      </c>
+      <c r="AG9">
+        <v>1.67</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.15</v>
       </c>
-      <c r="AE9">
-        <v>1</v>
-      </c>
-      <c r="AF9">
-        <v>2</v>
-      </c>
-      <c r="AG9">
-        <v>1.73</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.27</v>
-      </c>
       <c r="AK9">
-        <v>1.16</v>
+        <v>2.06</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,43 +1939,43 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.7</v>
+        <v>3.75</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q10">
-        <v>2.31</v>
+        <v>4.85</v>
       </c>
       <c r="R10">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="S10">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T10">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
         <v>1.03</v>
       </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
       <c r="Y10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z10">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AA10">
         <v>2.35</v>
@@ -1984,19 +1984,19 @@
         <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE10">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF10">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AG10">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
-        <v>2.06</v>
+        <v>1.16</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="Q11">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="R11">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -2138,28 +2138,28 @@
         <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
+        <v>2.1</v>
+      </c>
+      <c r="AB11">
         <v>1.72</v>
       </c>
-      <c r="AB11">
-        <v>1.92</v>
-      </c>
       <c r="AC11">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="Q12">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U12">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -2301,28 +2301,28 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA12">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AB12">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q14">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="R14">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U14">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="V14">
         <v>1.49</v>
@@ -2621,34 +2621,34 @@
         <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA14">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AC14">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AD14">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG14">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="AK14">
         <v>1.27</v>
@@ -2920,10 +2920,10 @@
         <v>2.31</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P16">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="Q16">
         <v>3.12</v>
@@ -2956,13 +2956,13 @@
         <v>2.86</v>
       </c>
       <c r="AA16">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB16">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>4.09</v>
+        <v>3.94</v>
       </c>
       <c r="AD16">
         <v>1.21</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AK16">
         <v>1.58</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O21">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q21">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S21">
         <v>1.2</v>
@@ -3765,22 +3765,22 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA21">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB21">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AC21">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AD21">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE21">
         <v>1.26</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
         <v>1.91</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O22">
         <v>3.25</v>
@@ -3910,10 +3910,10 @@
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T22">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U22">
         <v>3.08</v>
@@ -3928,13 +3928,13 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="AA22">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
         <v>1.75</v>
@@ -3952,7 +3952,7 @@
         <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>5.5</v>
+        <v>1.45</v>
       </c>
       <c r="O23">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P23">
-        <v>1.38</v>
+        <v>4.8</v>
       </c>
       <c r="Q23">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="R23">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U23">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V23">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W23">
         <v>1.14</v>
@@ -4091,31 +4091,31 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z23">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA23">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AB23">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AC23">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AD23">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE23">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF23">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>1.08</v>
+        <v>2.59</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.48</v>
+        <v>5.4</v>
       </c>
       <c r="O24">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P24">
-        <v>5.65</v>
+        <v>1.38</v>
       </c>
       <c r="Q24">
-        <v>1.92</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="U24">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="V24">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W24">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
         <v>5.5</v>
       </c>
       <c r="AA24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB24">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AC24">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD24">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE24">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>2.59</v>
+        <v>1.09</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P25">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Q25">
         <v>5.25</v>
@@ -4402,25 +4402,25 @@
         <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U25">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA25">
         <v>1.44</v>
@@ -4429,16 +4429,16 @@
         <v>2.43</v>
       </c>
       <c r="AC25">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AD25">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE25">
         <v>1.25</v>
       </c>
       <c r="AF25">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG25">
         <v>2.25</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>2.38</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4559,28 +4559,28 @@
         <v>2.6</v>
       </c>
       <c r="R26">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="Z26">
         <v>3</v>
@@ -4589,13 +4589,13 @@
         <v>1.81</v>
       </c>
       <c r="AB26">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AC26">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
         <v>1.1</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="O27">
         <v>3.35</v>
       </c>
       <c r="P27">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q27">
         <v>2.66</v>
@@ -4731,10 +4731,10 @@
         <v>3.08</v>
       </c>
       <c r="U27">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W27">
         <v>1.11</v>
@@ -4749,25 +4749,25 @@
         <v>4.1</v>
       </c>
       <c r="AA27">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB27">
         <v>2.25</v>
       </c>
       <c r="AC27">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AD27">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF27">
         <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.24</v>
       </c>
       <c r="AK27">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P28">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="R28">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="S28">
         <v>1.2</v>
@@ -4894,43 +4894,43 @@
         <v>4</v>
       </c>
       <c r="U28">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V28">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W28">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>4.9</v>
+        <v>6.29</v>
       </c>
       <c r="AA28">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AB28">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="AC28">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD28">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE28">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF28">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AG28">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB29">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5205,28 +5205,28 @@
         <v>3.55</v>
       </c>
       <c r="P30">
-        <v>5.35</v>
+        <v>4.45</v>
       </c>
       <c r="Q30">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="R30">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U30">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V30">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
         <v>1.03</v>
@@ -5235,10 +5235,10 @@
         <v>1.3</v>
       </c>
       <c r="Z30">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="AA30">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB30">
         <v>1.78</v>
@@ -5250,13 +5250,13 @@
         <v>1.29</v>
       </c>
       <c r="AE30">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
         <v>1.92</v>
       </c>
       <c r="AG30">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="O32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R32">
-        <v>2.81</v>
+        <v>2.97</v>
       </c>
       <c r="S32">
         <v>1.2</v>
       </c>
       <c r="T32">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="U32">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="V32">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W32">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z32">
-        <v>5.05</v>
+        <v>4.92</v>
       </c>
       <c r="AA32">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB32">
         <v>2.5</v>
       </c>
       <c r="AC32">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="AD32">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE32">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF32">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AG32">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK32">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O33">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S33">
         <v>1.26</v>
@@ -5709,7 +5709,7 @@
         <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V33">
         <v>1.57</v>
@@ -5721,16 +5721,16 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z33">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="AA33">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB33">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AC33">
         <v>2.29</v>
@@ -5739,13 +5739,13 @@
         <v>1.55</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF33">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,13 +5860,13 @@
         <v>4.32</v>
       </c>
       <c r="Q34">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
         <v>2.95</v>
@@ -5878,7 +5878,7 @@
         <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5896,7 +5896,7 @@
         <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD34">
         <v>1.35</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AK34">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6020,49 +6020,49 @@
         <v>3.75</v>
       </c>
       <c r="P35">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q35">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S35">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T35">
         <v>3.25</v>
       </c>
       <c r="U35">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z35">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA35">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB35">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AC35">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="AD35">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE35">
         <v>1.13</v>
@@ -6087,7 +6087,7 @@
         <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6183,13 +6183,13 @@
         <v>3.4</v>
       </c>
       <c r="P36">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q36">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="R36">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="S36">
         <v>1.43</v>
@@ -6219,10 +6219,10 @@
         <v>2.19</v>
       </c>
       <c r="AB36">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC36">
-        <v>3.91</v>
+        <v>3.84</v>
       </c>
       <c r="AD36">
         <v>1.18</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AK36">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O37">
         <v>3.85</v>
       </c>
       <c r="P37">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="Q37">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="R37">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="U37">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6373,31 +6373,31 @@
         <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z37">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="AA37">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB37">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="AD37">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE37">
         <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG37">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK37">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="O38">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="P38">
         <v>6</v>
       </c>
       <c r="Q38">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R38">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="U38">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V38">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AA38">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AC38">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AD38">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE38">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,10 +6669,10 @@
         <v>1.44</v>
       </c>
       <c r="O39">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="P39">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6838,22 +6838,22 @@
         <v>2.91</v>
       </c>
       <c r="Q40">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R40">
         <v>2.18</v>
       </c>
       <c r="S40">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U40">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W40">
         <v>1.1</v>
@@ -6865,7 +6865,7 @@
         <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA40">
         <v>1.78</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK40">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="O41">
         <v>4.4</v>
       </c>
       <c r="P41">
-        <v>5.4</v>
+        <v>6.25</v>
       </c>
       <c r="Q41">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R41">
         <v>2.43</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T41">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="U41">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V41">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W41">
         <v>1.13</v>
@@ -7025,25 +7025,25 @@
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z41">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB41">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="AC41">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AD41">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE41">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF41">
         <v>1.62</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK41">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="O42">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="P42">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="Q42">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S42">
         <v>1.21</v>
@@ -7188,22 +7188,22 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z42">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA42">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB42">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AC42">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD42">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE42">
         <v>1.28</v>
@@ -7212,7 +7212,7 @@
         <v>1.43</v>
       </c>
       <c r="AG42">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O43">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="P43">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Q43">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R43">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="S43">
         <v>1.29</v>
       </c>
       <c r="T43">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U43">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V43">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z43">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="AA43">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB43">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AC43">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AD43">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE43">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF43">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG43">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AK43">
         <v>3.2</v>
@@ -7481,37 +7481,37 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O44">
-        <v>3.72</v>
+        <v>3.57</v>
       </c>
       <c r="P44">
-        <v>3.88</v>
+        <v>3.18</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S44">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T44">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U44">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="V44">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
         <v>1.16</v>
@@ -7520,19 +7520,19 @@
         <v>4.15</v>
       </c>
       <c r="AA44">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB44">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC44">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD44">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
         <v>1.61</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O45">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P45">
         <v>2.37</v>
@@ -7656,37 +7656,37 @@
         <v>3.72</v>
       </c>
       <c r="R45">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
         <v>1.46</v>
       </c>
       <c r="T45">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U45">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="V45">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
         <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z45">
-        <v>2.92</v>
+        <v>3.24</v>
       </c>
       <c r="AA45">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AB45">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC45">
         <v>3.8</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK45">
         <v>1.37</v>
@@ -7816,22 +7816,22 @@
         <v>2.95</v>
       </c>
       <c r="Q46">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R46">
         <v>2.19</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T46">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U46">
         <v>2.33</v>
       </c>
       <c r="V46">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
         <v>1.11</v>
@@ -7843,7 +7843,7 @@
         <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA46">
         <v>1.65</v>
@@ -7852,19 +7852,19 @@
         <v>2.16</v>
       </c>
       <c r="AC46">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD46">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE46">
         <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>4.48</v>
       </c>
       <c r="Q48">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="R48">
         <v>1.96</v>
@@ -8172,7 +8172,7 @@
         <v>2.74</v>
       </c>
       <c r="AA48">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AB48">
         <v>1.68</v>
@@ -8206,7 +8206,7 @@
         <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="O50">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="P50">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q50">
         <v>3.63</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S50">
         <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U50">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
         <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA50">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB50">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC50">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AK50">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O51">
         <v>3.4</v>
@@ -8631,55 +8631,55 @@
         <v>2.1</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="R51">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="S51">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA51">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AC51">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="AD51">
         <v>1.39</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="O52">
-        <v>3.91</v>
+        <v>4.85</v>
       </c>
       <c r="P52">
-        <v>3.93</v>
+        <v>1.32</v>
       </c>
       <c r="Q52">
-        <v>2.24</v>
+        <v>5.95</v>
       </c>
       <c r="R52">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T52">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U52">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="V52">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z52">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AA52">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AB52">
-        <v>2.31</v>
+        <v>2.89</v>
       </c>
       <c r="AC52">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="AD52">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="AE52">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK52">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>6.25</v>
+        <v>1.86</v>
       </c>
       <c r="O53">
-        <v>5.4</v>
+        <v>3.91</v>
       </c>
       <c r="P53">
-        <v>1.36</v>
+        <v>3.93</v>
       </c>
       <c r="Q53">
-        <v>5.2</v>
+        <v>2.24</v>
       </c>
       <c r="R53">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="S53">
+        <v>1.28</v>
+      </c>
+      <c r="T53">
+        <v>3.34</v>
+      </c>
+      <c r="U53">
+        <v>2.36</v>
+      </c>
+      <c r="V53">
+        <v>1.56</v>
+      </c>
+      <c r="W53">
+        <v>1.09</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
         <v>1.18</v>
       </c>
-      <c r="T53">
-        <v>4.1</v>
-      </c>
-      <c r="U53">
-        <v>1.99</v>
-      </c>
-      <c r="V53">
-        <v>1.76</v>
-      </c>
-      <c r="W53">
-        <v>1.2</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.08</v>
-      </c>
       <c r="Z53">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AA53">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AB53">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC53">
-        <v>1.91</v>
+        <v>2.47</v>
       </c>
       <c r="AD53">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE53">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF53">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG53">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>2.63</v>
+        <v>1.19</v>
       </c>
       <c r="AK53">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="O54">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="P54">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q54">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="R54">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S54">
         <v>1.22</v>
@@ -9144,7 +9144,7 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z54">
         <v>5.1</v>
@@ -9156,7 +9156,7 @@
         <v>2.49</v>
       </c>
       <c r="AC54">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AD54">
         <v>1.66</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
         <v>1.3</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>3.58</v>
+        <v>4.7</v>
       </c>
       <c r="Q55">
         <v>2.13</v>
       </c>
       <c r="R55">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="S55">
         <v>1.17</v>
@@ -9295,7 +9295,7 @@
         <v>4.1</v>
       </c>
       <c r="U55">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="V55">
         <v>1.75</v>
@@ -9310,22 +9310,22 @@
         <v>1.06</v>
       </c>
       <c r="Z55">
-        <v>7</v>
+        <v>6.05</v>
       </c>
       <c r="AA55">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB55">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AC55">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AD55">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AE55">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AF55">
         <v>1.4</v>
@@ -9347,7 +9347,7 @@
         <v>1.19</v>
       </c>
       <c r="AK55">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,10 +9446,10 @@
         <v>1.95</v>
       </c>
       <c r="Q56">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="R56">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="S56">
         <v>1.19</v>
@@ -9458,10 +9458,10 @@
         <v>3.88</v>
       </c>
       <c r="U56">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="V56">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W56">
         <v>1.14</v>
@@ -9473,22 +9473,22 @@
         <v>1.08</v>
       </c>
       <c r="Z56">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA56">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB56">
         <v>2.62</v>
       </c>
       <c r="AC56">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AD56">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE56">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AF56">
         <v>1.39</v>
@@ -9510,7 +9510,7 @@
         <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="P57">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="Q57">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="R57">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="S57">
+        <v>1.14</v>
+      </c>
+      <c r="T57">
+        <v>5</v>
+      </c>
+      <c r="U57">
+        <v>1.84</v>
+      </c>
+      <c r="V57">
+        <v>1.94</v>
+      </c>
+      <c r="W57">
+        <v>1.25</v>
+      </c>
+      <c r="X57">
+        <v>1.01</v>
+      </c>
+      <c r="Y57">
+        <v>1.05</v>
+      </c>
+      <c r="Z57">
+        <v>8.5</v>
+      </c>
+      <c r="AA57">
+        <v>1.29</v>
+      </c>
+      <c r="AB57">
+        <v>3.28</v>
+      </c>
+      <c r="AC57">
+        <v>1.73</v>
+      </c>
+      <c r="AD57">
+        <v>2.05</v>
+      </c>
+      <c r="AE57">
+        <v>1.42</v>
+      </c>
+      <c r="AF57">
+        <v>1.27</v>
+      </c>
+      <c r="AG57">
+        <v>3.42</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.2</v>
       </c>
-      <c r="T57">
-        <v>3.82</v>
-      </c>
-      <c r="U57">
-        <v>2.06</v>
-      </c>
-      <c r="V57">
-        <v>1.69</v>
-      </c>
-      <c r="W57">
-        <v>1.17</v>
-      </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>1.08</v>
-      </c>
-      <c r="Z57">
-        <v>5.97</v>
-      </c>
-      <c r="AA57">
-        <v>1.44</v>
-      </c>
-      <c r="AB57">
-        <v>2.62</v>
-      </c>
-      <c r="AC57">
-        <v>2.04</v>
-      </c>
-      <c r="AD57">
-        <v>1.74</v>
-      </c>
-      <c r="AE57">
-        <v>1.27</v>
-      </c>
-      <c r="AF57">
-        <v>1.36</v>
-      </c>
-      <c r="AG57">
-        <v>2.77</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.22</v>
-      </c>
       <c r="AK57">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="O58">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="Q58">
-        <v>2.54</v>
+        <v>3.56</v>
       </c>
       <c r="R58">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="S58">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T58">
-        <v>4.8</v>
+        <v>3.82</v>
       </c>
       <c r="U58">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="V58">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="W58">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Z58">
-        <v>7</v>
+        <v>5.45</v>
       </c>
       <c r="AA58">
+        <v>1.38</v>
+      </c>
+      <c r="AB58">
+        <v>2.62</v>
+      </c>
+      <c r="AC58">
+        <v>2.04</v>
+      </c>
+      <c r="AD58">
+        <v>1.74</v>
+      </c>
+      <c r="AE58">
+        <v>1.27</v>
+      </c>
+      <c r="AF58">
+        <v>1.36</v>
+      </c>
+      <c r="AG58">
+        <v>2.77</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>1.22</v>
+      </c>
+      <c r="AK58">
         <v>1.3</v>
-      </c>
-      <c r="AB58">
-        <v>3.28</v>
-      </c>
-      <c r="AC58">
-        <v>1.73</v>
-      </c>
-      <c r="AD58">
-        <v>2.07</v>
-      </c>
-      <c r="AE58">
-        <v>1.42</v>
-      </c>
-      <c r="AF58">
-        <v>1.27</v>
-      </c>
-      <c r="AG58">
-        <v>3.3</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.2</v>
-      </c>
-      <c r="AK58">
-        <v>1.62</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,25 +9926,25 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="O59">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
       </c>
       <c r="R59">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S59">
         <v>1.4</v>
       </c>
       <c r="T59">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U59">
         <v>2.65</v>
@@ -9971,7 +9971,7 @@
         <v>1.83</v>
       </c>
       <c r="AC59">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AD59">
         <v>1.32</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AK59">
         <v>1.41</v>
@@ -10092,25 +10092,25 @@
         <v>2.25</v>
       </c>
       <c r="O60">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P60">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q60">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="R60">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
         <v>1.34</v>
       </c>
       <c r="T60">
-        <v>3.11</v>
+        <v>2.95</v>
       </c>
       <c r="U60">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V60">
         <v>1.43</v>
@@ -10125,22 +10125,22 @@
         <v>1.25</v>
       </c>
       <c r="Z60">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AA60">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB60">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC60">
         <v>3.12</v>
       </c>
       <c r="AD60">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE60">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF60">
         <v>1.6</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK60">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10258,31 +10258,31 @@
         <v>3.8</v>
       </c>
       <c r="P61">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="Q61">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R61">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S61">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T61">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U61">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V61">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W61">
         <v>1.05</v>
       </c>
       <c r="X61">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
         <v>1.25</v>
@@ -10294,22 +10294,22 @@
         <v>1.83</v>
       </c>
       <c r="AB61">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC61">
         <v>3.07</v>
       </c>
       <c r="AD61">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE61">
         <v>1.08</v>
       </c>
       <c r="AF61">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG61">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,52 +10424,52 @@
         <v>1.91</v>
       </c>
       <c r="Q62">
-        <v>3.96</v>
+        <v>3.87</v>
       </c>
       <c r="R62">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T62">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="U62">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="V62">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z62">
-        <v>3.96</v>
+        <v>3.82</v>
       </c>
       <c r="AA62">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB62">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AC62">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="AD62">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE62">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG62">
         <v>2.25</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AK62">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,34 +10587,34 @@
         <v>3.85</v>
       </c>
       <c r="Q63">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R63">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S63">
         <v>1.4</v>
       </c>
       <c r="T63">
+        <v>2.6</v>
+      </c>
+      <c r="U63">
         <v>2.88</v>
-      </c>
-      <c r="U63">
-        <v>3</v>
       </c>
       <c r="V63">
         <v>1.33</v>
       </c>
       <c r="W63">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X63">
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z63">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA63">
         <v>2.01</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O64">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P64">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q64">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="R64">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="S64">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="U64">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="V64">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W64">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z64">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="AA64">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AB64">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC64">
-        <v>2.83</v>
+        <v>3.34</v>
       </c>
       <c r="AD64">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE64">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF64">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AG64">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK64">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11239,13 +11239,13 @@
         <v>3.1</v>
       </c>
       <c r="Q67">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="R67">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S67">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T67">
         <v>3.02</v>
@@ -11260,25 +11260,25 @@
         <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
         <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>4.12</v>
+        <v>3.96</v>
       </c>
       <c r="AA67">
         <v>1.69</v>
       </c>
       <c r="AB67">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC67">
         <v>2.66</v>
       </c>
       <c r="AD67">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE67">
         <v>1.11</v>
@@ -11287,7 +11287,7 @@
         <v>1.56</v>
       </c>
       <c r="AG67">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
         <v>1.58</v>
@@ -11402,7 +11402,7 @@
         <v>4</v>
       </c>
       <c r="Q68">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R68">
         <v>2.35</v>
@@ -11414,10 +11414,10 @@
         <v>3.34</v>
       </c>
       <c r="U68">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="V68">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W68">
         <v>1.14</v>
@@ -11432,10 +11432,10 @@
         <v>4.5</v>
       </c>
       <c r="AA68">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AB68">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC68">
         <v>2.28</v>
@@ -11450,7 +11450,7 @@
         <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.17</v>
       </c>
       <c r="AK68">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="O69">
         <v>3.5</v>
       </c>
       <c r="P69">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q69">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R69">
         <v>2.21</v>
       </c>
       <c r="S69">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="T69">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U69">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="V69">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W69">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA69">
         <v>1.67</v>
       </c>
       <c r="AB69">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC69">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD69">
         <v>1.4</v>
       </c>
       <c r="AE69">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF69">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AG69">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.21</v>
+        <v>1.8</v>
       </c>
       <c r="AK69">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,19 +11728,19 @@
         <v>5.4</v>
       </c>
       <c r="Q70">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R70">
         <v>1.98</v>
       </c>
       <c r="S70">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T70">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="U70">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="V70">
         <v>1.31</v>
@@ -11749,19 +11749,19 @@
         <v>1.01</v>
       </c>
       <c r="X70">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z70">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA70">
         <v>2.17</v>
       </c>
       <c r="AB70">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC70">
         <v>3.95</v>
@@ -11773,10 +11773,10 @@
         <v>1.02</v>
       </c>
       <c r="AF70">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG70">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
         <v>2</v>
@@ -12211,13 +12211,13 @@
         <v>3.05</v>
       </c>
       <c r="O73">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P73">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q73">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="R73">
         <v>1.93</v>
@@ -12226,7 +12226,7 @@
         <v>1.49</v>
       </c>
       <c r="T73">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="U73">
         <v>3.32</v>
@@ -12241,25 +12241,25 @@
         <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z73">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AA73">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AB73">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC73">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD73">
         <v>1.19</v>
       </c>
       <c r="AE73">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF73">
         <v>1.96</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK73">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q74">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R74">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="S74">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T74">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="U74">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="V74">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="W74">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z74">
-        <v>6.1</v>
+        <v>6.65</v>
       </c>
       <c r="AA74">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB74">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AC74">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AD74">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AE74">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF74">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG74">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK74">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12712,13 +12712,13 @@
         <v>2.12</v>
       </c>
       <c r="S76">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T76">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="U76">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V76">
         <v>1.41</v>
@@ -12770,7 +12770,7 @@
         <v>1.24</v>
       </c>
       <c r="AK76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>2.55</v>
       </c>
       <c r="Q77">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="R77">
         <v>2.04</v>
@@ -12884,13 +12884,13 @@
         <v>2.86</v>
       </c>
       <c r="V77">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
         <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
         <v>1.27</v>
@@ -12917,7 +12917,7 @@
         <v>1.72</v>
       </c>
       <c r="AG77">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
         <v>1.32</v>
@@ -13026,28 +13026,28 @@
         <v>5</v>
       </c>
       <c r="O78">
-        <v>4.33</v>
+        <v>4.68</v>
       </c>
       <c r="P78">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q78">
         <v>5</v>
       </c>
       <c r="R78">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="S78">
         <v>1.2</v>
       </c>
       <c r="T78">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="U78">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="V78">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W78">
         <v>1.17</v>
@@ -13059,28 +13059,28 @@
         <v>1.08</v>
       </c>
       <c r="Z78">
-        <v>7</v>
+        <v>5.55</v>
       </c>
       <c r="AA78">
         <v>1.4</v>
       </c>
       <c r="AB78">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AC78">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AD78">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE78">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF78">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG78">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK78">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,19 +13195,19 @@
         <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="R79">
         <v>1.98</v>
       </c>
       <c r="S79">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T79">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="U79">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="V79">
         <v>1.36</v>
@@ -13222,13 +13222,13 @@
         <v>1.26</v>
       </c>
       <c r="Z79">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA79">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB79">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC79">
         <v>3.2</v>
@@ -13243,7 +13243,7 @@
         <v>1.7</v>
       </c>
       <c r="AG79">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK79">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13355,19 +13355,19 @@
         <v>3.34</v>
       </c>
       <c r="P80">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q80">
         <v>4.75</v>
       </c>
       <c r="R80">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S80">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T80">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U80">
         <v>2.75</v>
@@ -13385,7 +13385,7 @@
         <v>1.25</v>
       </c>
       <c r="Z80">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AA80">
         <v>1.85</v>
@@ -13397,13 +13397,13 @@
         <v>2.92</v>
       </c>
       <c r="AD80">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE80">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF80">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG80">
         <v>1.87</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O81">
         <v>2.62</v>
@@ -13527,22 +13527,22 @@
         <v>1.68</v>
       </c>
       <c r="S81">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="T81">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="U81">
         <v>4.2</v>
       </c>
       <c r="V81">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W81">
         <v>1.03</v>
       </c>
       <c r="X81">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y81">
         <v>1.69</v>
@@ -13551,13 +13551,13 @@
         <v>2.04</v>
       </c>
       <c r="AA81">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AB81">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC81">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="AD81">
         <v>1.04</v>
@@ -13566,10 +13566,10 @@
         <v>1.02</v>
       </c>
       <c r="AF81">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AG81">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,7 +13684,7 @@
         <v>3.9</v>
       </c>
       <c r="Q82">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="R82">
         <v>1.76</v>
@@ -13696,10 +13696,10 @@
         <v>2.1</v>
       </c>
       <c r="U82">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="V82">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W82">
         <v>1.03</v>
@@ -13708,10 +13708,10 @@
         <v>1.08</v>
       </c>
       <c r="Y82">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z82">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AA82">
         <v>2.88</v>
@@ -13729,10 +13729,10 @@
         <v>1.03</v>
       </c>
       <c r="AF82">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG82">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK82">
         <v>1.7</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O83">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P83">
         <v>3.4</v>
       </c>
       <c r="Q83">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R83">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="S83">
         <v>1.66</v>
@@ -13871,19 +13871,19 @@
         <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Z83">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AA83">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB83">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC83">
-        <v>6.21</v>
+        <v>6.1</v>
       </c>
       <c r="AD83">
         <v>1.06</v>
@@ -13892,7 +13892,7 @@
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AG83">
         <v>1.52</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK83">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,13 +14010,13 @@
         <v>3.03</v>
       </c>
       <c r="Q84">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R84">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="S84">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="T84">
         <v>2.18</v>
@@ -14028,22 +14028,22 @@
         <v>1.19</v>
       </c>
       <c r="W84">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X84">
         <v>1.08</v>
       </c>
       <c r="Y84">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Z84">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AA84">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="AB84">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC84">
         <v>5.3</v>
@@ -14058,7 +14058,7 @@
         <v>2.19</v>
       </c>
       <c r="AG84">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.32</v>
       </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14170,13 +14170,13 @@
         <v>3.3</v>
       </c>
       <c r="P85">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q85">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="R85">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S85">
         <v>1.36</v>
@@ -14185,7 +14185,7 @@
         <v>2.85</v>
       </c>
       <c r="U85">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="V85">
         <v>1.4</v>
@@ -14194,13 +14194,13 @@
         <v>1.05</v>
       </c>
       <c r="X85">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
         <v>1.23</v>
       </c>
       <c r="Z85">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="AA85">
         <v>1.95</v>
@@ -14209,16 +14209,16 @@
         <v>1.85</v>
       </c>
       <c r="AC85">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AD85">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE85">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF85">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AG85">
         <v>1.98</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>1.89</v>
       </c>
       <c r="Q86">
-        <v>4.42</v>
+        <v>3.68</v>
       </c>
       <c r="R86">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S86">
         <v>1.22</v>
       </c>
       <c r="T86">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U86">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="V86">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W86">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z86">
         <v>4.95</v>
       </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB86">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AC86">
         <v>2.16</v>
       </c>
       <c r="AD86">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE86">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF86">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG86">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.16</v>
       </c>
       <c r="AK86">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="P87">
-        <v>4.6</v>
+        <v>5.54</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB87">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O88">
+        <v>4.35</v>
+      </c>
+      <c r="P88">
         <v>5</v>
-      </c>
-      <c r="P88">
-        <v>5.05</v>
       </c>
       <c r="Q88">
         <v>1.85</v>
@@ -14668,16 +14668,16 @@
         <v>2.72</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T88">
         <v>4.4</v>
       </c>
       <c r="U88">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="V88">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W88">
         <v>1.19</v>
@@ -14695,13 +14695,13 @@
         <v>1.36</v>
       </c>
       <c r="AB88">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC88">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AD88">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE88">
         <v>1.27</v>
@@ -14710,7 +14710,7 @@
         <v>1.51</v>
       </c>
       <c r="AG88">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK88">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,22 +14816,22 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O89">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="Q89">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="R89">
         <v>2.06</v>
       </c>
       <c r="S89">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T89">
         <v>2.85</v>
@@ -14843,25 +14843,25 @@
         <v>1.4</v>
       </c>
       <c r="W89">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
         <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z89">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="AA89">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB89">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC89">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="AD89">
         <v>1.35</v>
@@ -14870,10 +14870,10 @@
         <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -15305,31 +15305,31 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="O92">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
-        <v>4.59</v>
+        <v>4.1</v>
       </c>
       <c r="Q92">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="R92">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="S92">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T92">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="U92">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V92">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W92">
         <v>1.05</v>
@@ -15338,28 +15338,28 @@
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z92">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA92">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB92">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC92">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AD92">
         <v>1.3</v>
       </c>
       <c r="AE92">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG92">
         <v>1.9</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
         <v>1.99</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="O94">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P94">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="Q94">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R94">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S94">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T94">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="U94">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="V94">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W94">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X94">
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z94">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA94">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB94">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC94">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD94">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE94">
         <v>1.04</v>
       </c>
       <c r="AF94">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG94">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK94">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>6.24</v>
       </c>
       <c r="Q95">
+        <v>2.28</v>
+      </c>
+      <c r="R95">
         <v>2.1</v>
       </c>
-      <c r="R95">
-        <v>2</v>
-      </c>
       <c r="S95">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="T95">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="U95">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V95">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W95">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X95">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y95">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Z95">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AA95">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AB95">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AC95">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="AD95">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE95">
         <v>1.01</v>
       </c>
       <c r="AF95">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AG95">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AK95">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O96">
         <v>3.25</v>
       </c>
       <c r="P96">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="O97">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P97">
-        <v>4.25</v>
+        <v>4.68</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16286,10 +16286,10 @@
         <v>2.1</v>
       </c>
       <c r="O98">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P98">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="Q98">
         <v>2.62</v>
@@ -16298,25 +16298,25 @@
         <v>2.04</v>
       </c>
       <c r="S98">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U98">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V98">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W98">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z98">
         <v>3.18</v>
@@ -16325,7 +16325,7 @@
         <v>2.03</v>
       </c>
       <c r="AB98">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC98">
         <v>3.3</v>
@@ -16337,10 +16337,10 @@
         <v>1.06</v>
       </c>
       <c r="AF98">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG98">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -17107,56 +17107,56 @@
         <v>1.45</v>
       </c>
       <c r="Q103">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="R103">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="S103">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T103">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="U103">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="V103">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W103">
+        <v>1.08</v>
+      </c>
+      <c r="X103">
+        <v>1.02</v>
+      </c>
+      <c r="Y103">
+        <v>1.18</v>
+      </c>
+      <c r="Z103">
+        <v>3.86</v>
+      </c>
+      <c r="AA103">
+        <v>1.66</v>
+      </c>
+      <c r="AB103">
+        <v>2.15</v>
+      </c>
+      <c r="AC103">
+        <v>2.89</v>
+      </c>
+      <c r="AD103">
+        <v>1.37</v>
+      </c>
+      <c r="AE103">
         <v>1.13</v>
       </c>
-      <c r="X103">
-        <v>1.01</v>
-      </c>
-      <c r="Y103">
-        <v>1.12</v>
-      </c>
-      <c r="Z103">
-        <v>4.7</v>
-      </c>
-      <c r="AA103">
-        <v>1.46</v>
-      </c>
-      <c r="AB103">
-        <v>2.38</v>
-      </c>
-      <c r="AC103">
-        <v>2.16</v>
-      </c>
-      <c r="AD103">
-        <v>1.62</v>
-      </c>
-      <c r="AE103">
-        <v>1.23</v>
-      </c>
       <c r="AF103">
+        <v>1.86</v>
+      </c>
+      <c r="AG103">
         <v>1.83</v>
       </c>
-      <c r="AG103">
-        <v>1.86</v>
-      </c>
       <c r="AH103" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK103">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17267,7 +17267,7 @@
         <v>2.7</v>
       </c>
       <c r="P104">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="O105">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P105">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="Q105">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="R105">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="S105">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T105">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="U105">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="V105">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W105">
         <v>1.05</v>
       </c>
       <c r="X105">
+        <v>1.01</v>
+      </c>
+      <c r="Y105">
+        <v>1.32</v>
+      </c>
+      <c r="Z105">
+        <v>2.88</v>
+      </c>
+      <c r="AA105">
+        <v>2.14</v>
+      </c>
+      <c r="AB105">
+        <v>1.65</v>
+      </c>
+      <c r="AC105">
+        <v>3.82</v>
+      </c>
+      <c r="AD105">
+        <v>1.18</v>
+      </c>
+      <c r="AE105">
         <v>1.02</v>
       </c>
-      <c r="Y105">
-        <v>1.35</v>
-      </c>
-      <c r="Z105">
-        <v>2.74</v>
-      </c>
-      <c r="AA105">
-        <v>2.23</v>
-      </c>
-      <c r="AB105">
-        <v>1.6</v>
-      </c>
-      <c r="AC105">
-        <v>4.05</v>
-      </c>
-      <c r="AD105">
-        <v>1.21</v>
-      </c>
-      <c r="AE105">
-        <v>1.01</v>
-      </c>
       <c r="AF105">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG105">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK105">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17590,16 +17590,16 @@
         <v>1.85</v>
       </c>
       <c r="O106">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P106">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q106">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R106">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="S106">
         <v>1.65</v>
@@ -17608,43 +17608,43 @@
         <v>2.17</v>
       </c>
       <c r="U106">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="V106">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W106">
         <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y106">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Z106">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AA106">
         <v>2.88</v>
       </c>
       <c r="AB106">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AC106">
-        <v>6.05</v>
+        <v>4.4</v>
       </c>
       <c r="AD106">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AE106">
         <v>1.02</v>
       </c>
       <c r="AF106">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG106">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.31</v>
       </c>
       <c r="AK106">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,28 +17750,28 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O107">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P107">
-        <v>4.8</v>
+        <v>5.45</v>
       </c>
       <c r="Q107">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="R107">
         <v>1.82</v>
       </c>
       <c r="S107">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="T107">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U107">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V107">
         <v>1.17</v>
@@ -17789,7 +17789,7 @@
         <v>2.16</v>
       </c>
       <c r="AA107">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AB107">
         <v>1.36</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK107">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,34 +17913,34 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O108">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P108">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
       <c r="Q108">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="R108">
         <v>1.94</v>
       </c>
       <c r="S108">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T108">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="U108">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="V108">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W108">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X108">
         <v>1.06</v>
@@ -17952,10 +17952,10 @@
         <v>2.44</v>
       </c>
       <c r="AA108">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AB108">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC108">
         <v>4.7</v>
@@ -17967,7 +17967,7 @@
         <v>1</v>
       </c>
       <c r="AF108">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AG108">
         <v>1.51</v>
@@ -17986,7 +17986,7 @@
         <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18079,61 +18079,61 @@
         <v>2.45</v>
       </c>
       <c r="O109">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P109">
         <v>2.88</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,55 +18248,55 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18405,13 +18405,13 @@
         <v>1.38</v>
       </c>
       <c r="O111">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="P111">
         <v>4.4</v>
       </c>
       <c r="Q111">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="R111">
         <v>2.85</v>
@@ -18420,13 +18420,13 @@
         <v>1.12</v>
       </c>
       <c r="T111">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="U111">
         <v>1.79</v>
       </c>
       <c r="V111">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="W111">
         <v>1.25</v>
@@ -18438,28 +18438,28 @@
         <v>1.04</v>
       </c>
       <c r="Z111">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA111">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AB111">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC111">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AD111">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AE111">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF111">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG111">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.14</v>
       </c>
       <c r="AK111">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="O112">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="P112">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q112">
         <v>2.63</v>
@@ -18580,19 +18580,19 @@
         <v>2.62</v>
       </c>
       <c r="S112">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T112">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="U112">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V112">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="W112">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X112">
         <v>1.01</v>
@@ -18607,10 +18607,10 @@
         <v>1.3</v>
       </c>
       <c r="AB112">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AC112">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD112">
         <v>2.08</v>
@@ -18619,7 +18619,7 @@
         <v>1.43</v>
       </c>
       <c r="AF112">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AG112">
         <v>2.8</v>
@@ -18638,7 +18638,7 @@
         <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O113">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P113">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -19060,13 +19060,13 @@
         <v>3.1</v>
       </c>
       <c r="P115">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q115">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="R115">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S115">
         <v>1.51</v>
@@ -19093,13 +19093,13 @@
         <v>2.46</v>
       </c>
       <c r="AA115">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AB115">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC115">
-        <v>4.72</v>
+        <v>4.55</v>
       </c>
       <c r="AD115">
         <v>1.13</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK115">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19389,10 +19389,10 @@
         <v>4.83</v>
       </c>
       <c r="Q117">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S117">
         <v>1.32</v>
@@ -19401,10 +19401,10 @@
         <v>2.92</v>
       </c>
       <c r="U117">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="V117">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W117">
         <v>1.09</v>
@@ -19416,28 +19416,28 @@
         <v>1.22</v>
       </c>
       <c r="Z117">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA117">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AB117">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AC117">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD117">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE117">
         <v>1.11</v>
       </c>
       <c r="AF117">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG117">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK117">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O120">
-        <v>3.98</v>
+        <v>4.22</v>
       </c>
       <c r="P120">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Q120">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="R120">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S120">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T120">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U120">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V120">
         <v>1.4</v>
       </c>
       <c r="W120">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X120">
         <v>1</v>
       </c>
       <c r="Y120">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z120">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AA120">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
         <v>1.9</v>
       </c>
       <c r="AC120">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AD120">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE120">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF120">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG120">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AK120">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20044,52 +20044,52 @@
         <v>2.2</v>
       </c>
       <c r="R121">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T121">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U121">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="V121">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W121">
+        <v>1.05</v>
+      </c>
+      <c r="X121">
+        <v>1.03</v>
+      </c>
+      <c r="Y121">
+        <v>1.27</v>
+      </c>
+      <c r="Z121">
+        <v>3.18</v>
+      </c>
+      <c r="AA121">
+        <v>1.99</v>
+      </c>
+      <c r="AB121">
+        <v>1.87</v>
+      </c>
+      <c r="AC121">
+        <v>3.3</v>
+      </c>
+      <c r="AD121">
+        <v>1.29</v>
+      </c>
+      <c r="AE121">
         <v>1.06</v>
       </c>
-      <c r="X121">
-        <v>1.01</v>
-      </c>
-      <c r="Y121">
-        <v>1.24</v>
-      </c>
-      <c r="Z121">
-        <v>3.38</v>
-      </c>
-      <c r="AA121">
-        <v>1.9</v>
-      </c>
-      <c r="AB121">
-        <v>1.85</v>
-      </c>
-      <c r="AC121">
-        <v>3.25</v>
-      </c>
-      <c r="AD121">
-        <v>1.33</v>
-      </c>
-      <c r="AE121">
-        <v>1.11</v>
-      </c>
       <c r="AF121">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG121">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AK121">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,55 +20195,55 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O122">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P122">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q122">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="R122">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S122">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T122">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="U122">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="V122">
         <v>1.41</v>
       </c>
       <c r="W122">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y122">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z122">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AA122">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB122">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC122">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD122">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE122">
         <v>1.07</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK122">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20684,80 +20684,80 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O125">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="P125">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q125">
-        <v>2.88</v>
+        <v>3.47</v>
       </c>
       <c r="R125">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="S125">
+        <v>1.58</v>
+      </c>
+      <c r="T125">
+        <v>2.27</v>
+      </c>
+      <c r="U125">
+        <v>3.6</v>
+      </c>
+      <c r="V125">
+        <v>1.22</v>
+      </c>
+      <c r="W125">
+        <v>1</v>
+      </c>
+      <c r="X125">
+        <v>1.07</v>
+      </c>
+      <c r="Y125">
+        <v>1.5</v>
+      </c>
+      <c r="Z125">
+        <v>2.28</v>
+      </c>
+      <c r="AA125">
+        <v>2.4</v>
+      </c>
+      <c r="AB125">
+        <v>1.53</v>
+      </c>
+      <c r="AC125">
+        <v>4.95</v>
+      </c>
+      <c r="AD125">
+        <v>1.11</v>
+      </c>
+      <c r="AE125">
+        <v>1.01</v>
+      </c>
+      <c r="AF125">
+        <v>2.14</v>
+      </c>
+      <c r="AG125">
+        <v>1.63</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
         <v>1.36</v>
       </c>
-      <c r="T125">
-        <v>2.84</v>
-      </c>
-      <c r="U125">
-        <v>2.73</v>
-      </c>
-      <c r="V125">
-        <v>1.39</v>
-      </c>
-      <c r="W125">
-        <v>1.05</v>
-      </c>
-      <c r="X125">
-        <v>1.01</v>
-      </c>
-      <c r="Y125">
-        <v>1.25</v>
-      </c>
-      <c r="Z125">
-        <v>3.6</v>
-      </c>
-      <c r="AA125">
-        <v>1.88</v>
-      </c>
-      <c r="AB125">
-        <v>1.87</v>
-      </c>
-      <c r="AC125">
-        <v>3.05</v>
-      </c>
-      <c r="AD125">
-        <v>1.28</v>
-      </c>
-      <c r="AE125">
-        <v>1.08</v>
-      </c>
-      <c r="AF125">
-        <v>1.69</v>
-      </c>
-      <c r="AG125">
-        <v>2.02</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.4</v>
-      </c>
       <c r="AK125">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20856,55 +20856,55 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="O127">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="P127">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q127">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R127">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="S127">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T127">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="U127">
         <v>2.85</v>
       </c>
       <c r="V127">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W127">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X127">
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z127">
         <v>3.12</v>
       </c>
       <c r="AA127">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB127">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC127">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AD127">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE127">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF127">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG127">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK127">
         <v>2.15</v>
@@ -21182,28 +21182,28 @@
         <v>3.29</v>
       </c>
       <c r="Q128">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R128">
         <v>2.1</v>
       </c>
       <c r="S128">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T128">
         <v>2.73</v>
       </c>
       <c r="U128">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="V128">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W128">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X128">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y128">
         <v>1.28</v>
@@ -21221,16 +21221,16 @@
         <v>3.44</v>
       </c>
       <c r="AD128">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE128">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF128">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG128">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>1.33</v>
       </c>
       <c r="AK128">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21345,22 +21345,22 @@
         <v>4.72</v>
       </c>
       <c r="Q129">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="R129">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S129">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T129">
         <v>3.28</v>
       </c>
       <c r="U129">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V129">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W129">
         <v>1.12</v>
@@ -21369,22 +21369,22 @@
         <v>1.03</v>
       </c>
       <c r="Y129">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z129">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA129">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AB129">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AC129">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD129">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE129">
         <v>1.12</v>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK129">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O132">
         <v>2.95</v>
       </c>
       <c r="P132">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q132">
-        <v>3.16</v>
+        <v>2.81</v>
       </c>
       <c r="R132">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S132">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T132">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="U132">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="V132">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W132">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X132">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="Z132">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AA132">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB132">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC132">
-        <v>4.7</v>
+        <v>3.86</v>
       </c>
       <c r="AD132">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE132">
         <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG132">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK132">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22160,10 +22160,10 @@
         <v>5.07</v>
       </c>
       <c r="Q134">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R134">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S134">
         <v>1.29</v>
@@ -22178,22 +22178,22 @@
         <v>1.44</v>
       </c>
       <c r="W134">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X134">
         <v>1.04</v>
       </c>
       <c r="Y134">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z134">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AA134">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB134">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC134">
         <v>2.74</v>
@@ -22205,7 +22205,7 @@
         <v>1.1</v>
       </c>
       <c r="AF134">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG134">
         <v>2</v>
@@ -22224,7 +22224,7 @@
         <v>1.14</v>
       </c>
       <c r="AK134">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="AL134">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P7">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>5.01</v>
+        <v>5.07</v>
       </c>
       <c r="R7">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S7">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="T7">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="U7">
         <v>3.34</v>
@@ -1480,19 +1480,19 @@
         <v>1.02</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z7">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AA7">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AB7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC7">
         <v>4</v>
@@ -1501,13 +1501,13 @@
         <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AG7">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
         <v>1.21</v>
@@ -1634,7 +1634,7 @@
         <v>2.89</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V8">
         <v>1.43</v>
@@ -1643,7 +1643,7 @@
         <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8">
         <v>1.22</v>
@@ -1661,7 +1661,7 @@
         <v>2.8</v>
       </c>
       <c r="AD8">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE8">
         <v>1.1</v>
@@ -1670,7 +1670,7 @@
         <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
         <v>1.83</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.7</v>
+        <v>3.48</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q9">
-        <v>2.31</v>
+        <v>5.02</v>
       </c>
       <c r="R9">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="S9">
         <v>1.5</v>
@@ -1800,19 +1800,19 @@
         <v>3.4</v>
       </c>
       <c r="V9">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
         <v>1.03</v>
       </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
       <c r="Y9">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z9">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="AA9">
         <v>2.35</v>
@@ -1821,19 +1821,19 @@
         <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF9">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AG9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AK9">
-        <v>2.06</v>
+        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.75</v>
+        <v>1.72</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="P10">
-        <v>1.95</v>
+        <v>4.3</v>
       </c>
       <c r="Q10">
-        <v>4.85</v>
+        <v>2.31</v>
       </c>
       <c r="R10">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="S10">
         <v>1.51</v>
       </c>
       <c r="T10">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="U10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V10">
         <v>1.27</v>
@@ -1969,34 +1969,34 @@
         <v>1.01</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z10">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AA10">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AB10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC10">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AG10">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>1.16</v>
+        <v>2.12</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="Q11">
         <v>2.43</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
         <v>1.39</v>
@@ -2123,43 +2123,43 @@
         <v>2.8</v>
       </c>
       <c r="U11">
-        <v>2.55</v>
+        <v>2.96</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA11">
         <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC11">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG11">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2274,55 +2274,55 @@
         <v>3.38</v>
       </c>
       <c r="Q12">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R12">
         <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AB12">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AC12">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AD12">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
         <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
         <v>1.89</v>
@@ -2440,46 +2440,46 @@
         <v>2.26</v>
       </c>
       <c r="R13">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T13">
         <v>3.82</v>
       </c>
       <c r="U13">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V13">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W13">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z13">
-        <v>5.2</v>
+        <v>6.57</v>
       </c>
       <c r="AA13">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AB13">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="AC13">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AD13">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE13">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AF13">
         <v>1.4</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3252,10 +3252,10 @@
         <v>3.34</v>
       </c>
       <c r="Q18">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="R18">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S18">
         <v>1.2</v>
@@ -3264,40 +3264,40 @@
         <v>4</v>
       </c>
       <c r="U18">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V18">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5.35</v>
+        <v>5.99</v>
       </c>
       <c r="AA18">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AB18">
-        <v>2.56</v>
+        <v>2.89</v>
       </c>
       <c r="AC18">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AD18">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE18">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG18">
         <v>2.7</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="O19">
-        <v>3.98</v>
+        <v>3.47</v>
       </c>
       <c r="P19">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="Q19">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R19">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T19">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="U19">
         <v>2.17</v>
       </c>
       <c r="V19">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="W19">
         <v>1.13</v>
@@ -3439,31 +3439,31 @@
         <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4.95</v>
+        <v>7.29</v>
       </c>
       <c r="AA19">
+        <v>1.56</v>
+      </c>
+      <c r="AB19">
+        <v>2.54</v>
+      </c>
+      <c r="AC19">
+        <v>2.31</v>
+      </c>
+      <c r="AD19">
+        <v>1.63</v>
+      </c>
+      <c r="AE19">
+        <v>1.21</v>
+      </c>
+      <c r="AF19">
         <v>1.46</v>
       </c>
-      <c r="AB19">
-        <v>2.38</v>
-      </c>
-      <c r="AC19">
-        <v>2.27</v>
-      </c>
-      <c r="AD19">
-        <v>1.55</v>
-      </c>
-      <c r="AE19">
-        <v>1.22</v>
-      </c>
-      <c r="AF19">
-        <v>1.44</v>
-      </c>
       <c r="AG19">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>3.38</v>
       </c>
       <c r="Q20">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="R20">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S20">
         <v>1.21</v>
@@ -3590,43 +3590,43 @@
         <v>3.68</v>
       </c>
       <c r="U20">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="V20">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W20">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>5.6</v>
+        <v>5.83</v>
       </c>
       <c r="AA20">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB20">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AC20">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AD20">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE20">
         <v>1.26</v>
       </c>
       <c r="AF20">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG20">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="O52">
-        <v>4.85</v>
+        <v>3.91</v>
       </c>
       <c r="P52">
-        <v>1.32</v>
+        <v>3.93</v>
       </c>
       <c r="Q52">
-        <v>5.95</v>
+        <v>2.24</v>
       </c>
       <c r="R52">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="S52">
+        <v>1.28</v>
+      </c>
+      <c r="T52">
+        <v>3.34</v>
+      </c>
+      <c r="U52">
+        <v>2.36</v>
+      </c>
+      <c r="V52">
+        <v>1.56</v>
+      </c>
+      <c r="W52">
+        <v>1.09</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
         <v>1.18</v>
       </c>
-      <c r="T52">
-        <v>4.1</v>
-      </c>
-      <c r="U52">
-        <v>1.98</v>
-      </c>
-      <c r="V52">
-        <v>1.77</v>
-      </c>
-      <c r="W52">
-        <v>1.18</v>
-      </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.06</v>
-      </c>
       <c r="Z52">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA52">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AB52">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="AC52">
-        <v>1.94</v>
+        <v>2.47</v>
       </c>
       <c r="AD52">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE52">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF52">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG52">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="O53">
-        <v>3.91</v>
+        <v>4.85</v>
       </c>
       <c r="P53">
-        <v>3.93</v>
+        <v>1.32</v>
       </c>
       <c r="Q53">
-        <v>2.24</v>
+        <v>5.95</v>
       </c>
       <c r="R53">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T53">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="U53">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="V53">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="W53">
+        <v>1.18</v>
+      </c>
+      <c r="X53">
+        <v>1.01</v>
+      </c>
+      <c r="Y53">
+        <v>1.06</v>
+      </c>
+      <c r="Z53">
+        <v>6.2</v>
+      </c>
+      <c r="AA53">
+        <v>1.32</v>
+      </c>
+      <c r="AB53">
+        <v>2.89</v>
+      </c>
+      <c r="AC53">
+        <v>1.94</v>
+      </c>
+      <c r="AD53">
+        <v>1.88</v>
+      </c>
+      <c r="AE53">
+        <v>1.32</v>
+      </c>
+      <c r="AF53">
+        <v>1.53</v>
+      </c>
+      <c r="AG53">
+        <v>2.35</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.16</v>
+      </c>
+      <c r="AK53">
         <v>1.09</v>
-      </c>
-      <c r="X53">
-        <v>1.03</v>
-      </c>
-      <c r="Y53">
-        <v>1.18</v>
-      </c>
-      <c r="Z53">
-        <v>4.6</v>
-      </c>
-      <c r="AA53">
-        <v>1.6</v>
-      </c>
-      <c r="AB53">
-        <v>2.25</v>
-      </c>
-      <c r="AC53">
-        <v>2.47</v>
-      </c>
-      <c r="AD53">
-        <v>1.55</v>
-      </c>
-      <c r="AE53">
-        <v>1.22</v>
-      </c>
-      <c r="AF53">
-        <v>1.54</v>
-      </c>
-      <c r="AG53">
-        <v>2.3</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.19</v>
-      </c>
-      <c r="AK53">
-        <v>2.08</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O83">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="P83">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="Q83">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="R83">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="S83">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="T83">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U83">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="V83">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X83">
         <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z83">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AA83">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AB83">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC83">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="AD83">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AG83">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK83">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O84">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="P84">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="Q84">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="R84">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="S84">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="T84">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U84">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="V84">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
         <v>1.08</v>
       </c>
       <c r="Y84">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z84">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AA84">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AB84">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC84">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="AD84">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="AG84">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK84">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -16772,22 +16772,22 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="O101">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P101">
         <v>2.88</v>
       </c>
       <c r="Q101">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="R101">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="S101">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T101">
         <v>2.56</v>
@@ -16796,7 +16796,7 @@
         <v>2.95</v>
       </c>
       <c r="V101">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W101">
         <v>1.05</v>
@@ -16808,16 +16808,16 @@
         <v>1.29</v>
       </c>
       <c r="Z101">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="AA101">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB101">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC101">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD101">
         <v>1.24</v>
@@ -16829,7 +16829,7 @@
         <v>1.78</v>
       </c>
       <c r="AG101">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>2.29</v>
+      </c>
+      <c r="R109">
+        <v>2.16</v>
+      </c>
+      <c r="S109">
+        <v>1.4</v>
+      </c>
+      <c r="T109">
+        <v>2.75</v>
+      </c>
+      <c r="U109">
         <v>3</v>
       </c>
-      <c r="P109">
-        <v>2.88</v>
-      </c>
-      <c r="Q109">
-        <v>3.1</v>
-      </c>
-      <c r="R109">
+      <c r="V109">
+        <v>1.33</v>
+      </c>
+      <c r="W109">
+        <v>1.05</v>
+      </c>
+      <c r="X109">
+        <v>1.03</v>
+      </c>
+      <c r="Y109">
+        <v>1.32</v>
+      </c>
+      <c r="Z109">
+        <v>3</v>
+      </c>
+      <c r="AA109">
+        <v>2.2</v>
+      </c>
+      <c r="AB109">
+        <v>1.65</v>
+      </c>
+      <c r="AC109">
+        <v>3.83</v>
+      </c>
+      <c r="AD109">
+        <v>1.25</v>
+      </c>
+      <c r="AE109">
+        <v>1.05</v>
+      </c>
+      <c r="AF109">
         <v>1.95</v>
       </c>
-      <c r="S109">
-        <v>1.51</v>
-      </c>
-      <c r="T109">
-        <v>2.36</v>
-      </c>
-      <c r="U109">
-        <v>3.35</v>
-      </c>
-      <c r="V109">
-        <v>1.27</v>
-      </c>
-      <c r="W109">
-        <v>1.01</v>
-      </c>
-      <c r="X109">
-        <v>1.05</v>
-      </c>
-      <c r="Y109">
-        <v>1.4</v>
-      </c>
-      <c r="Z109">
-        <v>2.56</v>
-      </c>
-      <c r="AA109">
-        <v>2.38</v>
-      </c>
-      <c r="AB109">
-        <v>1.55</v>
-      </c>
-      <c r="AC109">
-        <v>4.33</v>
-      </c>
-      <c r="AD109">
-        <v>1.14</v>
-      </c>
-      <c r="AE109">
-        <v>1.01</v>
-      </c>
-      <c r="AF109">
-        <v>1.97</v>
-      </c>
       <c r="AG109">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK109">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q110">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="R110">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="S110">
+        <v>1.51</v>
+      </c>
+      <c r="T110">
+        <v>2.36</v>
+      </c>
+      <c r="U110">
+        <v>3.35</v>
+      </c>
+      <c r="V110">
+        <v>1.27</v>
+      </c>
+      <c r="W110">
+        <v>1.01</v>
+      </c>
+      <c r="X110">
+        <v>1.05</v>
+      </c>
+      <c r="Y110">
         <v>1.4</v>
       </c>
-      <c r="T110">
-        <v>2.75</v>
-      </c>
-      <c r="U110">
-        <v>3</v>
-      </c>
-      <c r="V110">
-        <v>1.33</v>
-      </c>
-      <c r="W110">
-        <v>1.05</v>
-      </c>
-      <c r="X110">
-        <v>1.03</v>
-      </c>
-      <c r="Y110">
-        <v>1.32</v>
-      </c>
       <c r="Z110">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="AA110">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AB110">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC110">
-        <v>3.83</v>
+        <v>4.33</v>
       </c>
       <c r="AD110">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF110">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG110">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK110">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O124">
         <v>3.3</v>
@@ -20533,13 +20533,13 @@
         <v>3.93</v>
       </c>
       <c r="R124">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S124">
         <v>1.44</v>
       </c>
       <c r="T124">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U124">
         <v>3.05</v>
@@ -20548,7 +20548,7 @@
         <v>1.32</v>
       </c>
       <c r="W124">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X124">
         <v>1.01</v>
@@ -20557,7 +20557,7 @@
         <v>1.3</v>
       </c>
       <c r="Z124">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA124">
         <v>2.1</v>
@@ -20566,10 +20566,10 @@
         <v>1.7</v>
       </c>
       <c r="AC124">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD124">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE124">
         <v>1.03</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK124">
         <v>1.33</v>
@@ -21825,19 +21825,19 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O132">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P132">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="Q132">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="R132">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S132">
         <v>1.43</v>
@@ -21870,7 +21870,7 @@
         <v>1.65</v>
       </c>
       <c r="AC132">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="AD132">
         <v>1.18</v>
@@ -21882,7 +21882,7 @@
         <v>1.86</v>
       </c>
       <c r="AG132">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21988,16 +21988,16 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="O133">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P133">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="Q133">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="R133">
         <v>2.06</v>
@@ -22006,16 +22006,16 @@
         <v>1.37</v>
       </c>
       <c r="T133">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U133">
         <v>2.84</v>
       </c>
       <c r="V133">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W133">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X133">
         <v>1.01</v>
@@ -22024,28 +22024,28 @@
         <v>1.25</v>
       </c>
       <c r="Z133">
-        <v>3.51</v>
+        <v>3.28</v>
       </c>
       <c r="AA133">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB133">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC133">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD133">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE133">
         <v>1.11</v>
       </c>
       <c r="AF133">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG133">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="O18">
-        <v>3.92</v>
+        <v>3.47</v>
       </c>
       <c r="P18">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="Q18">
+        <v>2.34</v>
+      </c>
+      <c r="R18">
         <v>2.42</v>
       </c>
-      <c r="R18">
-        <v>2.63</v>
-      </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U18">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="V18">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>5.99</v>
+        <v>7.29</v>
       </c>
       <c r="AA18">
+        <v>1.56</v>
+      </c>
+      <c r="AB18">
+        <v>2.54</v>
+      </c>
+      <c r="AC18">
+        <v>2.31</v>
+      </c>
+      <c r="AD18">
+        <v>1.63</v>
+      </c>
+      <c r="AE18">
+        <v>1.21</v>
+      </c>
+      <c r="AF18">
         <v>1.46</v>
       </c>
-      <c r="AB18">
-        <v>2.89</v>
-      </c>
-      <c r="AC18">
-        <v>2.09</v>
-      </c>
-      <c r="AD18">
-        <v>1.76</v>
-      </c>
-      <c r="AE18">
+      <c r="AG18">
+        <v>2.53</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.29</v>
       </c>
-      <c r="AF18">
-        <v>1.36</v>
-      </c>
-      <c r="AG18">
-        <v>2.7</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.22</v>
-      </c>
       <c r="AK18">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="O19">
-        <v>3.47</v>
+        <v>3.92</v>
       </c>
       <c r="P19">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="Q19">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="R19">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="S19">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T19">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>7.29</v>
+        <v>5.99</v>
       </c>
       <c r="AA19">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AB19">
-        <v>2.54</v>
+        <v>2.89</v>
       </c>
       <c r="AC19">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="AD19">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AE19">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AF19">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AG19">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -6343,34 +6343,34 @@
         <v>1.65</v>
       </c>
       <c r="O37">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="Q37">
         <v>2.21</v>
       </c>
       <c r="R37">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T37">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="U37">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W37">
         <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
         <v>1.23</v>
@@ -6379,10 +6379,10 @@
         <v>3.74</v>
       </c>
       <c r="AA37">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC37">
         <v>2.86</v>
@@ -6391,13 +6391,13 @@
         <v>1.37</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -7647,40 +7647,40 @@
         <v>2.75</v>
       </c>
       <c r="O45">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="P45">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="Q45">
         <v>3.72</v>
       </c>
       <c r="R45">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S45">
         <v>1.46</v>
       </c>
       <c r="T45">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U45">
         <v>2.99</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z45">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="AA45">
         <v>2.08</v>
@@ -7689,7 +7689,7 @@
         <v>1.71</v>
       </c>
       <c r="AC45">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD45">
         <v>1.23</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="O52">
-        <v>3.91</v>
+        <v>4.85</v>
       </c>
       <c r="P52">
-        <v>3.93</v>
+        <v>1.32</v>
       </c>
       <c r="Q52">
-        <v>2.24</v>
+        <v>5.95</v>
       </c>
       <c r="R52">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T52">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="U52">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="V52">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="W52">
+        <v>1.18</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.06</v>
+      </c>
+      <c r="Z52">
+        <v>6.2</v>
+      </c>
+      <c r="AA52">
+        <v>1.32</v>
+      </c>
+      <c r="AB52">
+        <v>2.89</v>
+      </c>
+      <c r="AC52">
+        <v>1.94</v>
+      </c>
+      <c r="AD52">
+        <v>1.88</v>
+      </c>
+      <c r="AE52">
+        <v>1.32</v>
+      </c>
+      <c r="AF52">
+        <v>1.53</v>
+      </c>
+      <c r="AG52">
+        <v>2.35</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.16</v>
+      </c>
+      <c r="AK52">
         <v>1.09</v>
-      </c>
-      <c r="X52">
-        <v>1.03</v>
-      </c>
-      <c r="Y52">
-        <v>1.18</v>
-      </c>
-      <c r="Z52">
-        <v>4.6</v>
-      </c>
-      <c r="AA52">
-        <v>1.6</v>
-      </c>
-      <c r="AB52">
-        <v>2.25</v>
-      </c>
-      <c r="AC52">
-        <v>2.47</v>
-      </c>
-      <c r="AD52">
-        <v>1.55</v>
-      </c>
-      <c r="AE52">
-        <v>1.22</v>
-      </c>
-      <c r="AF52">
-        <v>1.54</v>
-      </c>
-      <c r="AG52">
-        <v>2.3</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.19</v>
-      </c>
-      <c r="AK52">
-        <v>2.08</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="O53">
-        <v>4.85</v>
+        <v>3.91</v>
       </c>
       <c r="P53">
-        <v>1.32</v>
+        <v>3.93</v>
       </c>
       <c r="Q53">
-        <v>5.95</v>
+        <v>2.24</v>
       </c>
       <c r="R53">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="S53">
+        <v>1.28</v>
+      </c>
+      <c r="T53">
+        <v>3.34</v>
+      </c>
+      <c r="U53">
+        <v>2.36</v>
+      </c>
+      <c r="V53">
+        <v>1.56</v>
+      </c>
+      <c r="W53">
+        <v>1.09</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
         <v>1.18</v>
       </c>
-      <c r="T53">
-        <v>4.1</v>
-      </c>
-      <c r="U53">
-        <v>1.98</v>
-      </c>
-      <c r="V53">
-        <v>1.77</v>
-      </c>
-      <c r="W53">
-        <v>1.18</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.06</v>
-      </c>
       <c r="Z53">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA53">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AB53">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="AC53">
-        <v>1.94</v>
+        <v>2.47</v>
       </c>
       <c r="AD53">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE53">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF53">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG53">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK53">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="O57">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="Q57">
-        <v>2.52</v>
+        <v>3.56</v>
       </c>
       <c r="R57">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="S57">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>5</v>
+        <v>3.82</v>
       </c>
       <c r="U57">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="V57">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="W57">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z57">
-        <v>8.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA57">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AB57">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="AC57">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AD57">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AE57">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AF57">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AG57">
-        <v>3.42</v>
+        <v>2.77</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.2</v>
+        <v>2.13</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="P58">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="Q58">
-        <v>3.56</v>
+        <v>2.52</v>
       </c>
       <c r="R58">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T58">
-        <v>3.82</v>
+        <v>5</v>
       </c>
       <c r="U58">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="V58">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="W58">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z58">
-        <v>5.45</v>
+        <v>8.5</v>
       </c>
       <c r="AA58">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AB58">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="AC58">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AD58">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AE58">
+        <v>1.42</v>
+      </c>
+      <c r="AF58">
         <v>1.27</v>
       </c>
-      <c r="AF58">
-        <v>1.36</v>
-      </c>
       <c r="AG58">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -12223,16 +12223,16 @@
         <v>1.93</v>
       </c>
       <c r="S73">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T73">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="U73">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V73">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W73">
         <v>1.03</v>
@@ -12241,31 +12241,31 @@
         <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z73">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA73">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AB73">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC73">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="AD73">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE73">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AG73">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK73">
         <v>1.31</v>
@@ -13349,19 +13349,19 @@
         </is>
       </c>
       <c r="N80">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O80">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
         <v>1.61</v>
       </c>
       <c r="Q80">
-        <v>4.75</v>
+        <v>5.38</v>
       </c>
       <c r="R80">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S80">
         <v>1.36</v>
@@ -13370,7 +13370,7 @@
         <v>2.85</v>
       </c>
       <c r="U80">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V80">
         <v>1.41</v>
@@ -13382,31 +13382,31 @@
         <v>1</v>
       </c>
       <c r="Y80">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z80">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AA80">
         <v>1.85</v>
       </c>
       <c r="AB80">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC80">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="AD80">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE80">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG80">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="O97">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P97">
-        <v>4.68</v>
+        <v>4.62</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O98">
         <v>3.32</v>
@@ -16292,7 +16292,7 @@
         <v>3.08</v>
       </c>
       <c r="Q98">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R98">
         <v>2.04</v>
@@ -16304,7 +16304,7 @@
         <v>2.88</v>
       </c>
       <c r="U98">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V98">
         <v>1.37</v>
@@ -16322,10 +16322,10 @@
         <v>3.18</v>
       </c>
       <c r="AA98">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB98">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC98">
         <v>3.3</v>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK98">
         <v>1.7</v>
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="R109">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S109">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T109">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U109">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V109">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W109">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X109">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z109">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA109">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB109">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC109">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="AD109">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE109">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF109">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG109">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK109">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O110">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="P110">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Q110">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R110">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="S110">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="T110">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="U110">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="V110">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W110">
         <v>1.01</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y110">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z110">
+        <v>2.35</v>
+      </c>
+      <c r="AA110">
         <v>2.56</v>
       </c>
-      <c r="AA110">
-        <v>2.38</v>
-      </c>
       <c r="AB110">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AC110">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AD110">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE110">
         <v>1.01</v>
       </c>
       <c r="AF110">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG110">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.4</v>
       </c>
       <c r="AK110">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19869,19 +19869,19 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O120">
-        <v>4.22</v>
+        <v>3.98</v>
       </c>
       <c r="P120">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="Q120">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R120">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S120">
         <v>1.35</v>
@@ -19902,16 +19902,16 @@
         <v>1</v>
       </c>
       <c r="Y120">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z120">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA120">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB120">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC120">
         <v>3.12</v>
@@ -19942,7 +19942,7 @@
         <v>1.23</v>
       </c>
       <c r="AK120">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,7 +20041,7 @@
         <v>5.14</v>
       </c>
       <c r="Q121">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="R121">
         <v>2.16</v>
@@ -20071,10 +20071,10 @@
         <v>3.18</v>
       </c>
       <c r="AA121">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AB121">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC121">
         <v>3.3</v>
@@ -20086,7 +20086,7 @@
         <v>1.06</v>
       </c>
       <c r="AF121">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG121">
         <v>1.79</v>
@@ -20105,7 +20105,7 @@
         <v>1.27</v>
       </c>
       <c r="AK121">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,10 +20195,10 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="O122">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P122">
         <v>2.45</v>
@@ -20234,10 +20234,10 @@
         <v>3.38</v>
       </c>
       <c r="AA122">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB122">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC122">
         <v>3.05</v>
@@ -20684,25 +20684,25 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O125">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P125">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q125">
-        <v>3.47</v>
+        <v>3.72</v>
       </c>
       <c r="R125">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="S125">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T125">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="U125">
         <v>3.6</v>
@@ -20711,34 +20711,34 @@
         <v>1.22</v>
       </c>
       <c r="W125">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X125">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y125">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z125">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AA125">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB125">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC125">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AD125">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE125">
         <v>1.01</v>
       </c>
       <c r="AF125">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG125">
         <v>1.63</v>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK125">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20856,55 +20856,55 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="R126">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S126">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T126">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U126">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="V126">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W126">
+        <v>1.05</v>
+      </c>
+      <c r="X126">
         <v>1.03</v>
       </c>
-      <c r="X126">
-        <v>1.05</v>
-      </c>
       <c r="Y126">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z126">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AA126">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB126">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC126">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="AD126">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE126">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF126">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG126">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK126">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,16 +21010,16 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="O127">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="P127">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q127">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R127">
         <v>2.07</v>
@@ -21043,16 +21043,16 @@
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z127">
         <v>3.12</v>
       </c>
       <c r="AA127">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB127">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC127">
         <v>3.24</v>
@@ -21083,7 +21083,7 @@
         <v>1.29</v>
       </c>
       <c r="AK127">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21182,10 +21182,10 @@
         <v>3.29</v>
       </c>
       <c r="Q128">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="R128">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S128">
         <v>1.4</v>
@@ -21194,7 +21194,7 @@
         <v>2.73</v>
       </c>
       <c r="U128">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V128">
         <v>1.33</v>
@@ -21206,16 +21206,16 @@
         <v>1</v>
       </c>
       <c r="Y128">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z128">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AA128">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB128">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC128">
         <v>3.44</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="O18">
-        <v>3.47</v>
+        <v>3.92</v>
       </c>
       <c r="P18">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="Q18">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="R18">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="S18">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="V18">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>7.29</v>
+        <v>5.99</v>
       </c>
       <c r="AA18">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AB18">
-        <v>2.54</v>
+        <v>2.89</v>
       </c>
       <c r="AC18">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="AD18">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AG18">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="O19">
-        <v>3.92</v>
+        <v>3.47</v>
       </c>
       <c r="P19">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="Q19">
+        <v>2.34</v>
+      </c>
+      <c r="R19">
         <v>2.42</v>
       </c>
-      <c r="R19">
-        <v>2.63</v>
-      </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U19">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="V19">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>5.99</v>
+        <v>7.29</v>
       </c>
       <c r="AA19">
+        <v>1.56</v>
+      </c>
+      <c r="AB19">
+        <v>2.54</v>
+      </c>
+      <c r="AC19">
+        <v>2.31</v>
+      </c>
+      <c r="AD19">
+        <v>1.63</v>
+      </c>
+      <c r="AE19">
+        <v>1.21</v>
+      </c>
+      <c r="AF19">
         <v>1.46</v>
       </c>
-      <c r="AB19">
-        <v>2.89</v>
-      </c>
-      <c r="AC19">
-        <v>2.09</v>
-      </c>
-      <c r="AD19">
-        <v>1.76</v>
-      </c>
-      <c r="AE19">
+      <c r="AG19">
+        <v>2.53</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.29</v>
       </c>
-      <c r="AF19">
-        <v>1.36</v>
-      </c>
-      <c r="AG19">
-        <v>2.7</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.22</v>
-      </c>
       <c r="AK19">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="O52">
-        <v>4.85</v>
+        <v>3.91</v>
       </c>
       <c r="P52">
-        <v>1.32</v>
+        <v>3.93</v>
       </c>
       <c r="Q52">
-        <v>5.95</v>
+        <v>2.24</v>
       </c>
       <c r="R52">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="S52">
+        <v>1.28</v>
+      </c>
+      <c r="T52">
+        <v>3.34</v>
+      </c>
+      <c r="U52">
+        <v>2.36</v>
+      </c>
+      <c r="V52">
+        <v>1.56</v>
+      </c>
+      <c r="W52">
+        <v>1.09</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
         <v>1.18</v>
       </c>
-      <c r="T52">
-        <v>4.1</v>
-      </c>
-      <c r="U52">
-        <v>1.98</v>
-      </c>
-      <c r="V52">
-        <v>1.77</v>
-      </c>
-      <c r="W52">
-        <v>1.18</v>
-      </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.06</v>
-      </c>
       <c r="Z52">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA52">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AB52">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="AC52">
-        <v>1.94</v>
+        <v>2.47</v>
       </c>
       <c r="AD52">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE52">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF52">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG52">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="O53">
-        <v>3.91</v>
+        <v>4.85</v>
       </c>
       <c r="P53">
-        <v>3.93</v>
+        <v>1.32</v>
       </c>
       <c r="Q53">
-        <v>2.24</v>
+        <v>5.95</v>
       </c>
       <c r="R53">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T53">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="U53">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="V53">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="W53">
+        <v>1.18</v>
+      </c>
+      <c r="X53">
+        <v>1.01</v>
+      </c>
+      <c r="Y53">
+        <v>1.06</v>
+      </c>
+      <c r="Z53">
+        <v>6.2</v>
+      </c>
+      <c r="AA53">
+        <v>1.32</v>
+      </c>
+      <c r="AB53">
+        <v>2.89</v>
+      </c>
+      <c r="AC53">
+        <v>1.94</v>
+      </c>
+      <c r="AD53">
+        <v>1.88</v>
+      </c>
+      <c r="AE53">
+        <v>1.32</v>
+      </c>
+      <c r="AF53">
+        <v>1.53</v>
+      </c>
+      <c r="AG53">
+        <v>2.35</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.16</v>
+      </c>
+      <c r="AK53">
         <v>1.09</v>
-      </c>
-      <c r="X53">
-        <v>1.03</v>
-      </c>
-      <c r="Y53">
-        <v>1.18</v>
-      </c>
-      <c r="Z53">
-        <v>4.6</v>
-      </c>
-      <c r="AA53">
-        <v>1.6</v>
-      </c>
-      <c r="AB53">
-        <v>2.25</v>
-      </c>
-      <c r="AC53">
-        <v>2.47</v>
-      </c>
-      <c r="AD53">
-        <v>1.55</v>
-      </c>
-      <c r="AE53">
-        <v>1.22</v>
-      </c>
-      <c r="AF53">
-        <v>1.54</v>
-      </c>
-      <c r="AG53">
-        <v>2.3</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.19</v>
-      </c>
-      <c r="AK53">
-        <v>2.08</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>1.91</v>
       </c>
       <c r="Q62">
-        <v>3.87</v>
+        <v>3.3</v>
       </c>
       <c r="R62">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="S62">
         <v>1.31</v>
@@ -10436,10 +10436,10 @@
         <v>2.97</v>
       </c>
       <c r="U62">
-        <v>2.53</v>
+        <v>2.23</v>
       </c>
       <c r="V62">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W62">
         <v>1.06</v>
@@ -10451,28 +10451,28 @@
         <v>1.19</v>
       </c>
       <c r="Z62">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AA62">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AB62">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AC62">
-        <v>2.78</v>
+        <v>2.43</v>
       </c>
       <c r="AD62">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AE62">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF62">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AG62">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AK62">
         <v>1.26</v>
@@ -11399,13 +11399,13 @@
         <v>3.8</v>
       </c>
       <c r="P68">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q68">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R68">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="S68">
         <v>1.24</v>
@@ -11414,13 +11414,13 @@
         <v>3.34</v>
       </c>
       <c r="U68">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V68">
         <v>1.56</v>
       </c>
       <c r="W68">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11432,10 +11432,10 @@
         <v>4.5</v>
       </c>
       <c r="AA68">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AB68">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AC68">
         <v>2.28</v>
@@ -11447,10 +11447,10 @@
         <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG68">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.17</v>
       </c>
       <c r="AK68">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="O97">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="P97">
-        <v>4.62</v>
+        <v>4.36</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16283,19 +16283,19 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="O98">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P98">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="Q98">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="R98">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S98">
         <v>1.36</v>
@@ -16304,43 +16304,43 @@
         <v>2.88</v>
       </c>
       <c r="U98">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="V98">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W98">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X98">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z98">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AA98">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB98">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC98">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD98">
         <v>1.25</v>
       </c>
       <c r="AE98">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF98">
         <v>1.76</v>
       </c>
       <c r="AG98">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="O107">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P107">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="Q107">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="R107">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="S107">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="T107">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="U107">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="V107">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="W107">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X107">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y107">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z107">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="AA107">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="AB107">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AC107">
-        <v>5.95</v>
+        <v>4.7</v>
       </c>
       <c r="AD107">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE107">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF107">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="AG107">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK107">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,80 +17913,80 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="O108">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P108">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="Q108">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="R108">
+        <v>1.82</v>
+      </c>
+      <c r="S108">
+        <v>1.63</v>
+      </c>
+      <c r="T108">
+        <v>2.13</v>
+      </c>
+      <c r="U108">
+        <v>3.75</v>
+      </c>
+      <c r="V108">
+        <v>1.17</v>
+      </c>
+      <c r="W108">
+        <v>1.03</v>
+      </c>
+      <c r="X108">
+        <v>1.08</v>
+      </c>
+      <c r="Y108">
+        <v>1.62</v>
+      </c>
+      <c r="Z108">
+        <v>2.16</v>
+      </c>
+      <c r="AA108">
+        <v>2.83</v>
+      </c>
+      <c r="AB108">
+        <v>1.36</v>
+      </c>
+      <c r="AC108">
+        <v>5.95</v>
+      </c>
+      <c r="AD108">
+        <v>1.07</v>
+      </c>
+      <c r="AE108">
+        <v>1.03</v>
+      </c>
+      <c r="AF108">
+        <v>2.6</v>
+      </c>
+      <c r="AG108">
+        <v>1.43</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ108">
+        <v>1.28</v>
+      </c>
+      <c r="AK108">
         <v>1.94</v>
-      </c>
-      <c r="S108">
-        <v>1.53</v>
-      </c>
-      <c r="T108">
-        <v>2.33</v>
-      </c>
-      <c r="U108">
-        <v>3.42</v>
-      </c>
-      <c r="V108">
-        <v>1.23</v>
-      </c>
-      <c r="W108">
-        <v>1.01</v>
-      </c>
-      <c r="X108">
-        <v>1.06</v>
-      </c>
-      <c r="Y108">
-        <v>1.49</v>
-      </c>
-      <c r="Z108">
-        <v>2.44</v>
-      </c>
-      <c r="AA108">
-        <v>2.42</v>
-      </c>
-      <c r="AB108">
-        <v>1.47</v>
-      </c>
-      <c r="AC108">
-        <v>4.7</v>
-      </c>
-      <c r="AD108">
-        <v>1.12</v>
-      </c>
-      <c r="AE108">
-        <v>1</v>
-      </c>
-      <c r="AF108">
-        <v>2.04</v>
-      </c>
-      <c r="AG108">
-        <v>1.51</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ108">
-        <v>1.24</v>
-      </c>
-      <c r="AK108">
-        <v>2.07</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R109">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S109">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T109">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U109">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V109">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W109">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z109">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB109">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC109">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD109">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE109">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG109">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK109">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -19869,25 +19869,25 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="O120">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="P120">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q120">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R120">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="S120">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T120">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U120">
         <v>2.73</v>
@@ -19896,16 +19896,16 @@
         <v>1.4</v>
       </c>
       <c r="W120">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
         <v>1</v>
       </c>
       <c r="Y120">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z120">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="AA120">
         <v>1.96</v>
@@ -19923,7 +19923,7 @@
         <v>1.12</v>
       </c>
       <c r="AF120">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG120">
         <v>1.73</v>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK120">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,52 +20041,52 @@
         <v>5.14</v>
       </c>
       <c r="Q121">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R121">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S121">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T121">
         <v>2.77</v>
       </c>
       <c r="U121">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="V121">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W121">
         <v>1.05</v>
       </c>
       <c r="X121">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
+        <v>1.29</v>
+      </c>
+      <c r="Z121">
+        <v>3.4</v>
+      </c>
+      <c r="AA121">
+        <v>1.98</v>
+      </c>
+      <c r="AB121">
+        <v>1.78</v>
+      </c>
+      <c r="AC121">
+        <v>3.18</v>
+      </c>
+      <c r="AD121">
         <v>1.27</v>
       </c>
-      <c r="Z121">
-        <v>3.18</v>
-      </c>
-      <c r="AA121">
-        <v>2.01</v>
-      </c>
-      <c r="AB121">
-        <v>1.86</v>
-      </c>
-      <c r="AC121">
-        <v>3.3</v>
-      </c>
-      <c r="AD121">
-        <v>1.29</v>
-      </c>
       <c r="AE121">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF121">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG121">
         <v>1.79</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK121">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,19 +20195,19 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="O122">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P122">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q122">
         <v>3.16</v>
       </c>
       <c r="R122">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
         <v>1.38</v>
@@ -20216,28 +20216,28 @@
         <v>2.81</v>
       </c>
       <c r="U122">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="V122">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W122">
         <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z122">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="AA122">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB122">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC122">
         <v>3.05</v>
@@ -20246,13 +20246,13 @@
         <v>1.29</v>
       </c>
       <c r="AE122">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG122">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK122">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20856,55 +20856,55 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S126">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T126">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U126">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V126">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W126">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X126">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y126">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z126">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA126">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB126">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC126">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD126">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE126">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF126">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG126">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK126">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,58 +21010,58 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O127">
         <v>3.75</v>
       </c>
       <c r="P127">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="Q127">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R127">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="S127">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T127">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U127">
         <v>2.85</v>
       </c>
       <c r="V127">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X127">
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z127">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AA127">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB127">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC127">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="AD127">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE127">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF127">
         <v>1.9</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21182,55 +21182,55 @@
         <v>3.29</v>
       </c>
       <c r="Q128">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="R128">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S128">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T128">
         <v>2.73</v>
       </c>
       <c r="U128">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V128">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W128">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X128">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y128">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z128">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AA128">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB128">
+        <v>1.72</v>
+      </c>
+      <c r="AC128">
+        <v>3.6</v>
+      </c>
+      <c r="AD128">
+        <v>1.25</v>
+      </c>
+      <c r="AE128">
+        <v>1.09</v>
+      </c>
+      <c r="AF128">
         <v>1.75</v>
       </c>
-      <c r="AC128">
-        <v>3.44</v>
-      </c>
-      <c r="AD128">
-        <v>1.23</v>
-      </c>
-      <c r="AE128">
-        <v>1.04</v>
-      </c>
-      <c r="AF128">
-        <v>1.78</v>
-      </c>
       <c r="AG128">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21837,19 +21837,19 @@
         <v>2.66</v>
       </c>
       <c r="R132">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S132">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T132">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U132">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="V132">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W132">
         <v>1.05</v>
@@ -21858,7 +21858,7 @@
         <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z132">
         <v>2.9</v>
@@ -21870,19 +21870,19 @@
         <v>1.65</v>
       </c>
       <c r="AC132">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="AD132">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE132">
         <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AG132">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL132">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="O3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q3">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="R3">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="S3">
         <v>1.22</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U3">
         <v>2.2</v>
@@ -825,7 +825,7 @@
         <v>1.58</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -834,28 +834,28 @@
         <v>1.1</v>
       </c>
       <c r="Z3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA3">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AB3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC3">
         <v>2.25</v>
       </c>
       <c r="AD3">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE3">
         <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG3">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,13 +970,13 @@
         <v>3.35</v>
       </c>
       <c r="Q4">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="R4">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
         <v>2.92</v>
@@ -988,22 +988,22 @@
         <v>1.43</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z4">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA4">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB4">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AC4">
         <v>2.7</v>
@@ -1015,10 +1015,10 @@
         <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>2.74</v>
       </c>
       <c r="AA5">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AB5">
         <v>1.67</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
         <v>2</v>
       </c>
       <c r="Q7">
-        <v>5.07</v>
+        <v>4.2</v>
       </c>
       <c r="R7">
         <v>1.93</v>
       </c>
       <c r="S7">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T7">
         <v>2.36</v>
       </c>
       <c r="U7">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V7">
         <v>1.28</v>
@@ -1489,7 +1489,7 @@
         <v>2.57</v>
       </c>
       <c r="AA7">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AB7">
         <v>1.58</v>
@@ -1501,13 +1501,13 @@
         <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG7">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,31 +1622,31 @@
         <v>4.22</v>
       </c>
       <c r="Q8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R8">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="U8">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
         <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z8">
         <v>3.54</v>
@@ -1655,22 +1655,22 @@
         <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
         <v>2.8</v>
       </c>
       <c r="AD8">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
         <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P9">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q9">
         <v>5.02</v>
@@ -1815,25 +1815,25 @@
         <v>2.64</v>
       </c>
       <c r="AA9">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AB9">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC9">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AD9">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
         <v>1</v>
       </c>
       <c r="AF9">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="R10">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T10">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="U10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V10">
         <v>1.27</v>
@@ -1969,34 +1969,34 @@
         <v>1.01</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z10">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AA10">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AB10">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE10">
         <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AG10">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,37 +2105,37 @@
         <v>1.8</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="P11">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q11">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U11">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z11">
         <v>3.04</v>
@@ -2144,7 +2144,7 @@
         <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC11">
         <v>3.58</v>
@@ -2159,7 +2159,7 @@
         <v>1.86</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
         <v>3.38</v>
       </c>
       <c r="Q12">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="S12">
         <v>1.34</v>
@@ -2286,10 +2286,10 @@
         <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -2298,19 +2298,19 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
         <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD12">
         <v>1.31</v>
@@ -2319,7 +2319,7 @@
         <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
         <v>2</v>
@@ -2338,7 +2338,7 @@
         <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,40 +2437,40 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R13">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S13">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
         <v>3.82</v>
       </c>
       <c r="U13">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="V13">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>6.57</v>
+        <v>10.2</v>
       </c>
       <c r="AA13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AC13">
         <v>2.06</v>
@@ -2479,13 +2479,13 @@
         <v>1.78</v>
       </c>
       <c r="AE13">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
         <v>1.4</v>
       </c>
       <c r="AG13">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="O16">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="Q16">
         <v>3.12</v>
@@ -2956,7 +2956,7 @@
         <v>2.86</v>
       </c>
       <c r="AA16">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB16">
         <v>1.72</v>
@@ -2965,7 +2965,7 @@
         <v>3.94</v>
       </c>
       <c r="AD16">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE16">
         <v>1.02</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AK16">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="O18">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="Q18">
+        <v>2.24</v>
+      </c>
+      <c r="R18">
         <v>2.42</v>
       </c>
-      <c r="R18">
-        <v>2.63</v>
-      </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U18">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="V18">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>5.99</v>
+        <v>7.29</v>
       </c>
       <c r="AA18">
+        <v>1.53</v>
+      </c>
+      <c r="AB18">
+        <v>2.4</v>
+      </c>
+      <c r="AC18">
+        <v>2.31</v>
+      </c>
+      <c r="AD18">
+        <v>1.63</v>
+      </c>
+      <c r="AE18">
+        <v>1.21</v>
+      </c>
+      <c r="AF18">
         <v>1.46</v>
       </c>
-      <c r="AB18">
-        <v>2.89</v>
-      </c>
-      <c r="AC18">
-        <v>2.09</v>
-      </c>
-      <c r="AD18">
-        <v>1.76</v>
-      </c>
-      <c r="AE18">
-        <v>1.29</v>
-      </c>
-      <c r="AF18">
-        <v>1.36</v>
-      </c>
       <c r="AG18">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="O19">
-        <v>3.47</v>
+        <v>3.92</v>
       </c>
       <c r="P19">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="Q19">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="R19">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="U19">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>7.29</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="AC19">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="AD19">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE19">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF19">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG19">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,49 +3578,49 @@
         <v>3.38</v>
       </c>
       <c r="Q20">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="R20">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="S20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="U20">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W20">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>5.83</v>
+        <v>5.65</v>
       </c>
       <c r="AA20">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB20">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AC20">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AD20">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF20">
         <v>1.4</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
         <v>1.86</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
         <v>3.3</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="R21">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="S21">
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U21">
         <v>2.05</v>
@@ -3771,13 +3771,13 @@
         <v>5.55</v>
       </c>
       <c r="AA21">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB21">
-        <v>2.64</v>
+        <v>2.77</v>
       </c>
       <c r="AC21">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD21">
         <v>1.73</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
         <v>1.91</v>
@@ -3898,61 +3898,61 @@
         <v>1.92</v>
       </c>
       <c r="O22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
         <v>3.55</v>
       </c>
       <c r="Q22">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="R22">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T22">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U22">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="AD22">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG22">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.55</v>
+        <v>5.1</v>
       </c>
       <c r="O25">
         <v>4.3</v>
       </c>
       <c r="P25">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q25">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="R25">
         <v>2.47</v>
@@ -4402,19 +4402,19 @@
         <v>1.22</v>
       </c>
       <c r="T25">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U25">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V25">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W25">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
         <v>1.1</v>
@@ -4426,7 +4426,7 @@
         <v>1.44</v>
       </c>
       <c r="AB25">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC25">
         <v>2.32</v>
@@ -4435,13 +4435,13 @@
         <v>1.58</v>
       </c>
       <c r="AE25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF25">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK25">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4559,13 +4559,13 @@
         <v>2.6</v>
       </c>
       <c r="R26">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T26">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
         <v>2.45</v>
@@ -4574,7 +4574,7 @@
         <v>1.5</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,16 +4583,16 @@
         <v>1.23</v>
       </c>
       <c r="Z26">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AB26">
         <v>1.96</v>
       </c>
       <c r="AC26">
-        <v>2.85</v>
+        <v>3.65</v>
       </c>
       <c r="AD26">
         <v>1.36</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,22 +4710,22 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q27">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R27">
         <v>2.16</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
         <v>3.08</v>
@@ -4734,7 +4734,7 @@
         <v>2.38</v>
       </c>
       <c r="V27">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
         <v>1.11</v>
@@ -4743,16 +4743,16 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA27">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB27">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AC27">
         <v>2.52</v>
@@ -4761,13 +4761,13 @@
         <v>1.41</v>
       </c>
       <c r="AE27">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
         <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
         <v>1.61</v>
@@ -5199,65 +5199,65 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O30">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>4.45</v>
+        <v>5.75</v>
       </c>
       <c r="Q30">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="R30">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="U30">
         <v>2.77</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="AA30">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AB30">
+        <v>1.86</v>
+      </c>
+      <c r="AC30">
+        <v>3.14</v>
+      </c>
+      <c r="AD30">
+        <v>1.27</v>
+      </c>
+      <c r="AE30">
+        <v>1.1</v>
+      </c>
+      <c r="AF30">
+        <v>1.95</v>
+      </c>
+      <c r="AG30">
         <v>1.78</v>
       </c>
-      <c r="AC30">
-        <v>3.3</v>
-      </c>
-      <c r="AD30">
-        <v>1.29</v>
-      </c>
-      <c r="AE30">
-        <v>1.06</v>
-      </c>
-      <c r="AF30">
-        <v>1.92</v>
-      </c>
-      <c r="AG30">
-        <v>1.79</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK30">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>2.01</v>
       </c>
       <c r="AG31">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O32">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P32">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q32">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="R32">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="U32">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="V32">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z32">
-        <v>4.92</v>
+        <v>5.25</v>
       </c>
       <c r="AA32">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB32">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AC32">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AD32">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF32">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AG32">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK32">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5866,10 +5866,10 @@
         <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T34">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U34">
         <v>2.55</v>
@@ -5890,25 +5890,25 @@
         <v>3.5</v>
       </c>
       <c r="AA34">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB34">
         <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD34">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
         <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O35">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P35">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q35">
-        <v>4.78</v>
+        <v>4.82</v>
       </c>
       <c r="R35">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="S35">
         <v>1.27</v>
@@ -6035,10 +6035,10 @@
         <v>3.25</v>
       </c>
       <c r="U35">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6050,22 +6050,22 @@
         <v>1.15</v>
       </c>
       <c r="Z35">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA35">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB35">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC35">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="AD35">
         <v>1.41</v>
       </c>
       <c r="AE35">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
         <v>1.61</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="O36">
         <v>3.4</v>
@@ -6186,10 +6186,10 @@
         <v>3.9</v>
       </c>
       <c r="Q36">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="R36">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="S36">
         <v>1.43</v>
@@ -6198,10 +6198,10 @@
         <v>2.59</v>
       </c>
       <c r="U36">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="V36">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W36">
         <v>1.01</v>
@@ -6213,13 +6213,13 @@
         <v>1.32</v>
       </c>
       <c r="Z36">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA36">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AB36">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC36">
         <v>3.84</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AK36">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="P37">
-        <v>4.65</v>
+        <v>4.35</v>
       </c>
       <c r="Q37">
         <v>2.21</v>
@@ -6355,16 +6355,16 @@
         <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>3.23</v>
+        <v>3.08</v>
       </c>
       <c r="U37">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6376,19 +6376,19 @@
         <v>1.23</v>
       </c>
       <c r="Z37">
-        <v>3.74</v>
+        <v>3.93</v>
       </c>
       <c r="AA37">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AB37">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC37">
         <v>2.86</v>
       </c>
       <c r="AD37">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE37">
         <v>1.11</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="O38">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="P38">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="Q38">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="R38">
         <v>2.89</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T38">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="U38">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V38">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W38">
         <v>1.16</v>
@@ -6539,28 +6539,28 @@
         <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA38">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AB38">
         <v>2.75</v>
       </c>
       <c r="AC38">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD38">
         <v>1.7</v>
       </c>
       <c r="AE38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF38">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK38">
         <v>2.8</v>
@@ -6669,7 +6669,7 @@
         <v>1.44</v>
       </c>
       <c r="O39">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="P39">
         <v>8.4</v>
@@ -6838,13 +6838,13 @@
         <v>2.91</v>
       </c>
       <c r="Q40">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R40">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T40">
         <v>3</v>
@@ -6856,13 +6856,13 @@
         <v>1.48</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z40">
         <v>3.8</v>
@@ -6874,7 +6874,7 @@
         <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD40">
         <v>1.39</v>
@@ -6883,10 +6883,10 @@
         <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AG40">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="O41">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="P41">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="Q41">
         <v>1.94</v>
@@ -7007,13 +7007,13 @@
         <v>2.43</v>
       </c>
       <c r="S41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U41">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V41">
         <v>1.62</v>
@@ -7031,10 +7031,10 @@
         <v>5</v>
       </c>
       <c r="AA41">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB41">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AC41">
         <v>2.27</v>
@@ -7043,13 +7043,13 @@
         <v>1.61</v>
       </c>
       <c r="AE41">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
         <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK41">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="O42">
         <v>4.15</v>
@@ -7173,10 +7173,10 @@
         <v>1.21</v>
       </c>
       <c r="T42">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="U42">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V42">
         <v>1.73</v>
@@ -7185,19 +7185,19 @@
         <v>1.16</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z42">
-        <v>5.9</v>
+        <v>6.04</v>
       </c>
       <c r="AA42">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB42">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AC42">
         <v>2</v>
@@ -7206,13 +7206,13 @@
         <v>1.78</v>
       </c>
       <c r="AE42">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF42">
         <v>1.43</v>
       </c>
       <c r="AG42">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
+        <v>2.77</v>
+      </c>
+      <c r="O45">
+        <v>3</v>
+      </c>
+      <c r="P45">
+        <v>2.37</v>
+      </c>
+      <c r="Q45">
+        <v>3.35</v>
+      </c>
+      <c r="R45">
+        <v>2.07</v>
+      </c>
+      <c r="S45">
+        <v>1.4</v>
+      </c>
+      <c r="T45">
         <v>2.75</v>
       </c>
-      <c r="O45">
-        <v>3.28</v>
-      </c>
-      <c r="P45">
-        <v>2.08</v>
-      </c>
-      <c r="Q45">
-        <v>3.72</v>
-      </c>
-      <c r="R45">
-        <v>1.95</v>
-      </c>
-      <c r="S45">
-        <v>1.46</v>
-      </c>
-      <c r="T45">
-        <v>2.5</v>
-      </c>
       <c r="U45">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="V45">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y45">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z45">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA45">
         <v>2.08</v>
       </c>
       <c r="AB45">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC45">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="AD45">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF45">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG45">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AK45">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7813,13 +7813,13 @@
         <v>3.45</v>
       </c>
       <c r="P46">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q46">
         <v>2.68</v>
       </c>
       <c r="R46">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
         <v>1.28</v>
@@ -7852,16 +7852,16 @@
         <v>2.16</v>
       </c>
       <c r="AC46">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="AD46">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE46">
         <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG46">
         <v>2.36</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>4.48</v>
       </c>
       <c r="Q48">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="R48">
         <v>1.96</v>
@@ -8190,7 +8190,7 @@
         <v>1.97</v>
       </c>
       <c r="AG48">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="O52">
-        <v>3.91</v>
+        <v>4.85</v>
       </c>
       <c r="P52">
-        <v>3.93</v>
+        <v>1.32</v>
       </c>
       <c r="Q52">
-        <v>2.24</v>
+        <v>5.95</v>
       </c>
       <c r="R52">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T52">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="U52">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="V52">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="W52">
+        <v>1.18</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.06</v>
+      </c>
+      <c r="Z52">
+        <v>6.2</v>
+      </c>
+      <c r="AA52">
+        <v>1.32</v>
+      </c>
+      <c r="AB52">
+        <v>2.89</v>
+      </c>
+      <c r="AC52">
+        <v>1.94</v>
+      </c>
+      <c r="AD52">
+        <v>1.88</v>
+      </c>
+      <c r="AE52">
+        <v>1.32</v>
+      </c>
+      <c r="AF52">
+        <v>1.53</v>
+      </c>
+      <c r="AG52">
+        <v>2.35</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.16</v>
+      </c>
+      <c r="AK52">
         <v>1.09</v>
-      </c>
-      <c r="X52">
-        <v>1.03</v>
-      </c>
-      <c r="Y52">
-        <v>1.18</v>
-      </c>
-      <c r="Z52">
-        <v>4.6</v>
-      </c>
-      <c r="AA52">
-        <v>1.6</v>
-      </c>
-      <c r="AB52">
-        <v>2.25</v>
-      </c>
-      <c r="AC52">
-        <v>2.47</v>
-      </c>
-      <c r="AD52">
-        <v>1.55</v>
-      </c>
-      <c r="AE52">
-        <v>1.22</v>
-      </c>
-      <c r="AF52">
-        <v>1.54</v>
-      </c>
-      <c r="AG52">
-        <v>2.3</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.19</v>
-      </c>
-      <c r="AK52">
-        <v>2.08</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="O53">
-        <v>4.85</v>
+        <v>3.91</v>
       </c>
       <c r="P53">
-        <v>1.32</v>
+        <v>3.93</v>
       </c>
       <c r="Q53">
-        <v>5.95</v>
+        <v>2.24</v>
       </c>
       <c r="R53">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="S53">
+        <v>1.28</v>
+      </c>
+      <c r="T53">
+        <v>3.34</v>
+      </c>
+      <c r="U53">
+        <v>2.36</v>
+      </c>
+      <c r="V53">
+        <v>1.56</v>
+      </c>
+      <c r="W53">
+        <v>1.09</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
         <v>1.18</v>
       </c>
-      <c r="T53">
-        <v>4.1</v>
-      </c>
-      <c r="U53">
-        <v>1.98</v>
-      </c>
-      <c r="V53">
-        <v>1.77</v>
-      </c>
-      <c r="W53">
-        <v>1.18</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.06</v>
-      </c>
       <c r="Z53">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA53">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AB53">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="AC53">
-        <v>1.94</v>
+        <v>2.47</v>
       </c>
       <c r="AD53">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE53">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF53">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG53">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK53">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="O54">
         <v>3.55</v>
       </c>
       <c r="P54">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="Q54">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="R54">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
         <v>1.22</v>
@@ -9156,10 +9156,10 @@
         <v>2.49</v>
       </c>
       <c r="AC54">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AD54">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE54">
         <v>1.24</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="Q55">
         <v>2.13</v>
@@ -9289,10 +9289,10 @@
         <v>2.54</v>
       </c>
       <c r="S55">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T55">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U55">
         <v>2.05</v>
@@ -9307,25 +9307,25 @@
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z55">
-        <v>6.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA55">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB55">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="AC55">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD55">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AE55">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF55">
         <v>1.4</v>
@@ -9446,19 +9446,19 @@
         <v>1.95</v>
       </c>
       <c r="Q56">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="R56">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S56">
         <v>1.19</v>
       </c>
       <c r="T56">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="U56">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="V56">
         <v>1.67</v>
@@ -9470,31 +9470,31 @@
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AA56">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB56">
         <v>2.62</v>
       </c>
       <c r="AC56">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AD56">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE56">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG56">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK56">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="O57">
+        <v>3.49</v>
+      </c>
+      <c r="P57">
+        <v>2.91</v>
+      </c>
+      <c r="Q57">
+        <v>2.47</v>
+      </c>
+      <c r="R57">
+        <v>2.63</v>
+      </c>
+      <c r="S57">
+        <v>1.14</v>
+      </c>
+      <c r="T57">
+        <v>4.5</v>
+      </c>
+      <c r="U57">
+        <v>1.8</v>
+      </c>
+      <c r="V57">
+        <v>1.98</v>
+      </c>
+      <c r="W57">
+        <v>1.24</v>
+      </c>
+      <c r="X57">
+        <v>1.01</v>
+      </c>
+      <c r="Y57">
+        <v>1.04</v>
+      </c>
+      <c r="Z57">
+        <v>7.1</v>
+      </c>
+      <c r="AA57">
+        <v>1.29</v>
+      </c>
+      <c r="AB57">
         <v>3.5</v>
       </c>
-      <c r="P57">
-        <v>1.93</v>
-      </c>
-      <c r="Q57">
-        <v>3.56</v>
-      </c>
-      <c r="R57">
-        <v>2.46</v>
-      </c>
-      <c r="S57">
-        <v>1.22</v>
-      </c>
-      <c r="T57">
-        <v>3.82</v>
-      </c>
-      <c r="U57">
+      <c r="AC57">
+        <v>1.72</v>
+      </c>
+      <c r="AD57">
         <v>2.06</v>
       </c>
-      <c r="V57">
-        <v>1.7</v>
-      </c>
-      <c r="W57">
-        <v>1.17</v>
-      </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>1.12</v>
-      </c>
-      <c r="Z57">
-        <v>5.45</v>
-      </c>
-      <c r="AA57">
-        <v>1.38</v>
-      </c>
-      <c r="AB57">
-        <v>2.62</v>
-      </c>
-      <c r="AC57">
-        <v>2.04</v>
-      </c>
-      <c r="AD57">
-        <v>1.74</v>
-      </c>
       <c r="AE57">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AF57">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG57">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="O58">
-        <v>3.49</v>
+        <v>3.94</v>
       </c>
       <c r="P58">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="Q58">
-        <v>2.52</v>
+        <v>3.13</v>
       </c>
       <c r="R58">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S58">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T58">
-        <v>5</v>
+        <v>3.82</v>
       </c>
       <c r="U58">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V58">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="W58">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z58">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA58">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AB58">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="AC58">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AD58">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AE58">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AF58">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AG58">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK58">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="O59">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P59">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
       </c>
       <c r="R59">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S59">
         <v>1.4</v>
@@ -9965,13 +9965,13 @@
         <v>3.3</v>
       </c>
       <c r="AA59">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB59">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC59">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AD59">
         <v>1.32</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
+        <v>2.28</v>
+      </c>
+      <c r="O60">
+        <v>3.36</v>
+      </c>
+      <c r="P60">
+        <v>2.96</v>
+      </c>
+      <c r="Q60">
+        <v>2.9</v>
+      </c>
+      <c r="R60">
         <v>2.25</v>
-      </c>
-      <c r="O60">
-        <v>3.25</v>
-      </c>
-      <c r="P60">
-        <v>2.75</v>
-      </c>
-      <c r="Q60">
-        <v>2.85</v>
-      </c>
-      <c r="R60">
-        <v>2.1</v>
       </c>
       <c r="S60">
         <v>1.34</v>
       </c>
       <c r="T60">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="U60">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V60">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W60">
         <v>1.05</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z60">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="AA60">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB60">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC60">
-        <v>3.12</v>
+        <v>2.81</v>
       </c>
       <c r="AD60">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE60">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF60">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG60">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK60">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="O61">
         <v>3.8</v>
       </c>
       <c r="P61">
-        <v>4.85</v>
+        <v>4.33</v>
       </c>
       <c r="Q61">
         <v>2.2</v>
       </c>
       <c r="R61">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S61">
         <v>1.34</v>
@@ -10294,10 +10294,10 @@
         <v>1.83</v>
       </c>
       <c r="AB61">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC61">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="AD61">
         <v>1.31</v>
@@ -10306,10 +10306,10 @@
         <v>1.08</v>
       </c>
       <c r="AF61">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG61">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>2.35</v>
       </c>
       <c r="S62">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
         <v>2.97</v>
@@ -10442,13 +10442,13 @@
         <v>1.5</v>
       </c>
       <c r="W62">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z62">
         <v>4</v>
@@ -10593,10 +10593,10 @@
         <v>2.02</v>
       </c>
       <c r="S63">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T63">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U63">
         <v>2.88</v>
@@ -10605,7 +10605,7 @@
         <v>1.33</v>
       </c>
       <c r="W63">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X63">
         <v>1.02</v>
@@ -10750,7 +10750,7 @@
         <v>3.5</v>
       </c>
       <c r="Q64">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
         <v>1.99</v>
@@ -10780,10 +10780,10 @@
         <v>3.04</v>
       </c>
       <c r="AA64">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB64">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC64">
         <v>3.34</v>
@@ -10798,7 +10798,7 @@
         <v>1.81</v>
       </c>
       <c r="AG64">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
         <v>1.72</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="O67">
         <v>3.4</v>
       </c>
       <c r="P67">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q67">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="R67">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="S67">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
         <v>3.02</v>
       </c>
       <c r="U67">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V67">
         <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y67">
         <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="AA67">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB67">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC67">
         <v>2.66</v>
       </c>
       <c r="AD67">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE67">
         <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG67">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,7 +11402,7 @@
         <v>3.8</v>
       </c>
       <c r="Q68">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R68">
         <v>2.34</v>
@@ -11417,7 +11417,7 @@
         <v>2.25</v>
       </c>
       <c r="V68">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W68">
         <v>1.11</v>
@@ -11429,7 +11429,7 @@
         <v>1.13</v>
       </c>
       <c r="Z68">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA68">
         <v>1.61</v>
@@ -11444,7 +11444,7 @@
         <v>1.5</v>
       </c>
       <c r="AE68">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF68">
         <v>1.52</v>
@@ -11556,19 +11556,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O69">
         <v>3.5</v>
       </c>
       <c r="P69">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q69">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R69">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
         <v>1.31</v>
@@ -11577,43 +11577,43 @@
         <v>3.15</v>
       </c>
       <c r="U69">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="V69">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W69">
         <v>1.08</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z69">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA69">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB69">
         <v>2.1</v>
       </c>
       <c r="AC69">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD69">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AE69">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF69">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="AK69">
         <v>1.25</v>
@@ -11728,34 +11728,34 @@
         <v>5.4</v>
       </c>
       <c r="Q70">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="R70">
         <v>1.98</v>
       </c>
       <c r="S70">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U70">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V70">
         <v>1.31</v>
       </c>
       <c r="W70">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y70">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z70">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA70">
         <v>2.17</v>
@@ -11767,16 +11767,16 @@
         <v>3.95</v>
       </c>
       <c r="AD70">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE70">
         <v>1.02</v>
       </c>
       <c r="AF70">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG70">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12241,10 +12241,10 @@
         <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z73">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AA73">
         <v>2.34</v>
@@ -12253,10 +12253,10 @@
         <v>1.7</v>
       </c>
       <c r="AC73">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="AD73">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE73">
         <v>1.03</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O74">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="P74">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q74">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="R74">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T74">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="U74">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V74">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W74">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z74">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
       <c r="AA74">
         <v>1.36</v>
       </c>
       <c r="AB74">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="AC74">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AD74">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AE74">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF74">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AG74">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK74">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12709,19 +12709,19 @@
         <v>3.72</v>
       </c>
       <c r="R76">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="S76">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T76">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U76">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V76">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W76">
         <v>1.09</v>
@@ -12733,10 +12733,10 @@
         <v>1.2</v>
       </c>
       <c r="Z76">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AA76">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
         <v>2</v>
@@ -12869,10 +12869,10 @@
         <v>2.55</v>
       </c>
       <c r="Q77">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="R77">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
         <v>1.36</v>
@@ -12881,10 +12881,10 @@
         <v>2.75</v>
       </c>
       <c r="U77">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="V77">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W77">
         <v>1.07</v>
@@ -12893,13 +12893,13 @@
         <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z77">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA77">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB77">
         <v>1.76</v>
@@ -12933,7 +12933,7 @@
         <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13195,40 +13195,40 @@
         <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R79">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S79">
         <v>1.43</v>
       </c>
       <c r="T79">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="U79">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y79">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA79">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB79">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC79">
         <v>3.2</v>
@@ -13237,13 +13237,13 @@
         <v>1.26</v>
       </c>
       <c r="AE79">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF79">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG79">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK79">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13355,13 +13355,13 @@
         <v>3.6</v>
       </c>
       <c r="P80">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q80">
         <v>5.38</v>
       </c>
       <c r="R80">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S80">
         <v>1.36</v>
@@ -13370,43 +13370,43 @@
         <v>2.85</v>
       </c>
       <c r="U80">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="V80">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W80">
         <v>1.06</v>
       </c>
       <c r="X80">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z80">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AA80">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB80">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC80">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="AD80">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE80">
         <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG80">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK80">
         <v>1.15</v>
@@ -13518,58 +13518,58 @@
         <v>2.62</v>
       </c>
       <c r="P81">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q81">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="R81">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S81">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="T81">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="U81">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V81">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W81">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X81">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y81">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Z81">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AA81">
-        <v>3.08</v>
+        <v>3.48</v>
       </c>
       <c r="AB81">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC81">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="AD81">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AE81">
         <v>1.02</v>
       </c>
       <c r="AF81">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AG81">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13687,7 +13687,7 @@
         <v>2.78</v>
       </c>
       <c r="R82">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="S82">
         <v>1.65</v>
@@ -13699,7 +13699,7 @@
         <v>4.15</v>
       </c>
       <c r="V82">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="W82">
         <v>1.03</v>
@@ -13723,7 +13723,7 @@
         <v>6.25</v>
       </c>
       <c r="AD82">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE82">
         <v>1.03</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O83">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="P83">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="Q83">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="R83">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="S83">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="T83">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U83">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="V83">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
         <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z83">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AA83">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AB83">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC83">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD83">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AG83">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK83">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O84">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="P84">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="Q84">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="R84">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="S84">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="T84">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U84">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="V84">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W84">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X84">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y84">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z84">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AA84">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AB84">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC84">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="AD84">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AG84">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK84">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="O85">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P85">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q85">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="R85">
         <v>2.18</v>
@@ -14185,43 +14185,43 @@
         <v>2.85</v>
       </c>
       <c r="U85">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V85">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W85">
         <v>1.05</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z85">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA85">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB85">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC85">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD85">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE85">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF85">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG85">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK85">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,16 +14336,16 @@
         <v>1.89</v>
       </c>
       <c r="Q86">
-        <v>3.68</v>
+        <v>4.39</v>
       </c>
       <c r="R86">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S86">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T86">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U86">
         <v>2.13</v>
@@ -14354,25 +14354,25 @@
         <v>1.63</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z86">
         <v>4.95</v>
       </c>
       <c r="AA86">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB86">
         <v>2.46</v>
       </c>
       <c r="AC86">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD86">
         <v>1.62</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O87">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P87">
-        <v>5.54</v>
+        <v>5</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14653,10 +14653,10 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O88">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P88">
         <v>5</v>
@@ -14674,7 +14674,7 @@
         <v>4.4</v>
       </c>
       <c r="U88">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="V88">
         <v>1.71</v>
@@ -14698,19 +14698,19 @@
         <v>2.7</v>
       </c>
       <c r="AC88">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AD88">
         <v>1.72</v>
       </c>
       <c r="AE88">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF88">
         <v>1.51</v>
       </c>
       <c r="AG88">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>2.2</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P89">
         <v>3.03</v>
@@ -14834,16 +14834,16 @@
         <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="U89">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V89">
         <v>1.4</v>
       </c>
       <c r="W89">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
         <v>1.03</v>
@@ -14852,16 +14852,16 @@
         <v>1.26</v>
       </c>
       <c r="Z89">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="AA89">
         <v>1.85</v>
       </c>
       <c r="AB89">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC89">
-        <v>3.13</v>
+        <v>2.97</v>
       </c>
       <c r="AD89">
         <v>1.35</v>
@@ -14873,7 +14873,7 @@
         <v>1.65</v>
       </c>
       <c r="AG89">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,55 +14988,55 @@
         <v>0</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="P91">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,31 +15305,31 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q92">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R92">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S92">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="T92">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="U92">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V92">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W92">
         <v>1.05</v>
@@ -15338,31 +15338,31 @@
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z92">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA92">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AB92">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC92">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD92">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF92">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG92">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK92">
         <v>1.99</v>
@@ -15634,28 +15634,28 @@
         <v>2.65</v>
       </c>
       <c r="O94">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P94">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q94">
-        <v>3.44</v>
+        <v>3.13</v>
       </c>
       <c r="R94">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S94">
         <v>1.43</v>
       </c>
       <c r="T94">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U94">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="V94">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W94">
         <v>1.02</v>
@@ -15670,13 +15670,13 @@
         <v>3.08</v>
       </c>
       <c r="AA94">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB94">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC94">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD94">
         <v>1.23</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK94">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="O95">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P95">
-        <v>6.24</v>
+        <v>6.4</v>
       </c>
       <c r="Q95">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R95">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S95">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T95">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U95">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V95">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W95">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X95">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y95">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z95">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA95">
-        <v>2.49</v>
+        <v>2.87</v>
       </c>
       <c r="AB95">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AC95">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD95">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF95">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AG95">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK95">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O96">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
-        <v>5.2</v>
+        <v>6.24</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA96">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AB96">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,19 +16772,19 @@
         </is>
       </c>
       <c r="N101">
+        <v>2.06</v>
+      </c>
+      <c r="O101">
+        <v>3.4</v>
+      </c>
+      <c r="P101">
+        <v>3.1</v>
+      </c>
+      <c r="Q101">
+        <v>2.7</v>
+      </c>
+      <c r="R101">
         <v>2.1</v>
-      </c>
-      <c r="O101">
-        <v>3.32</v>
-      </c>
-      <c r="P101">
-        <v>2.88</v>
-      </c>
-      <c r="Q101">
-        <v>2.87</v>
-      </c>
-      <c r="R101">
-        <v>1.96</v>
       </c>
       <c r="S101">
         <v>1.44</v>
@@ -16805,19 +16805,19 @@
         <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z101">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="AA101">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB101">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC101">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AD101">
         <v>1.24</v>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK101">
         <v>1.61</v>
@@ -17107,10 +17107,10 @@
         <v>1.45</v>
       </c>
       <c r="Q103">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="R103">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S103">
         <v>1.3</v>
@@ -17119,43 +17119,43 @@
         <v>3.1</v>
       </c>
       <c r="U103">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="V103">
         <v>1.45</v>
       </c>
       <c r="W103">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z103">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AA103">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB103">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC103">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AD103">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE103">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AG103">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK103">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O104">
         <v>2.7</v>
       </c>
       <c r="P104">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O105">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P105">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Q105">
         <v>2.01</v>
@@ -17466,13 +17466,13 @@
         <v>2.14</v>
       </c>
       <c r="AB105">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC105">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="AD105">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE105">
         <v>1.02</v>
@@ -17481,7 +17481,7 @@
         <v>2.28</v>
       </c>
       <c r="AG105">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O106">
         <v>2.95</v>
@@ -17596,55 +17596,55 @@
         <v>4.4</v>
       </c>
       <c r="Q106">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="R106">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="S106">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="T106">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="U106">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="V106">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W106">
         <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y106">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z106">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AA106">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AB106">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC106">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AD106">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE106">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF106">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG106">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK106">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="O107">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P107">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q107">
-        <v>2.27</v>
+        <v>2.71</v>
       </c>
       <c r="R107">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="S107">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="T107">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="U107">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="V107">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="W107">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X107">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y107">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="Z107">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="AA107">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AB107">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AC107">
-        <v>4.7</v>
+        <v>5.95</v>
       </c>
       <c r="AD107">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE107">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF107">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AG107">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK107">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="O108">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P108">
-        <v>5.45</v>
+        <v>5.85</v>
       </c>
       <c r="Q108">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="R108">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="S108">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="T108">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="U108">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="V108">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W108">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X108">
         <v>1.08</v>
       </c>
       <c r="Y108">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z108">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="AA108">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AB108">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC108">
-        <v>5.95</v>
+        <v>4.5</v>
       </c>
       <c r="AD108">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AE108">
         <v>1.03</v>
       </c>
       <c r="AF108">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AG108">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK108">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O110">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P110">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q110">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="R110">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S110">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="T110">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="U110">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="V110">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W110">
         <v>1.01</v>
       </c>
       <c r="X110">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y110">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Z110">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AA110">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AB110">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC110">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD110">
         <v>1.13</v>
       </c>
       <c r="AE110">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF110">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG110">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK110">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18405,16 +18405,16 @@
         <v>1.38</v>
       </c>
       <c r="O111">
+        <v>4.25</v>
+      </c>
+      <c r="P111">
         <v>4.45</v>
       </c>
-      <c r="P111">
-        <v>4.4</v>
-      </c>
       <c r="Q111">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="R111">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="S111">
         <v>1.12</v>
@@ -18426,7 +18426,7 @@
         <v>1.79</v>
       </c>
       <c r="V111">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="W111">
         <v>1.25</v>
@@ -18435,28 +18435,28 @@
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z111">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
       <c r="AA111">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AB111">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AC111">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD111">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AE111">
         <v>1.43</v>
       </c>
       <c r="AF111">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG111">
         <v>2.94</v>
@@ -18475,7 +18475,7 @@
         <v>1.14</v>
       </c>
       <c r="AK111">
-        <v>2.49</v>
+        <v>2.12</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="O112">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="P112">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q112">
         <v>2.63</v>
@@ -18586,13 +18586,13 @@
         <v>4.75</v>
       </c>
       <c r="U112">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V112">
         <v>1.93</v>
       </c>
       <c r="W112">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X112">
         <v>1.01</v>
@@ -18604,10 +18604,10 @@
         <v>7.5</v>
       </c>
       <c r="AA112">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AB112">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AC112">
         <v>1.71</v>
@@ -18619,10 +18619,10 @@
         <v>1.43</v>
       </c>
       <c r="AF112">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AG112">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O113">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P113">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>2.45</v>
       </c>
       <c r="AA113">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB113">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="O114">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P114">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O115">
         <v>3.1</v>
@@ -19063,43 +19063,43 @@
         <v>3.8</v>
       </c>
       <c r="Q115">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R115">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S115">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T115">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="U115">
         <v>3.46</v>
       </c>
       <c r="V115">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="W115">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
         <v>1.05</v>
       </c>
       <c r="Y115">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Z115">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="AA115">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AB115">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC115">
-        <v>4.55</v>
+        <v>4.72</v>
       </c>
       <c r="AD115">
         <v>1.13</v>
@@ -19108,10 +19108,10 @@
         <v>1</v>
       </c>
       <c r="AF115">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AG115">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>1.28</v>
       </c>
       <c r="AK115">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19389,13 +19389,13 @@
         <v>4.83</v>
       </c>
       <c r="Q117">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R117">
         <v>2.28</v>
       </c>
       <c r="S117">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T117">
         <v>2.92</v>
@@ -19413,13 +19413,13 @@
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z117">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA117">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AB117">
         <v>1.92</v>
@@ -19428,10 +19428,10 @@
         <v>2.9</v>
       </c>
       <c r="AD117">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE117">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF117">
         <v>1.7</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AK117">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O124">
         <v>3.3</v>
@@ -20530,19 +20530,19 @@
         <v>2.2</v>
       </c>
       <c r="Q124">
-        <v>3.93</v>
+        <v>3.45</v>
       </c>
       <c r="R124">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S124">
         <v>1.44</v>
       </c>
       <c r="T124">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="U124">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V124">
         <v>1.32</v>
@@ -20551,7 +20551,7 @@
         <v>1.04</v>
       </c>
       <c r="X124">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y124">
         <v>1.3</v>
@@ -20560,7 +20560,7 @@
         <v>2.97</v>
       </c>
       <c r="AA124">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB124">
         <v>1.7</v>
@@ -20578,7 +20578,7 @@
         <v>1.81</v>
       </c>
       <c r="AG124">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AK124">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20693,7 +20693,7 @@
         <v>2.75</v>
       </c>
       <c r="Q125">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="R125">
         <v>1.92</v>
@@ -20705,16 +20705,16 @@
         <v>2.25</v>
       </c>
       <c r="U125">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="V125">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W125">
         <v>1.04</v>
       </c>
       <c r="X125">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y125">
         <v>1.51</v>
@@ -20732,7 +20732,7 @@
         <v>4.5</v>
       </c>
       <c r="AD125">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE125">
         <v>1.01</v>
@@ -20856,55 +20856,55 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21345,25 +21345,25 @@
         <v>4.72</v>
       </c>
       <c r="Q129">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="R129">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S129">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T129">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U129">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V129">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W129">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X129">
         <v>1.03</v>
@@ -21372,28 +21372,28 @@
         <v>1.16</v>
       </c>
       <c r="Z129">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA129">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AB129">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AC129">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="AD129">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE129">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF129">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AG129">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK129">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21834,7 +21834,7 @@
         <v>3.2</v>
       </c>
       <c r="Q132">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="R132">
         <v>2.05</v>
@@ -21879,7 +21879,7 @@
         <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG132">
         <v>1.8</v>
@@ -21898,7 +21898,7 @@
         <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21988,16 +21988,16 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="O133">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P133">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q133">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R133">
         <v>2.06</v>
@@ -22018,16 +22018,16 @@
         <v>1.06</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y133">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z133">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AA133">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB133">
         <v>1.83</v>
@@ -22036,10 +22036,10 @@
         <v>3.2</v>
       </c>
       <c r="AD133">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE133">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF133">
         <v>1.67</v>
@@ -22160,16 +22160,16 @@
         <v>5.07</v>
       </c>
       <c r="Q134">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R134">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S134">
         <v>1.29</v>
       </c>
       <c r="T134">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="U134">
         <v>2.47</v>
@@ -22184,28 +22184,28 @@
         <v>1.04</v>
       </c>
       <c r="Y134">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z134">
-        <v>3.78</v>
+        <v>2.9</v>
       </c>
       <c r="AA134">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB134">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC134">
         <v>2.74</v>
       </c>
       <c r="AD134">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE134">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF134">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG134">
         <v>2</v>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK134">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="AL134">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -1299,13 +1299,13 @@
         <v>2.2</v>
       </c>
       <c r="R6">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="U6">
         <v>2.71</v>
@@ -1314,7 +1314,7 @@
         <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1326,10 +1326,10 @@
         <v>3.5</v>
       </c>
       <c r="AA6">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
         <v>2.97</v>
@@ -1341,10 +1341,10 @@
         <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.82</v>
+        <v>4.5</v>
       </c>
       <c r="U13">
         <v>2.05</v>
@@ -2455,7 +2455,7 @@
         <v>1.75</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2473,19 +2473,19 @@
         <v>3.14</v>
       </c>
       <c r="AC13">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AD13">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF13">
         <v>1.4</v>
       </c>
       <c r="AG13">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P14">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="R14">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S14">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
         <v>1.08</v>
@@ -2624,28 +2624,28 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>3.84</v>
+        <v>4.23</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AC14">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
         <v>2.21</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2766,25 +2766,25 @@
         <v>2.25</v>
       </c>
       <c r="R15">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="S15">
         <v>1.39</v>
       </c>
       <c r="T15">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="U15">
         <v>2.86</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
         <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
         <v>1.28</v>
@@ -2793,16 +2793,16 @@
         <v>3.08</v>
       </c>
       <c r="AA15">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB15">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AC15">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
         <v>1.06</v>
@@ -3089,56 +3089,56 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R17">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U17">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA17">
+        <v>1.81</v>
+      </c>
+      <c r="AB17">
+        <v>1.88</v>
+      </c>
+      <c r="AC17">
+        <v>2.92</v>
+      </c>
+      <c r="AD17">
+        <v>1.31</v>
+      </c>
+      <c r="AE17">
+        <v>1.08</v>
+      </c>
+      <c r="AF17">
+        <v>1.91</v>
+      </c>
+      <c r="AG17">
         <v>1.75</v>
       </c>
-      <c r="AB17">
-        <v>2.05</v>
-      </c>
-      <c r="AC17">
-        <v>3</v>
-      </c>
-      <c r="AD17">
-        <v>1.33</v>
-      </c>
-      <c r="AE17">
-        <v>1.09</v>
-      </c>
-      <c r="AF17">
-        <v>1.8</v>
-      </c>
-      <c r="AG17">
-        <v>1.91</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
         <v>2.17</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>2.03</v>
+      </c>
+      <c r="O18">
+        <v>3.92</v>
+      </c>
+      <c r="P18">
+        <v>3.34</v>
+      </c>
+      <c r="Q18">
+        <v>2.45</v>
+      </c>
+      <c r="R18">
+        <v>2.5</v>
+      </c>
+      <c r="S18">
+        <v>1.22</v>
+      </c>
+      <c r="T18">
+        <v>4.5</v>
+      </c>
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
+        <v>1.69</v>
+      </c>
+      <c r="W18">
+        <v>1.16</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.1</v>
+      </c>
+      <c r="Z18">
+        <v>6</v>
+      </c>
+      <c r="AA18">
+        <v>1.37</v>
+      </c>
+      <c r="AB18">
+        <v>2.94</v>
+      </c>
+      <c r="AC18">
+        <v>1.98</v>
+      </c>
+      <c r="AD18">
         <v>1.77</v>
       </c>
-      <c r="O18">
-        <v>3.75</v>
-      </c>
-      <c r="P18">
-        <v>3.25</v>
-      </c>
-      <c r="Q18">
-        <v>2.24</v>
-      </c>
-      <c r="R18">
-        <v>2.42</v>
-      </c>
-      <c r="S18">
-        <v>1.21</v>
-      </c>
-      <c r="T18">
-        <v>3.68</v>
-      </c>
-      <c r="U18">
-        <v>2.17</v>
-      </c>
-      <c r="V18">
-        <v>1.63</v>
-      </c>
-      <c r="W18">
-        <v>1.13</v>
-      </c>
-      <c r="X18">
-        <v>1.03</v>
-      </c>
-      <c r="Y18">
-        <v>1.12</v>
-      </c>
-      <c r="Z18">
-        <v>7.29</v>
-      </c>
-      <c r="AA18">
-        <v>1.53</v>
-      </c>
-      <c r="AB18">
-        <v>2.4</v>
-      </c>
-      <c r="AC18">
-        <v>2.31</v>
-      </c>
-      <c r="AD18">
-        <v>1.63</v>
-      </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF18">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG18">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="O19">
-        <v>3.92</v>
+        <v>3.55</v>
       </c>
       <c r="P19">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="Q19">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="R19">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T19">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="V19">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>4.54</v>
       </c>
       <c r="AA19">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AB19">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AC19">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="AD19">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE19">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF19">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AG19">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK19">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3614,10 +3614,10 @@
         <v>2.75</v>
       </c>
       <c r="AC20">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD20">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE20">
         <v>1.27</v>
@@ -3642,7 +3642,7 @@
         <v>1.27</v>
       </c>
       <c r="AK20">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="O23">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P23">
-        <v>4.8</v>
+        <v>5.85</v>
       </c>
       <c r="Q23">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R23">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="S23">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T23">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="U23">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V23">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z23">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA23">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB23">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AC23">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AD23">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE23">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="O24">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P24">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q24">
         <v>5</v>
       </c>
       <c r="R24">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="S24">
         <v>1.22</v>
@@ -4242,10 +4242,10 @@
         <v>3.8</v>
       </c>
       <c r="U24">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="V24">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W24">
         <v>1.14</v>
@@ -4254,32 +4254,32 @@
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="AA24">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB24">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="AC24">
+        <v>2.25</v>
+      </c>
+      <c r="AD24">
+        <v>1.62</v>
+      </c>
+      <c r="AE24">
+        <v>1.21</v>
+      </c>
+      <c r="AF24">
+        <v>1.6</v>
+      </c>
+      <c r="AG24">
         <v>2.15</v>
       </c>
-      <c r="AD24">
-        <v>1.69</v>
-      </c>
-      <c r="AE24">
-        <v>1.28</v>
-      </c>
-      <c r="AF24">
-        <v>1.57</v>
-      </c>
-      <c r="AG24">
-        <v>2.25</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>2.63</v>
       </c>
       <c r="AK24">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.13</v>
+        <v>1.86</v>
       </c>
       <c r="O26">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="P26">
-        <v>3.41</v>
+        <v>4.12</v>
       </c>
       <c r="Q26">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S26">
         <v>1.32</v>
@@ -4580,31 +4580,31 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z26">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA26">
         <v>2.07</v>
       </c>
       <c r="AB26">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AC26">
         <v>3.65</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O28">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q28">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R28">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S28">
         <v>1.2</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="U28">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="V28">
         <v>1.69</v>
       </c>
       <c r="W28">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z28">
-        <v>6.29</v>
+        <v>5.8</v>
       </c>
       <c r="AA28">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB28">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="AC28">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD28">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE28">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF28">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P33">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="R33">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="S33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U33">
         <v>2.29</v>
@@ -5715,22 +5715,22 @@
         <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
         <v>4.45</v>
       </c>
       <c r="AA33">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="AC33">
         <v>2.29</v>
@@ -5739,7 +5739,7 @@
         <v>1.55</v>
       </c>
       <c r="AE33">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
         <v>1.5</v>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.96</v>
+        <v>4.2</v>
       </c>
       <c r="O34">
-        <v>3.11</v>
+        <v>3.9</v>
       </c>
       <c r="P34">
-        <v>4.32</v>
+        <v>1.66</v>
       </c>
       <c r="Q34">
-        <v>2.43</v>
+        <v>4.82</v>
       </c>
       <c r="R34">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="S34">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U34">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z34">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA34">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AB34">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG34">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>1.94</v>
+        <v>1.14</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-07-26 10:00:00</t>
+          <t>2026-07-26 10:45:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>4.2</v>
+        <v>1.74</v>
       </c>
       <c r="O35">
+        <v>3.4</v>
+      </c>
+      <c r="P35">
         <v>3.9</v>
       </c>
-      <c r="P35">
-        <v>1.66</v>
-      </c>
       <c r="Q35">
-        <v>4.82</v>
+        <v>2.38</v>
       </c>
       <c r="R35">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="S35">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="T35">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="U35">
-        <v>2.46</v>
+        <v>3.19</v>
       </c>
       <c r="V35">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z35">
-        <v>4.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA35">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AB35">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AC35">
-        <v>2.58</v>
+        <v>3.84</v>
       </c>
       <c r="AD35">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AF35">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="AG35">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK35">
-        <v>1.14</v>
+        <v>1.99</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-07-26 10:45:00</t>
+          <t>2026-07-26 11:00:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>4.02</v>
       </c>
       <c r="P36">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="Q36">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="R36">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T36">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="U36">
-        <v>3.19</v>
+        <v>2.62</v>
       </c>
       <c r="V36">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z36">
-        <v>3.04</v>
+        <v>3.93</v>
       </c>
       <c r="AA36">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="AB36">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AC36">
-        <v>3.84</v>
+        <v>2.86</v>
       </c>
       <c r="AD36">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE36">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="O37">
-        <v>4.02</v>
+        <v>4.85</v>
       </c>
       <c r="P37">
-        <v>4.35</v>
+        <v>6.6</v>
       </c>
       <c r="Q37">
-        <v>2.21</v>
+        <v>1.81</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="T37">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="U37">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>3.93</v>
+        <v>5.5</v>
       </c>
       <c r="AA37">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="AB37">
-        <v>2.03</v>
+        <v>2.75</v>
       </c>
       <c r="AC37">
-        <v>2.86</v>
+        <v>2.06</v>
       </c>
       <c r="AD37">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG37">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="O38">
-        <v>4.85</v>
+        <v>3.11</v>
       </c>
       <c r="P38">
-        <v>6.6</v>
+        <v>4.32</v>
       </c>
       <c r="Q38">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="R38">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="T38">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="U38">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="V38">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
+        <v>1.25</v>
+      </c>
+      <c r="Z38">
+        <v>3.5</v>
+      </c>
+      <c r="AA38">
+        <v>1.87</v>
+      </c>
+      <c r="AB38">
+        <v>1.9</v>
+      </c>
+      <c r="AC38">
+        <v>3</v>
+      </c>
+      <c r="AD38">
+        <v>1.33</v>
+      </c>
+      <c r="AE38">
         <v>1.08</v>
       </c>
-      <c r="Z38">
-        <v>5.5</v>
-      </c>
-      <c r="AA38">
-        <v>1.45</v>
-      </c>
-      <c r="AB38">
-        <v>2.75</v>
-      </c>
-      <c r="AC38">
-        <v>2.06</v>
-      </c>
-      <c r="AD38">
-        <v>1.7</v>
-      </c>
-      <c r="AE38">
-        <v>1.29</v>
-      </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AG38">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.8</v>
+        <v>1.94</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,7 +6669,7 @@
         <v>1.44</v>
       </c>
       <c r="O39">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="P39">
         <v>8.4</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
       <c r="P40">
-        <v>2.91</v>
+        <v>3.32</v>
       </c>
       <c r="Q40">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R40">
         <v>2.2</v>
@@ -6862,31 +6862,31 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z40">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA40">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB40">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AC40">
         <v>3.3</v>
       </c>
       <c r="AD40">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AG40">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="O43">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="P43">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q43">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R43">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
         <v>1.29</v>
       </c>
       <c r="T43">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U43">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V43">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB43">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AC43">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="AD43">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE43">
         <v>1.15</v>
       </c>
       <c r="AF43">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O44">
-        <v>3.57</v>
+        <v>3.72</v>
       </c>
       <c r="P44">
-        <v>3.18</v>
+        <v>3.88</v>
       </c>
       <c r="Q44">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="R44">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T44">
         <v>3.15</v>
       </c>
       <c r="U44">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V44">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W44">
         <v>1.1</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>4.15</v>
+        <v>4.42</v>
       </c>
       <c r="AA44">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB44">
         <v>2.2</v>
       </c>
       <c r="AC44">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AD44">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE44">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
         <v>1.61</v>
       </c>
       <c r="AG44">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8462,10 +8462,10 @@
         <v>2.8</v>
       </c>
       <c r="O50">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P50">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q50">
         <v>3.63</v>
@@ -8474,10 +8474,10 @@
         <v>2.11</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T50">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U50">
         <v>2.56</v>
@@ -8489,34 +8489,34 @@
         <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AA50">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB50">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
         <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8622,22 +8622,22 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="O51">
+        <v>3.6</v>
+      </c>
+      <c r="P51">
+        <v>2.19</v>
+      </c>
+      <c r="Q51">
         <v>3.4</v>
       </c>
-      <c r="P51">
-        <v>2.1</v>
-      </c>
-      <c r="Q51">
-        <v>3.46</v>
-      </c>
       <c r="R51">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
         <v>3.3</v>
@@ -8646,7 +8646,7 @@
         <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
         <v>1.08</v>
@@ -8655,19 +8655,19 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA51">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AB51">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC51">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="AD51">
         <v>1.39</v>
@@ -8676,10 +8676,10 @@
         <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AG51">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
         <v>1.38</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="O52">
-        <v>4.85</v>
+        <v>3.91</v>
       </c>
       <c r="P52">
-        <v>1.32</v>
+        <v>3.93</v>
       </c>
       <c r="Q52">
-        <v>5.95</v>
+        <v>2.23</v>
       </c>
       <c r="R52">
-        <v>2.68</v>
+        <v>2.32</v>
       </c>
       <c r="S52">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T52">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="U52">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="V52">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>6.2</v>
+        <v>4.65</v>
       </c>
       <c r="AA52">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AB52">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="AC52">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="AD52">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="AE52">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF52">
         <v>1.53</v>
       </c>
       <c r="AG52">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.09</v>
+        <v>2.1</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,61 +8948,61 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.86</v>
+        <v>6.75</v>
       </c>
       <c r="O53">
-        <v>3.91</v>
+        <v>5.4</v>
       </c>
       <c r="P53">
-        <v>3.93</v>
+        <v>1.36</v>
       </c>
       <c r="Q53">
-        <v>2.24</v>
+        <v>5.95</v>
       </c>
       <c r="R53">
-        <v>2.54</v>
+        <v>2.97</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T53">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="U53">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="V53">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="W53">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z53">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AA53">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AB53">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="AC53">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
       <c r="AD53">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AE53">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF53">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG53">
         <v>2.3</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK53">
-        <v>2.08</v>
+        <v>1.09</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="O57">
-        <v>3.49</v>
+        <v>3.94</v>
       </c>
       <c r="P57">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q57">
-        <v>2.47</v>
+        <v>3.13</v>
       </c>
       <c r="R57">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>4.5</v>
+        <v>3.82</v>
       </c>
       <c r="U57">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="V57">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="W57">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z57">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA57">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AB57">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC57">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="AD57">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="AE57">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AF57">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG57">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK57">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="O58">
-        <v>3.94</v>
+        <v>3.49</v>
       </c>
       <c r="P58">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="Q58">
-        <v>3.13</v>
+        <v>2.47</v>
       </c>
       <c r="R58">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S58">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T58">
-        <v>3.82</v>
+        <v>4.5</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="V58">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="W58">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z58">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA58">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AB58">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="AC58">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AD58">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="AE58">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AF58">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG58">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="O59">
-        <v>2.87</v>
+        <v>3.11</v>
       </c>
       <c r="P59">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="Q59">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R59">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S59">
         <v>1.4</v>
@@ -9956,34 +9956,34 @@
         <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z59">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA59">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB59">
+        <v>1.74</v>
+      </c>
+      <c r="AC59">
+        <v>3.4</v>
+      </c>
+      <c r="AD59">
+        <v>1.26</v>
+      </c>
+      <c r="AE59">
+        <v>1.05</v>
+      </c>
+      <c r="AF59">
         <v>1.8</v>
       </c>
-      <c r="AC59">
-        <v>3</v>
-      </c>
-      <c r="AD59">
-        <v>1.32</v>
-      </c>
-      <c r="AE59">
-        <v>1.07</v>
-      </c>
-      <c r="AF59">
-        <v>1.71</v>
-      </c>
       <c r="AG59">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AK59">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10424,22 +10424,22 @@
         <v>1.91</v>
       </c>
       <c r="Q62">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R62">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="S62">
         <v>1.3</v>
       </c>
       <c r="T62">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="U62">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="V62">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W62">
         <v>1.1</v>
@@ -10454,19 +10454,19 @@
         <v>4</v>
       </c>
       <c r="AA62">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB62">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AC62">
         <v>2.43</v>
       </c>
       <c r="AD62">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AE62">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
         <v>1.47</v>
@@ -10488,7 +10488,7 @@
         <v>1.57</v>
       </c>
       <c r="AK62">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11402,7 +11402,7 @@
         <v>3.8</v>
       </c>
       <c r="Q68">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R68">
         <v>2.34</v>
@@ -11450,7 +11450,7 @@
         <v>1.52</v>
       </c>
       <c r="AG68">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O78">
-        <v>4.68</v>
+        <v>4.4</v>
       </c>
       <c r="P78">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Q78">
         <v>5</v>
       </c>
       <c r="R78">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="S78">
         <v>1.2</v>
@@ -13056,28 +13056,28 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z78">
-        <v>5.55</v>
+        <v>6.26</v>
       </c>
       <c r="AA78">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB78">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AC78">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD78">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE78">
         <v>1.28</v>
       </c>
       <c r="AF78">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG78">
         <v>2.44</v>
@@ -13096,7 +13096,7 @@
         <v>1.19</v>
       </c>
       <c r="AK78">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O81">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="P81">
         <v>3.35</v>
       </c>
       <c r="Q81">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="R81">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="S81">
         <v>1.76</v>
@@ -13536,13 +13536,13 @@
         <v>4.33</v>
       </c>
       <c r="V81">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W81">
         <v>1.02</v>
       </c>
       <c r="X81">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Y81">
         <v>1.75</v>
@@ -13557,10 +13557,10 @@
         <v>1.28</v>
       </c>
       <c r="AC81">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AD81">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AE81">
         <v>1.02</v>
@@ -13684,7 +13684,7 @@
         <v>3.9</v>
       </c>
       <c r="Q82">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="R82">
         <v>1.83</v>
@@ -13699,7 +13699,7 @@
         <v>4.15</v>
       </c>
       <c r="V82">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W82">
         <v>1.03</v>
@@ -13708,10 +13708,10 @@
         <v>1.08</v>
       </c>
       <c r="Y82">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z82">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AA82">
         <v>2.88</v>
@@ -13723,16 +13723,16 @@
         <v>6.25</v>
       </c>
       <c r="AD82">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE82">
         <v>1.03</v>
       </c>
       <c r="AF82">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AG82">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O83">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="P83">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="Q83">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="R83">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="S83">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="T83">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U83">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="V83">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X83">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y83">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z83">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AA83">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="AB83">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC83">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD83">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG83">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK83">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O84">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="P84">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="Q84">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="R84">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="S84">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="T84">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U84">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="V84">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
+        <v>1.08</v>
+      </c>
+      <c r="Y84">
+        <v>1.62</v>
+      </c>
+      <c r="Z84">
+        <v>2.16</v>
+      </c>
+      <c r="AA84">
+        <v>3.1</v>
+      </c>
+      <c r="AB84">
+        <v>1.36</v>
+      </c>
+      <c r="AC84">
+        <v>5.4</v>
+      </c>
+      <c r="AD84">
         <v>1.1</v>
-      </c>
-      <c r="Y84">
-        <v>1.57</v>
-      </c>
-      <c r="Z84">
-        <v>2.25</v>
-      </c>
-      <c r="AA84">
-        <v>2.6</v>
-      </c>
-      <c r="AB84">
-        <v>1.37</v>
-      </c>
-      <c r="AC84">
-        <v>5.3</v>
-      </c>
-      <c r="AD84">
-        <v>1.13</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG84">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK84">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q90">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="R90">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="S90">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="U90">
-        <v>3.76</v>
+        <v>3.32</v>
       </c>
       <c r="V90">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="W90">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X90">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y90">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="Z90">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AA90">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AB90">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AC90">
-        <v>5.35</v>
+        <v>4.13</v>
       </c>
       <c r="AD90">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AE90">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF90">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG90">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK90">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,65 +15142,65 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="R91">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="S91">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="T91">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="U91">
-        <v>3.32</v>
+        <v>3.76</v>
       </c>
       <c r="V91">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X91">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y91">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z91">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AA91">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AB91">
+        <v>1.39</v>
+      </c>
+      <c r="AC91">
+        <v>5.35</v>
+      </c>
+      <c r="AD91">
+        <v>1.09</v>
+      </c>
+      <c r="AE91">
+        <v>1.03</v>
+      </c>
+      <c r="AF91">
+        <v>2.17</v>
+      </c>
+      <c r="AG91">
         <v>1.58</v>
       </c>
-      <c r="AC91">
-        <v>4.13</v>
-      </c>
-      <c r="AD91">
-        <v>1.21</v>
-      </c>
-      <c r="AE91">
-        <v>1</v>
-      </c>
-      <c r="AF91">
-        <v>1.93</v>
-      </c>
-      <c r="AG91">
-        <v>1.75</v>
-      </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK91">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15797,10 +15797,10 @@
         <v>1.63</v>
       </c>
       <c r="O95">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P95">
-        <v>6.4</v>
+        <v>5.91</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -16005,7 +16005,7 @@
         <v>5.12</v>
       </c>
       <c r="AD96">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE96">
         <v>1.01</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK96">
         <v>2.14</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="O97">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="P97">
-        <v>4.36</v>
+        <v>4.46</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O98">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P98">
         <v>3.4</v>
@@ -16295,7 +16295,7 @@
         <v>2.63</v>
       </c>
       <c r="R98">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S98">
         <v>1.36</v>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O105">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P105">
         <v>5.6</v>
       </c>
       <c r="Q105">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="R105">
         <v>2.11</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O106">
         <v>2.95</v>
@@ -17623,7 +17623,7 @@
         <v>1.61</v>
       </c>
       <c r="Z106">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AA106">
         <v>2.81</v>
@@ -17632,7 +17632,7 @@
         <v>1.33</v>
       </c>
       <c r="AC106">
-        <v>5.8</v>
+        <v>6.05</v>
       </c>
       <c r="AD106">
         <v>1.07</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="O107">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P107">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q107">
-        <v>2.71</v>
+        <v>2.32</v>
       </c>
       <c r="R107">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S107">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T107">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U107">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="V107">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W107">
+        <v>1.01</v>
+      </c>
+      <c r="X107">
+        <v>1.08</v>
+      </c>
+      <c r="Y107">
+        <v>1.57</v>
+      </c>
+      <c r="Z107">
+        <v>2.36</v>
+      </c>
+      <c r="AA107">
+        <v>2.59</v>
+      </c>
+      <c r="AB107">
+        <v>1.39</v>
+      </c>
+      <c r="AC107">
+        <v>4.5</v>
+      </c>
+      <c r="AD107">
+        <v>1.15</v>
+      </c>
+      <c r="AE107">
         <v>1.03</v>
       </c>
-      <c r="X107">
-        <v>1.1</v>
-      </c>
-      <c r="Y107">
-        <v>1.56</v>
-      </c>
-      <c r="Z107">
-        <v>2.23</v>
-      </c>
-      <c r="AA107">
-        <v>2.88</v>
-      </c>
-      <c r="AB107">
-        <v>1.36</v>
-      </c>
-      <c r="AC107">
-        <v>5.95</v>
-      </c>
-      <c r="AD107">
-        <v>1.07</v>
-      </c>
-      <c r="AE107">
-        <v>1.02</v>
-      </c>
       <c r="AF107">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AG107">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK107">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="O108">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="P108">
-        <v>5.85</v>
+        <v>4</v>
       </c>
       <c r="Q108">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="R108">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="S108">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="T108">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U108">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="V108">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="W108">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X108">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y108">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="Z108">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="AA108">
-        <v>2.59</v>
+        <v>2.92</v>
       </c>
       <c r="AB108">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AC108">
-        <v>4.5</v>
+        <v>6.15</v>
       </c>
       <c r="AD108">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE108">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF108">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AG108">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK108">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18734,7 +18734,7 @@
         <v>3.2</v>
       </c>
       <c r="P113">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O115">
         <v>3.1</v>
@@ -19869,16 +19869,16 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O120">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="P120">
-        <v>6.8</v>
+        <v>6.25</v>
       </c>
       <c r="Q120">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R120">
         <v>2.24</v>
@@ -19899,19 +19899,19 @@
         <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z120">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="AA120">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC120">
         <v>3.12</v>
@@ -20047,7 +20047,7 @@
         <v>2.2</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T121">
         <v>2.77</v>
@@ -20056,7 +20056,7 @@
         <v>2.88</v>
       </c>
       <c r="V121">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W121">
         <v>1.05</v>
@@ -20089,7 +20089,7 @@
         <v>1.92</v>
       </c>
       <c r="AG121">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AK121">
         <v>2.2</v>
@@ -20195,10 +20195,10 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="O122">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P122">
         <v>2.65</v>
@@ -20234,10 +20234,10 @@
         <v>3.35</v>
       </c>
       <c r="AA122">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB122">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC122">
         <v>3.05</v>
@@ -21013,28 +21013,28 @@
         <v>1.68</v>
       </c>
       <c r="O127">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="P127">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="Q127">
         <v>2.23</v>
       </c>
       <c r="R127">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S127">
         <v>1.42</v>
       </c>
       <c r="T127">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U127">
         <v>2.85</v>
       </c>
       <c r="V127">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W127">
         <v>1.05</v>
@@ -21182,13 +21182,13 @@
         <v>3.29</v>
       </c>
       <c r="Q128">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R128">
         <v>2.05</v>
       </c>
       <c r="S128">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T128">
         <v>2.73</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK128">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AL128">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O11">
+        <v>3.3</v>
+      </c>
+      <c r="P11">
         <v>3.38</v>
       </c>
-      <c r="P11">
-        <v>3.6</v>
-      </c>
       <c r="Q11">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
         <v>1.06</v>
@@ -2135,31 +2135,31 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="AA11">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB11">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="AD11">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P12">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="Q12">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R12">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
+        <v>2.66</v>
+      </c>
+      <c r="U12">
         <v>2.88</v>
       </c>
-      <c r="U12">
-        <v>2.4</v>
-      </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -2298,32 +2298,32 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="AA12">
+        <v>2.1</v>
+      </c>
+      <c r="AB12">
+        <v>1.72</v>
+      </c>
+      <c r="AC12">
+        <v>3.58</v>
+      </c>
+      <c r="AD12">
+        <v>1.21</v>
+      </c>
+      <c r="AE12">
+        <v>1.03</v>
+      </c>
+      <c r="AF12">
+        <v>1.86</v>
+      </c>
+      <c r="AG12">
         <v>1.85</v>
       </c>
-      <c r="AB12">
-        <v>1.95</v>
-      </c>
-      <c r="AC12">
-        <v>3</v>
-      </c>
-      <c r="AD12">
-        <v>1.31</v>
-      </c>
-      <c r="AE12">
-        <v>1.09</v>
-      </c>
-      <c r="AF12">
-        <v>1.67</v>
-      </c>
-      <c r="AG12">
-        <v>2</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,58 +8785,58 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.86</v>
+        <v>6.75</v>
       </c>
       <c r="O52">
-        <v>3.91</v>
+        <v>5.4</v>
       </c>
       <c r="P52">
-        <v>3.93</v>
+        <v>1.36</v>
       </c>
       <c r="Q52">
-        <v>2.23</v>
+        <v>5.95</v>
       </c>
       <c r="R52">
-        <v>2.32</v>
+        <v>2.97</v>
       </c>
       <c r="S52">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T52">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="U52">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="V52">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z52">
-        <v>4.65</v>
+        <v>6.2</v>
       </c>
       <c r="AA52">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AB52">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="AC52">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="AD52">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="AE52">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF52">
         <v>1.53</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK52">
-        <v>2.1</v>
+        <v>1.09</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,58 +8948,58 @@
         </is>
       </c>
       <c r="N53">
-        <v>6.75</v>
+        <v>1.86</v>
       </c>
       <c r="O53">
-        <v>5.4</v>
+        <v>3.91</v>
       </c>
       <c r="P53">
-        <v>1.36</v>
+        <v>3.93</v>
       </c>
       <c r="Q53">
-        <v>5.95</v>
+        <v>2.23</v>
       </c>
       <c r="R53">
-        <v>2.97</v>
+        <v>2.32</v>
       </c>
       <c r="S53">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="U53">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="V53">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="W53">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z53">
-        <v>6.2</v>
+        <v>4.65</v>
       </c>
       <c r="AA53">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AB53">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="AC53">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="AD53">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="AE53">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF53">
         <v>1.53</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.09</v>
+        <v>2.1</v>
       </c>
       <c r="AL53">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="O2">
+        <v>3.5</v>
+      </c>
+      <c r="P2">
+        <v>2.25</v>
+      </c>
+      <c r="Q2">
+        <v>2.93</v>
+      </c>
+      <c r="R2">
+        <v>2.22</v>
+      </c>
+      <c r="S2">
+        <v>1.29</v>
+      </c>
+      <c r="T2">
         <v>3.4</v>
       </c>
-      <c r="P2">
-        <v>2.7</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,22 +807,22 @@
         <v>3.85</v>
       </c>
       <c r="Q3">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U3">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="V3">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
         <v>1.15</v>
@@ -831,7 +831,7 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z3">
         <v>5</v>
@@ -843,19 +843,19 @@
         <v>2.38</v>
       </c>
       <c r="AC3">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AD3">
         <v>1.64</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF3">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG3">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P11">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
+        <v>2.56</v>
+      </c>
+      <c r="U11">
         <v>2.88</v>
       </c>
-      <c r="U11">
-        <v>2.4</v>
-      </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
         <v>1.06</v>
@@ -2135,31 +2135,31 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="AA11">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC11">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="AD11">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G12">
@@ -2268,28 +2268,28 @@
         <v>1.8</v>
       </c>
       <c r="O12">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="P12">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q12">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -2298,47 +2298,47 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z12">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="AD12">
+        <v>1.31</v>
+      </c>
+      <c r="AE12">
+        <v>1.09</v>
+      </c>
+      <c r="AF12">
+        <v>1.67</v>
+      </c>
+      <c r="AG12">
+        <v>2</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.21</v>
       </c>
-      <c r="AE12">
-        <v>1.03</v>
-      </c>
-      <c r="AF12">
-        <v>1.86</v>
-      </c>
-      <c r="AG12">
-        <v>1.85</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.23</v>
-      </c>
       <c r="AK12">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="O18">
-        <v>3.92</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="Q18">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="R18">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T18">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="V18">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="W18">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>4.54</v>
       </c>
       <c r="AA18">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AB18">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="AC18">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="AD18">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AE18">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AG18">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK18">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="O19">
-        <v>3.55</v>
+        <v>3.92</v>
       </c>
       <c r="P19">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="Q19">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="R19">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="U19">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>4.54</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AB19">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="AC19">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="AD19">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AE19">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF19">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG19">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -12371,31 +12371,31 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>8.1</v>
+        <v>8.65</v>
       </c>
       <c r="Q74">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R74">
         <v>3</v>
       </c>
       <c r="S74">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="T74">
-        <v>4.15</v>
+        <v>3.13</v>
       </c>
       <c r="U74">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V74">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="W74">
         <v>1.18</v>
@@ -12410,7 +12410,7 @@
         <v>6.9</v>
       </c>
       <c r="AA74">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AB74">
         <v>2.64</v>
@@ -12425,10 +12425,10 @@
         <v>1.36</v>
       </c>
       <c r="AF74">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AG74">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
+        <v>2.4</v>
+      </c>
+      <c r="O82">
+        <v>2.84</v>
+      </c>
+      <c r="P82">
+        <v>3.03</v>
+      </c>
+      <c r="Q82">
+        <v>3.3</v>
+      </c>
+      <c r="R82">
         <v>1.95</v>
       </c>
-      <c r="O82">
-        <v>2.8</v>
-      </c>
-      <c r="P82">
-        <v>3.9</v>
-      </c>
-      <c r="Q82">
-        <v>2.77</v>
-      </c>
-      <c r="R82">
-        <v>1.83</v>
-      </c>
       <c r="S82">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="T82">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U82">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="V82">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X82">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y82">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z82">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AA82">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AB82">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AC82">
-        <v>6.25</v>
+        <v>5.3</v>
       </c>
       <c r="AD82">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AE82">
         <v>1.03</v>
       </c>
       <c r="AF82">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AG82">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK82">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O83">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="P83">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="Q83">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="R83">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="S83">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="T83">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U83">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="V83">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="W83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
+        <v>1.08</v>
+      </c>
+      <c r="Y83">
+        <v>1.62</v>
+      </c>
+      <c r="Z83">
+        <v>2.16</v>
+      </c>
+      <c r="AA83">
+        <v>3.1</v>
+      </c>
+      <c r="AB83">
+        <v>1.36</v>
+      </c>
+      <c r="AC83">
+        <v>5.4</v>
+      </c>
+      <c r="AD83">
         <v>1.1</v>
-      </c>
-      <c r="Y83">
-        <v>1.57</v>
-      </c>
-      <c r="Z83">
-        <v>2.25</v>
-      </c>
-      <c r="AA83">
-        <v>2.66</v>
-      </c>
-      <c r="AB83">
-        <v>1.37</v>
-      </c>
-      <c r="AC83">
-        <v>5.3</v>
-      </c>
-      <c r="AD83">
-        <v>1.13</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG83">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK83">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,28 +14001,28 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O84">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P84">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q84">
-        <v>3.06</v>
+        <v>2.77</v>
       </c>
       <c r="R84">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="S84">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="T84">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U84">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="V84">
         <v>1.16</v>
@@ -14034,31 +14034,31 @@
         <v>1.08</v>
       </c>
       <c r="Y84">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z84">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AA84">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB84">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC84">
-        <v>5.4</v>
+        <v>6.25</v>
       </c>
       <c r="AD84">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AG84">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK84">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,65 +14979,65 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="R90">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="S90">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="T90">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="U90">
-        <v>3.32</v>
+        <v>3.76</v>
       </c>
       <c r="V90">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X90">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y90">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z90">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AA90">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AB90">
+        <v>1.39</v>
+      </c>
+      <c r="AC90">
+        <v>5.35</v>
+      </c>
+      <c r="AD90">
+        <v>1.09</v>
+      </c>
+      <c r="AE90">
+        <v>1.03</v>
+      </c>
+      <c r="AF90">
+        <v>2.17</v>
+      </c>
+      <c r="AG90">
         <v>1.58</v>
       </c>
-      <c r="AC90">
-        <v>4.13</v>
-      </c>
-      <c r="AD90">
-        <v>1.21</v>
-      </c>
-      <c r="AE90">
-        <v>1</v>
-      </c>
-      <c r="AF90">
-        <v>1.93</v>
-      </c>
-      <c r="AG90">
-        <v>1.75</v>
-      </c>
       <c r="AH90" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK90">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q91">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="R91">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="S91">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="T91">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="U91">
-        <v>3.76</v>
+        <v>3.32</v>
       </c>
       <c r="V91">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="W91">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y91">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="Z91">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AA91">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AB91">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AC91">
-        <v>5.35</v>
+        <v>4.13</v>
       </c>
       <c r="AD91">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AE91">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF91">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG91">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK91">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N93">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O94">
         <v>2.95</v>
@@ -15646,10 +15646,10 @@
         <v>1.95</v>
       </c>
       <c r="S94">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U94">
         <v>2.88</v>
@@ -15664,13 +15664,13 @@
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z94">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA94">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="AB94">
         <v>1.73</v>
@@ -17119,13 +17119,13 @@
         <v>3.1</v>
       </c>
       <c r="U103">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V103">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W103">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
         <v>1.04</v>
@@ -17137,13 +17137,13 @@
         <v>3.95</v>
       </c>
       <c r="AA103">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB103">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC103">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AD103">
         <v>1.39</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q109">
-        <v>2.34</v>
+        <v>3.12</v>
       </c>
       <c r="R109">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="S109">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="T109">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="U109">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="V109">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="W109">
         <v>1.01</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y109">
+        <v>1.45</v>
+      </c>
+      <c r="Z109">
+        <v>2.41</v>
+      </c>
+      <c r="AA109">
+        <v>2.55</v>
+      </c>
+      <c r="AB109">
+        <v>1.5</v>
+      </c>
+      <c r="AC109">
+        <v>4.5</v>
+      </c>
+      <c r="AD109">
+        <v>1.13</v>
+      </c>
+      <c r="AE109">
+        <v>1</v>
+      </c>
+      <c r="AF109">
+        <v>2.03</v>
+      </c>
+      <c r="AG109">
+        <v>1.67</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
         <v>1.36</v>
       </c>
-      <c r="Z109">
-        <v>3.1</v>
-      </c>
-      <c r="AA109">
-        <v>2</v>
-      </c>
-      <c r="AB109">
-        <v>1.65</v>
-      </c>
-      <c r="AC109">
-        <v>3.6</v>
-      </c>
-      <c r="AD109">
-        <v>1.19</v>
-      </c>
-      <c r="AE109">
-        <v>1.05</v>
-      </c>
-      <c r="AF109">
-        <v>2</v>
-      </c>
-      <c r="AG109">
-        <v>1.82</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.26</v>
-      </c>
       <c r="AK109">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,80 +18239,80 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.12</v>
+        <v>2.34</v>
       </c>
       <c r="R110">
-        <v>1.74</v>
+        <v>2.18</v>
       </c>
       <c r="S110">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="T110">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="U110">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="V110">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="W110">
         <v>1.01</v>
       </c>
       <c r="X110">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="Z110">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="AA110">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AB110">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC110">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD110">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE110">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
+        <v>2</v>
+      </c>
+      <c r="AG110">
+        <v>1.82</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
+        <v>1.26</v>
+      </c>
+      <c r="AK110">
         <v>2.03</v>
-      </c>
-      <c r="AG110">
-        <v>1.67</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.36</v>
-      </c>
-      <c r="AK110">
-        <v>1.44</v>
       </c>
       <c r="AL110">
         <v>0</v>

--- a/jogos_2026-07-26.xlsx
+++ b/jogos_2026-07-26.xlsx
@@ -674,10 +674,10 @@
         <v>3.75</v>
       </c>
       <c r="AA2">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB2">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC2">
         <v>2.6</v>
@@ -843,7 +843,7 @@
         <v>2.38</v>
       </c>
       <c r="AC3">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AD3">
         <v>1.64</v>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q4">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="R4">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
         <v>1.11</v>
@@ -994,28 +994,28 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AA4">
         <v>1.72</v>
       </c>
       <c r="AB4">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AC4">
         <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
         <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG4">
         <v>2.2</v>
@@ -1034,7 +1034,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         <v>2.74</v>
       </c>
       <c r="AA5">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AB5">
         <v>1.67</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O6">
         <v>3.55</v>
       </c>
       <c r="P6">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="Q6">
+        <v>2.1</v>
+      </c>
+      <c r="R6">
         <v>2.2</v>
-      </c>
-      <c r="R6">
-        <v>2.33</v>
       </c>
       <c r="S6">
         <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="U6">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA6">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
         <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P7">
         <v>2</v>
@@ -1489,22 +1489,22 @@
         <v>2.57</v>
       </c>
       <c r="AA7">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AC7">
         <v>4</v>
       </c>
       <c r="AD7">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG7">
         <v>1.7</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
         <v>1.22</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="O8">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="Q8">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
         <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V8">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
         <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
         <v>1.23</v>
       </c>
       <c r="Z8">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AA8">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
         <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AD8">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,43 +1776,43 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="O9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q9">
-        <v>5.02</v>
+        <v>4.85</v>
       </c>
       <c r="R9">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S9">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T9">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U9">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z9">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AA9">
         <v>2.23</v>
@@ -1827,7 +1827,7 @@
         <v>1.17</v>
       </c>
       <c r="AE9">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
         <v>2</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="AK9">
         <v>1.22</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="P10">
         <v>4.5</v>
@@ -1957,25 +1957,25 @@
         <v>1.5</v>
       </c>
       <c r="T10">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U10">
         <v>3.3</v>
       </c>
       <c r="V10">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
         <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z10">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AA10">
         <v>2.38</v>
@@ -1984,7 +1984,7 @@
         <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="AD10">
         <v>1.15</v>
@@ -2012,7 +2012,7 @@
         <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="O11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
         <v>3.9</v>
       </c>
       <c r="Q11">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
         <v>1.06</v>
@@ -2135,31 +2135,31 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="AA11">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB11">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="AD11">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G12">
@@ -2268,28 +2268,28 @@
         <v>1.8</v>
       </c>
       <c r="O12">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>3.25</v>
+        <v>3.97</v>
       </c>
       <c r="Q12">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R12">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
+        <v>2.56</v>
+      </c>
+      <c r="U12">
         <v>2.88</v>
       </c>
-      <c r="U12">
-        <v>2.4</v>
-      </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -2298,31 +2298,31 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC12">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="AD12">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -2443,7 +2443,7 @@
         <v>2.55</v>
       </c>
       <c r="S13">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
         <v>4.5</v>
@@ -2452,16 +2452,16 @@
         <v>2.05</v>
       </c>
       <c r="V13">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="W13">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z13">
         <v>10.2</v>
@@ -2473,19 +2473,19 @@
         <v>3.14</v>
       </c>
       <c r="AC13">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="AD13">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE13">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF13">
         <v>1.4</v>
       </c>
       <c r="AG13">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2763,28 +2763,28 @@
         <v>4.6</v>
       </c>
       <c r="Q15">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="S15">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U15">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
         <v>1.28</v>
@@ -2796,22 +2796,22 @@
         <v>2</v>
       </c>
       <c r="AB15">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC15">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG15">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="P16">
         <v>2.67</v>
@@ -2938,7 +2938,7 @@
         <v>2.6</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="V16">
         <v>1.33</v>
@@ -2962,7 +2962,7 @@
         <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="AD16">
         <v>1.23</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AK16">
         <v>1.49</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q17">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="R17">
         <v>2.19</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="U17">
         <v>2.63</v>
@@ -3107,37 +3107,37 @@
         <v>1.39</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z17">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AA17">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB17">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC17">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD17">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AG17">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3246,16 +3246,16 @@
         <v>1.93</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
       </c>
       <c r="R18">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="S18">
         <v>1.21</v>
@@ -3273,10 +3273,10 @@
         <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z18">
         <v>4.54</v>
@@ -3297,10 +3297,10 @@
         <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK18">
         <v>1.83</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="O19">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="Q19">
         <v>2.45</v>
       </c>
       <c r="R19">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T19">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U19">
         <v>2</v>
       </c>
       <c r="V19">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W19">
         <v>1.16</v>
@@ -3445,7 +3445,7 @@
         <v>6</v>
       </c>
       <c r="AA19">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AB19">
         <v>2.94</v>
@@ -3460,10 +3460,10 @@
         <v>1.3</v>
       </c>
       <c r="AF19">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG19">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
         <v>1.79</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="O20">
-        <v>3.83</v>
+        <v>3.55</v>
       </c>
       <c r="P20">
-        <v>3.38</v>
+        <v>2.78</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -3587,7 +3587,7 @@
         <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="U20">
         <v>2.1</v>
@@ -3605,7 +3605,7 @@
         <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="AA20">
         <v>1.47</v>
@@ -3614,10 +3614,10 @@
         <v>2.75</v>
       </c>
       <c r="AC20">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="AD20">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AE20">
         <v>1.27</v>
@@ -3626,7 +3626,7 @@
         <v>1.4</v>
       </c>
       <c r="AG20">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.27</v>
       </c>
       <c r="AK20">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O21">
         <v>3.7</v>
@@ -3747,10 +3747,10 @@
         <v>2.46</v>
       </c>
       <c r="S21">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>3.7</v>
+        <v>3.